--- a/ai_curriculum/AI_course_syllabi_analyzed.xlsx
+++ b/ai_curriculum/AI_course_syllabi_analyzed.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[('12221', 'Program computers to operate machinery.')]</t>
+          <t>[('12221', 'Program computers to operate machinery.'), ('2805', 'Conduct searches to find needed information, using such sources as the Internet.'), ('16257', 'Develop or implement data analysis algorithms.'), ('14293', 'Collaborate with other operators to solve unit problems.'), ('16208', 'Devise missions, challenges, or puzzles to be encountered in game play.')]</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Build and develop chips for artificial intelligence computing.', 'A6.A.8.h.24670'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Develop and apply machine learning and artificial intelligence techniques in robotics and computer vision.', 'A6.J.12.d.28754'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Implement and apply Bayesian modeling techniques in multimodal data analysis, including feature selection and hierarchical Bayesian techniques.', 'A6.C.4.k.28775')]</t>
+          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Build and develop chips for artificial intelligence computing.', 'A6.A.8.h.24670'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Develop and apply machine learning and artificial intelligence techniques in robotics and computer vision.', 'A6.J.12.d.28754'), ('Understand and apply search engine algorithms and ranking factors to enhance organic search results.', 'A6.E.5.l.14614'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Ability to navigate and solve problems in ambiguous and complex situations.', 'A6.B.0.l.18508'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Implement and apply Bayesian modeling techniques in multimodal data analysis, including feature selection and hierarchical Bayesian techniques.', 'A6.C.4.k.28775'), ('Familiarity with reinforcement learning techniques, applications, and advanced optimization methods in various contexts.', 'A6.A.16.b.28784')]</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>0.697</v>
+        <v>0.629</v>
       </c>
       <c r="U2" t="n">
-        <v>0.71</v>
+        <v>0.701</v>
       </c>
       <c r="V2" t="n">
-        <v>0.702</v>
+        <v>0.65</v>
       </c>
       <c r="W2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -852,7 +852,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[('16518', 'Plan mobile robot paths and teach path plans to robots.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16787', 'Develop data models and databases.'), ('12482', 'Collect or select samples for testing or for use as models.'), ('7380', 'Perform validation and testing of models to ensure adequacy, and reformulate models, as necessary.'), ('16257', 'Develop or implement data analysis algorithms.'), ('23947', 'Create mechanical models to simulate mechatronic design concepts.')]</t>
+          <t>[('16518', 'Plan mobile robot paths and teach path plans to robots.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16787', 'Develop data models and databases.'), ('12482', 'Collect or select samples for testing or for use as models.'), ('7380', 'Perform validation and testing of models to ensure adequacy, and reformulate models, as necessary.'), ('15425', 'Create and implement inspection and testing criteria or procedures.'), ('16257', 'Develop or implement data analysis algorithms.'), ('23947', 'Create mechanical models to simulate mechatronic design concepts.')]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[('Solid understanding of machine learning concepts, algorithms, techniques, and their practical applications.', 'A6.J.3.c.29814'), ('Advance learning-based approaches in robotics, including reinforcement learning, imitation learning, and task and motion planning.', 'A6.J.0.e.25091'), ('Research and implement state-of-the-art AI algorithms and techniques to enhance model performance and optimize accuracy, speed, and robustness.', 'A6.J.2.m.28729'), ('Deep understanding of machine learning algorithms and concepts, including supervised, unsupervised, semi-supervised, and reinforcement learning techniques.', 'A6.A.16.b.29090'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Build and apply regression, decision tree, and clustering models for data analysis.', 'A6.J.14.a.28626'), ('Develop and apply statistical and data mining techniques.', 'A6.C.4.r.28458'), ('Program and prototype algorithms using MATLAB, Python, and other engineering tools.', 'A6.B.8.q.26434'), ('Proven experience in developing and applying supervised, unsupervised, and semi-supervised machine learning techniques and algorithms, including regression, classification, and clustering, for data curation and real-world problem solving.', 'A6.J.11.j.28285'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Collect model training data, design model architectures, and train custom models while supporting data preprocessing, evaluation, and performance optimization.', 'A6.J.11.j.27572'), ('Understand and apply model evaluation metrics and techniques for model training and validation.', 'A6.J.11.g.28405'), ('Optimize model performance through hyperparameter tuning, feature engineering, and algorithm selection.', 'A6.E.5.e.29725'), ('Implement algorithms for data analysis and processing.', 'A6.J.8.f.29898'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Implement and manage anomaly detection and predictive maintenance applications and solutions.', 'A6.J.8.f.27841'), ('Develop and test control algorithms, including classical methods, adaptive techniques, and PID tuning, using modeling and simulation for validation.', 'A6.J.9.c.16123'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Solid understanding of data preprocessing, feature engineering, model evaluation, and data manipulation techniques in machine learning.', 'A6.J.11.j.28838'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Proficient in machine learning and deep learning, including building, deploying, and tuning models using supervised, unsupervised, and reinforcement learning techniques.', 'A6.A.16.b.29242'), ('Develop and implement machine learning models and algorithms, including feature engineering and model evaluation.', 'A6.J.11.h.29580'), ('Expertise in selecting, manipulating, and transforming data into features for machine learning algorithms using dimensionality reduction, feature importance, and feature selection techniques.', 'A6.A.16.b.29068'), ('Apply machine learning techniques and mathematical modeling for data analysis and optimization.', 'A6.J.14.a.29132'), ('Possesses a deep understanding of machine learning and deep learning frameworks, techniques, and algorithms, including reinforcement learning and practical implementation experience.', 'A6.A.16.b.29228'), ('Perform modeling, machine learning, and simulations.', 'A6.J.14.d.28308')]</t>
+          <t>[('Possesses an understanding of data needs for AI algorithms and knowledge of AI tools for data analysis and process optimization.', 'A6.J.12.e.25106'), ('Solid understanding of machine learning concepts, algorithms, techniques, and their practical applications.', 'A6.J.3.c.29814'), ('Demonstrates excellent reasoning, analytical, troubleshooting, and problem-solving skills.', 'A6.B.0.c.15752'), ('Advance learning-based approaches in robotics, including reinforcement learning, imitation learning, and task and motion planning.', 'A6.J.0.e.25091'), ('Research and implement state-of-the-art AI algorithms and techniques to enhance model performance and optimize accuracy, speed, and robustness.', 'A6.J.2.m.28729'), ('Deep understanding of machine learning algorithms and concepts, including supervised, unsupervised, semi-supervised, and reinforcement learning techniques.', 'A6.A.16.b.29090'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Build and apply regression, decision tree, and clustering models for data analysis.', 'A6.J.14.a.28626'), ('Develop and apply statistical and data mining techniques.', 'A6.C.4.r.28458'), ('Program and prototype algorithms using MATLAB, Python, and other engineering tools.', 'A6.B.8.q.26434'), ('Proven experience in developing and applying supervised, unsupervised, and semi-supervised machine learning techniques and algorithms, including regression, classification, and clustering, for data curation and real-world problem solving.', 'A6.J.11.j.28285'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Collect model training data, design model architectures, and train custom models while supporting data preprocessing, evaluation, and performance optimization.', 'A6.J.11.j.27572'), ('Understand and apply model evaluation metrics and techniques for model training and validation.', 'A6.J.11.g.28405'), ('Optimize model performance through hyperparameter tuning, feature engineering, and algorithm selection.', 'A6.E.5.e.29725'), ('Proficient in instruction tuning and reinforcement learning from feedback during alignment and post-training processes.', 'A6.A.21.e.25020'), ('Implement algorithms for data analysis and processing.', 'A6.J.8.f.29898'), ('Ability to effectively communicate findings to non-technical audiences while training large language and computer vision models, demonstrated expertise in subdomains such as training optimization, self-supervised learning, explainability, and reinforcement learning from human feedback (RLHF), along with a strong engineering mindset for delivering models at scale.', 'A6.J.11.d.23856'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Apply machine learning techniques, including physics-informed neural networks, for signal or image processing, pattern recognition, and optimization in computational fluid dynamics and finite element analysis.', 'A6.G.0.n.26572'), ('Implement and manage anomaly detection and predictive maintenance applications and solutions.', 'A6.J.8.f.27841'), ('Optimize processes and resources using various optimization techniques and tools.', 'A6.E.5.e.17116'), ('Develop and test control algorithms, including classical methods, adaptive techniques, and PID tuning, using modeling and simulation for validation.', 'A6.J.9.c.16123'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Solid understanding of data preprocessing, feature engineering, model evaluation, and data manipulation techniques in machine learning.', 'A6.J.11.j.28838'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Proficient in machine learning and deep learning, including building, deploying, and tuning models using supervised, unsupervised, and reinforcement learning techniques.', 'A6.A.16.b.29242'), ('Develop and implement machine learning models and algorithms, including feature engineering and model evaluation.', 'A6.J.11.h.29580'), ('Expertise in selecting, manipulating, and transforming data into features for machine learning algorithms using dimensionality reduction, feature importance, and feature selection techniques.', 'A6.A.16.b.29068'), ('Apply machine learning techniques and mathematical modeling for data analysis and optimization.', 'A6.J.14.a.29132'), ('Possesses a deep understanding of machine learning and deep learning frameworks, techniques, and algorithms, including reinforcement learning and practical implementation experience.', 'A6.A.16.b.29228'), ('Perform modeling, machine learning, and simulations.', 'A6.J.14.d.28308')]</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -871,25 +871,25 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S3" t="n">
         <v>24</v>
       </c>
       <c r="T3" t="n">
-        <v>0.677</v>
+        <v>0.647</v>
       </c>
       <c r="U3" t="n">
-        <v>0.722</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.671</v>
+        <v>0.65</v>
       </c>
       <c r="W3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X3" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('21487', 'Develop conceptual designs of security systems.')]</t>
+          <t>[('16577', 'Program complex robotic systems, such as vision systems.'), ('10997', 'Study different techniques to learn how to apply them to artistic endeavors.'), ('4558', "Plan routines, choose appropriate music, and choose different movements for each set of muscles, depending on participants' capabilities and limitations."), ('15952', 'Design or implement products and services to mitigate risk or facilitate use of technology-based tools and methods.'), ('22569', 'Collaborate with other colleagues, such as copyists, to complete final scores.'), ('21128', 'Schedule courses.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('21669', 'Develop or direct software system testing or validation procedures, programming, or documentation.'), ('12751', 'Observe tracks to detect obstructions.'), ('21487', 'Develop conceptual designs of security systems.')]</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Collaborate with data scientists and engineers to design, develop, and implement AI algorithms and models for various applications.', 'A6.J.0.n.28706'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Design, develop, and deploy AI and machine learning models and algorithms for various applications.', 'A6.J.4.d.29855'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Knowledge of various machine learning techniques and algorithms, including their real-world advantages and drawbacks, for effective business decision-making.', 'A6.A.16.a.28018'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Apply advanced machine learning methods, including natural language processing and convolutional neural networks, for predictive modeling and simulation.', 'A6.J.1.d.29179'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Research and develop novel computer vision and machine learning algorithms for 3D scene reconstruction, object detection, motion tracking, and real-time scene understanding.', 'A6.A.10.c.26726'), ('Design and develop algorithms for generative models using deep learning techniques and natural language processing (NLP).', 'A6.J.10.a.29664'), ('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Develop and implement advanced machine learning and generative AI techniques in enterprise applications.', 'A6.J.0.b.29439')]</t>
+          <t>[('Ability to stay updated with the latest advancements in AI, machine learning, data science, and related technologies to drive innovation and improve practices.', 'A6.J.2.s.21248'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Design and implement technology solutions across various applications and infrastructure.', 'A6.F.6.m.15776'), ('Collaborate with data scientists and engineers to design, develop, and implement AI algorithms and models for various applications.', 'A6.J.0.n.28706'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Design, develop, and deploy AI and machine learning models and algorithms for various applications.', 'A6.J.4.d.29855'), ('Develop and maintain applications using Python and other scripting languages in a development environment.', 'A6.K.0.b.18316'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Understand and apply model evaluation metrics and techniques for model training and validation.', 'A6.J.11.g.28405'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Knowledge of various machine learning techniques and algorithms, including their real-world advantages and drawbacks, for effective business decision-making.', 'A6.A.16.a.28018'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Apply advanced machine learning methods, including natural language processing and convolutional neural networks, for predictive modeling and simulation.', 'A6.J.1.d.29179'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Research and develop novel computer vision and machine learning algorithms for 3D scene reconstruction, object detection, motion tracking, and real-time scene understanding.', 'A6.A.10.c.26726'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Design and develop algorithms for generative models using deep learning techniques and natural language processing (NLP).', 'A6.J.10.a.29664'), ('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Develop and implement advanced machine learning and generative AI techniques in enterprise applications.', 'A6.J.0.b.29439'), ('Develop and apply expertise in autonomous system development, including mechanical and electrical design, autonomous control, software engineering, navigation algorithms, and machine learning.', 'A6.J.5.i.21856')]</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1095,25 +1095,25 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
       </c>
       <c r="T4" t="n">
-        <v>0.718</v>
+        <v>0.671</v>
       </c>
       <c r="U4" t="n">
-        <v>0.711</v>
+        <v>0.702</v>
       </c>
       <c r="V4" t="n">
-        <v>0.711</v>
+        <v>0.673</v>
       </c>
       <c r="W4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Use Python programming for data analysis, automation, and manipulation tasks.', 'A6.B.8.a.26861'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589')]</t>
+          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Strong understanding of machine learning concepts, including algorithms, natural language processing, deep learning, and their applications in various contexts such as code generation and information retrieval.', 'A6.A.16.a.29375'), ('Use Python programming for data analysis, automation, and manipulation tasks.', 'A6.B.8.a.26861'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589')]</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1236,25 +1236,25 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
         <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>0.727</v>
+        <v>0.723</v>
       </c>
       <c r="U5" t="n">
         <v>0.726</v>
       </c>
       <c r="V5" t="n">
-        <v>0.725</v>
+        <v>0.719</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('20327', 'Improve search-related activities through ongoing analysis, experimentation, or optimization tests, using A/B or multivariate methods.'), ('12221', 'Program computers to operate machinery.'), ('6463', 'Arrange for lectures by experts in designated fields.'), ('20083', 'Review books and journal articles for potential publication.'), ('17062', 'Engage in self-directed learning and continuing education activities.'), ('6582', 'Assign lessons and correct homework.'), ('8967', 'Examine theories, such as those of probability and inference, to discover mathematical bases for new or improved methods of obtaining and evaluating numerical data.'), ('21487', 'Develop conceptual designs of security systems.'), ('16180', 'Assist in the development of online transaction or security policies.'), ('21109', 'Develop and maintain Web sites for online courses.')]</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[('Develop and implement algorithms and data structures to solve problems using web technologies and object-oriented programming.', 'A6.G.0.e.18538'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Understand, implement, and codify algorithms while evaluating their performance and suitability for problem-solving in various applications.', 'A6.G.0.e.26376'), ('Strong problem identification and problem-solving skills.', 'A6.B.0.y.15226'), ('Ability to utilize and conduct problem-solving techniques effectively.', 'A6.B.0.f.14814'), ('Ability to effectively identify, analyze, and resolve challenges through critical and strategic thinking skills.', 'A6.B.0.l.11403')]</t>
+          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develop and implement algorithms and data structures to solve problems using web technologies and object-oriented programming.', 'A6.G.0.e.18538'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Understand, implement, and codify algorithms while evaluating their performance and suitability for problem-solving in various applications.', 'A6.G.0.e.26376'), ('Strong problem identification and problem-solving skills.', 'A6.B.0.y.15226'), ('Ability to utilize and conduct problem-solving techniques effectively.', 'A6.B.0.f.14814'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Support the development and management of knowledge graphs and semantic models using relevant technologies.', 'A6.E.0.j.24528'), ('Experience with graph databases, semantic layers, and data ontologies.', 'A6.E.3.f.21813'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Possess expert knowledge of machine learning algorithms and techniques.', 'A6.A.16.b.29834'), ('Possesses expert knowledge of human-computer interaction principles.', 'A6.A.3.c.25588'), ('Make informed recommendations and provide training based on technical expertise and data analysis.', 'A6.E.1.g.18146'), ('Develop and apply expertise in autonomous system development, including mechanical and electrical design, autonomous control, software engineering, navigation algorithms, and machine learning.', 'A6.J.5.i.21856'), ('Configure, train, and optimize AI models, including chatbots and autonomous agents, with a focus on prompt engineering and operationalization.', 'A6.J.11.b.28862'), ('Strong foundational knowledge of engineering principles, practices, and methodologies, complemented by logical thinking.', 'A6.A.21.c.20356'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('Knowledge of computer science principles and computer-based accounting systems, including basic accounting principles.', 'A6.A.3.b.15929'), ('Ability to understand and work with mathematical and statistical concepts, including probability and statistical inference.', 'A6.B.5.d.16182'), ('Ability to apply strong knowledge of algorithms and data structures to solve complex business and technical problems.', 'A6.B.0.d.20576'), ('Ability to stay informed about and evaluate emerging trends in AI and machine learning to integrate innovative solutions and strategies within various organizational contexts.', 'A6.J.2.s.26250'), ('Ability to effectively identify, analyze, and resolve challenges through critical and strategic thinking skills.', 'A6.B.0.l.11403'), ('Ability to navigate and solve problems in ambiguous and complex situations.', 'A6.B.0.l.18508'), ('Design, develop, and implement knowledge-based systems, including ontologies, taxonomies, and knowledge graphs to support data integration and semantic search.', 'A6.G.0.j.27688')]</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1493,25 +1493,25 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.499</v>
+        <v>0.551</v>
       </c>
       <c r="U6" t="n">
-        <v>0.849</v>
+        <v>0.722</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.598</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('16208', 'Devise missions, challenges, or puzzles to be encountered in game play.'), ('20327', 'Improve search-related activities through ongoing analysis, experimentation, or optimization tests, using A/B or multivariate methods.'), ('14730', 'Develop system interaction or sequence diagrams.')]</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687')]</t>
+          <t>[('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Strong knowledge and understanding of data structures, algorithms, and object-oriented programming.', 'A6.A.9.c.22782'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Design, develop, and implement knowledge-based systems, including ontologies, taxonomies, and knowledge graphs to support data integration and semantic search.', 'A6.G.0.j.27688')]</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1629,25 +1629,25 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>0.766</v>
+        <v>0.702</v>
       </c>
       <c r="U7" t="n">
         <v>0.78</v>
       </c>
       <c r="V7" t="n">
-        <v>0.766</v>
+        <v>0.71</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>[('11059', 'Teach writing classes.')]</t>
+          <t>[('14633', 'Design computers and the software that runs them.'), ('11059', 'Teach writing classes.'), ('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop expertise and conduct research in areas such as algorithmic game theory, artificial general intelligence, automated theorem proving, program synthesis, and machine learning.', 'A6.J.0.b.24974'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Apply machine learning techniques for natural language processing in biological data and clinical settings.', 'A6.J.14.f.28109'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Design and implement advanced machine learning algorithms and models for classification, regression, clustering, recommendation, and natural language processing tasks.', 'A6.J.11.b.28592')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop expertise and conduct research in areas such as algorithmic game theory, artificial general intelligence, automated theorem proving, program synthesis, and machine learning.', 'A6.J.0.b.24974'), ('Apply computer science methods and techniques to store, manipulate, transform, or present information using computer systems.', 'A6.A.3.b.25374'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Design and create logical and physical databases using relational database principles.', 'A6.E.3.f.18280'), ('Apply machine learning techniques for natural language processing in biological data and clinical settings.', 'A6.J.14.f.28109'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Use SQL and data mining tools to analyze game and player data for understanding behavior and trends.', 'A6.C.4.n.22046'), ('Design, develop, and implement knowledge-based systems, including ontologies, taxonomies, and knowledge graphs to support data integration and semantic search.', 'A6.G.0.j.27688'), ('Design and implement advanced machine learning algorithms and models for classification, regression, clustering, recommendation, and natural language processing tasks.', 'A6.J.11.b.28592')]</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1802,25 +1802,25 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>0.714</v>
+        <v>0.666</v>
       </c>
       <c r="U8" t="n">
-        <v>0.677</v>
+        <v>0.716</v>
       </c>
       <c r="V8" t="n">
-        <v>0.714</v>
+        <v>0.699</v>
       </c>
       <c r="W8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('6541', 'Establish clear objectives for all lessons, units, and projects and communicate those objectives to students.'), ('20930', 'Input specifications into computers to assist with pattern design and pattern cutting.')]</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Strong problem identification and problem-solving skills.', 'A6.B.0.y.15226'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Solid understanding of machine learning concepts, algorithms, techniques, and their practical applications.', 'A6.J.3.c.29814'), ('Possesses expert knowledge of human-computer interaction principles.', 'A6.A.3.c.25588'), ('Design machine learning systems and algorithms to generate accurate predictions.', 'A6.J.2.h.29884'), ('Use data mining techniques to extract valuable information for business decision-making and insights.', 'A6.D.0.e.27580')]</t>
+          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Strong problem identification and problem-solving skills.', 'A6.B.0.y.15226'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Perform predictive analysis using advanced statistical methods and probability-based modeling techniques.', 'A6.B.5.c.29752'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Solid understanding of machine learning concepts, algorithms, techniques, and their practical applications.', 'A6.J.3.c.29814'), ('Possesses expert knowledge of human-computer interaction principles.', 'A6.A.3.c.25588'), ('Design machine learning systems and algorithms to generate accurate predictions.', 'A6.J.2.h.29884'), ('Use data mining techniques to extract valuable information for business decision-making and insights.', 'A6.D.0.e.27580')]</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -2074,25 +2074,25 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
         <v>16</v>
       </c>
       <c r="T9" t="n">
-        <v>0.695</v>
+        <v>0.7</v>
       </c>
       <c r="U9" t="n">
         <v>0.85</v>
       </c>
       <c r="V9" t="n">
-        <v>0.731</v>
+        <v>0.733</v>
       </c>
       <c r="W9" t="n">
         <v>3</v>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>[('9796', 'Select statistical tests for analyzing data.')]</t>
+          <t>[('21831', 'Identify business problems or management objectives that can be addressed through data analysis.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.'), ('7277', 'Analyze data gathered and develop solutions or alternative methods of proceeding.'), ('21128', 'Schedule courses.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('9796', 'Select statistical tests for analyzing data.'), ('2435', 'Discuss use and features of various parts, based on knowledge of machines or equipment.'), ('21058', 'Evaluate robotic systems or prototypes.'), ('3288', 'Prepare personnel forecasts to project employment needs.'), ('23672', 'Separate models or patterns from molds and examine products for accuracy.'), ('8283', 'Cover surfaces with laminated plastic covering material.'), ('7929', 'Design or implement control measures to prevent or counteract damage caused by wildlife or people.'), ('1146', 'Monitor and follow applicable laws and regulations.'), ('20847', 'Perform managerial duties such as hiring and training employees and overseeing facility needs or requirements.'), ('7383', 'Study and analyze information about alternative courses of action to determine which plan will offer the best outcomes.'), ('21818', 'Evaluate new blockchain technologies and vendor products.'), ('805', 'Transmit work electronically to other locations.')]</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Research and apply modern AI capabilities in machine learning, algorithms, and ethical considerations while assisting with robotic solutions.', 'A6.A.10.a.28513'), ('Identifies and promotes opportunities for implementing machine learning and artificial intelligence to enhance business operations.', 'A6.J.2.m.26499'), ('Work with stakeholders throughout the organization to identify opportunities for leveraging data and artificial intelligence to drive business solutions.', 'A6.D.0.a.21945'), ('Demonstrate experience with Machine Learning and Deep Learning concepts, algorithms, and models.', 'A6.A.16.a.29352'), ('Build and develop chips for artificial intelligence computing.', 'A6.A.8.h.24670'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Experience in using statistical analysis to determine data modeling approaches and training machine learning tests and experiments.', 'A6.C.4.p.24994'), ('Knowledge of machine learning workflows, frameworks, and applications in scientific contexts.', 'A6.A.16.a.28903'), ('Apply machine learning techniques such as clustering, logistic regression, CART, random forests, SVM, and neural networks to solve regression and classification problems.', 'A6.J.14.e.29739'), ('Work with machine learning libraries and frameworks such as PyTorch, TensorFlow, and ONNX.', 'A6.J.11.a.28822'), ('Design and implement evaluation frameworks and metrics for agentic AI systems.', 'A6.J.4.d.29858'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Understand and apply deep learning techniques and methods, including explainability and interpretability, transfer learning, and NLP.', 'A6.A.16.c.28603'), ('Expertise in responsible AI practices, including ethical considerations, safety evaluations, compliance with data protection regulations, bias mitigation, and AI governance frameworks.', 'A6.G.2.g.28971'), ('Expertise in Responsible AI practices, governance, and technical solutions, ensuring transparency and safety in AI innovations.', 'A6.G.2.g.28708'), ('Evaluate and integrate emerging AI technologies and tools to enhance platform capabilities and solve complex problems.', 'A6.J.0.m.27726')]</t>
+          <t>[('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Research and apply modern AI capabilities in machine learning, algorithms, and ethical considerations while assisting with robotic solutions.', 'A6.A.10.a.28513'), ('Ability to establish and govern data and algorithms for analysis and automated decision-making, ensuring quality, trust, and ethical standards in AI technology.', 'A6.J.0.n.27567'), ('Identifies and promotes opportunities for implementing machine learning and artificial intelligence to enhance business operations.', 'A6.J.2.m.26499'), ('Work with stakeholders throughout the organization to identify opportunities for leveraging data and artificial intelligence to drive business solutions.', 'A6.D.0.a.21945'), ('Demonstrate experience with Machine Learning and Deep Learning concepts, algorithms, and models.', 'A6.A.16.a.29352'), ('Demonstrates a strong drive to learn, master, and apply new programming, data analysis techniques, and technologies to solve problems.', 'A6.J.0.k.22471'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Build and develop chips for artificial intelligence computing.', 'A6.A.8.h.24670'), ('Stay updated with the latest advancements in AI and machine learning technologies, applying innovative techniques to improve systems and solve business problems.', 'A6.J.2.s.27362'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Manage and develop pattern recognition and predictive modeling techniques.', 'A6.J.11.f.29584'), ('Experience in using statistical analysis to determine data modeling approaches and training machine learning tests and experiments.', 'A6.C.4.p.24994'), ('Knowledge of machine learning workflows, frameworks, and applications in scientific contexts.', 'A6.A.16.a.28903'), ('Apply machine learning techniques such as clustering, logistic regression, CART, random forests, SVM, and neural networks to solve regression and classification problems.', 'A6.J.14.e.29739'), ('Work with machine learning libraries and frameworks such as PyTorch, TensorFlow, and ONNX.', 'A6.J.11.a.28822'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Design and implement evaluation frameworks and metrics for agentic AI systems.', 'A6.J.4.d.29858'), ('Optimize AI algorithms and applications for performance, scalability, reliability, and cost-effectiveness.', 'A6.E.5.e.28686'), ('Proficient in utilizing machine learning algorithms and modeling techniques to automate tasks and develop scalable, repeatable solutions.', 'A6.J.11.c.29729'), ('Develop, maintain, and enhance predictive modeling tools and methods for operational outcomes, including data quality improvement and anomaly detection.', 'A6.J.4.f.25140'), ('Manage large datasets, develop and test machine learning models, and integrate these models into applications using APIs and platforms like Azure and ChatGPT4.', 'A6.J.6.b.28439'), ('Create predictive models and forecasts to support decision-making and inform HR strategies.', 'A6.J.6.g.25036'), ('Optimize model performance through hyperparameter tuning, feature engineering, and algorithm selection.', 'A6.E.5.e.29725'), ('Own and manage feature delivery and tradeoffs of a product, including integration with feature stores and ML data pipelines.', 'A6.J.11.j.23250'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Promotes responsible AI practices, emphasizing transparency, fairness, accountability, and interpretability in machine learning initiatives.', 'A6.G.2.k.27674'), ('Interact with data scientists, industry experts, and stakeholders to understand data conversion, loading, and presentation needs, as well as to identify potential new features and algorithms.', 'A6.H.2.c.23912'), ('Understanding data is essential for effective data science.', 'A6.D.0.w.29780'), ('Strong grasp of AI ethics, data privacy, and responsible practices, including principles for minimizing bias and ensuring compliance with regulatory frameworks.', 'A6.G.2.k.29791'), ('Ability to evaluate and adapt emerging AI technologies and tools to align with data privacy regulations and support legal practices.', 'A6.J.2.s.27797'), ('Train, evaluate, and monitor machine learning and deep learning models for various tasks.', 'A6.J.10.c.29881'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Familiarity with machine learning is an advantageous skill.', 'A6.J.11.h.29131'), ('Develop predictive models and evaluate their performance using statistical and algorithmic solutions.', 'A6.J.3.a.29835'), ('Understand and apply deep learning techniques and methods, including explainability and interpretability, transfer learning, and NLP.', 'A6.A.16.c.28603'), ('Expertise in responsible AI practices, including ethical considerations, safety evaluations, compliance with data protection regulations, bias mitigation, and AI governance frameworks.', 'A6.G.2.g.28971'), ('Strong understanding of emerging technologies, particularly in robotics, and their potential impact on research, development, and industry trends.', 'A6.J.2.s.26425'), ('Expertise in Responsible AI practices, governance, and technical solutions, ensuring transparency and safety in AI innovations.', 'A6.G.2.g.28708'), ('Collaborate with data scientists and engineers to develop, evaluate, and integrate AI/ML models into production systems and workflows.', 'A6.J.0.n.25812'), ('Ability to stay informed about and evaluate emerging trends in AI and machine learning to integrate innovative solutions and strategies within various organizational contexts.', 'A6.J.2.s.26250'), ('Ability to drive the adoption and implementation of AI, machine learning, and automation tools to enhance workflows, operational processes, and data management across the organization.', 'A6.J.4.i.26045'), ('Configure, train, and optimize AI models, including chatbots and autonomous agents, with a focus on prompt engineering and operationalization.', 'A6.J.11.b.28862'), ('Ability to support and facilitate data collection in AIC environments.', 'A6.H.5.e.25785'), ('Develop predictive models to forecast future trends, outcomes, and labor demands.', 'A6.C.4.r.29134'), ('Ability to work on innovative and impactful AI-driven machine learning projects that shape the future of technology.', 'A6.J.4.i.26325'), ('Work on innovative projects in robotics, automation, augmented reality, audio technology, RFID, IoT, data gathering solutions, and purpose-driven engineering contributing to national security.', 'A6.F.7.c.16656'), ('Evaluate and integrate emerging AI technologies and tools to enhance platform capabilities and solve complex problems.', 'A6.J.0.m.27726')]</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -2457,25 +2457,25 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="S10" t="n">
         <v>13</v>
       </c>
       <c r="T10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="U10" t="n">
         <v>0.663</v>
       </c>
-      <c r="U10" t="n">
-        <v>0.6879999999999999</v>
-      </c>
       <c r="V10" t="n">
-        <v>0.663</v>
+        <v>0.658</v>
       </c>
       <c r="W10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('7276', 'Gather and organize information on problems or procedures.'), ('16208', 'Devise missions, challenges, or puzzles to be encountered in game play.'), ('22082', 'Interpret engineering sketches, specifications, or drawings.'), ('17559', 'Study communication code languages or foreign languages to translate intelligence.'), ('21751', 'Develop presentations on threat intelligence.'), ('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Knowledge and application of natural language processing, machine learning, information retrieval, and analytics in intelligence and recommender system use cases.', 'A6.A.16.c.26812'), ('Expertise in natural language processing (NLP), including machine translation, conversational AI, and computational linguistics techniques.', 'A6.A.16.c.28715'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892')]</t>
+          <t>[('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Ability to utilize and conduct problem-solving techniques effectively.', 'A6.B.0.f.14814'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Prototype and evaluate optimization algorithms, such as linear programming, dynamic programming, and heuristic algorithms, for large-scale, non-linear, constrained optimization problems.', 'A6.J.9.k.19568'), ('Knowledge and application of natural language processing, machine learning, information retrieval, and analytics in intelligence and recommender system use cases.', 'A6.A.16.c.26812'), ('Expertise in natural language processing (NLP), including machine translation, conversational AI, and computational linguistics techniques.', 'A6.A.16.c.28715'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Proficient in applying AI and machine learning principles to solve complex problems, with strong problem-solving and communication skills, along with knowledge of algorithms and the Scientific and Medical Affairs domain.', 'A6.J.7.e.24225'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892')]</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -2618,25 +2618,25 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
         <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>0.726</v>
+        <v>0.631</v>
       </c>
       <c r="U11" t="n">
         <v>0.726</v>
       </c>
       <c r="V11" t="n">
-        <v>0.705</v>
+        <v>0.64</v>
       </c>
       <c r="W11" t="n">
         <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>[('5687', 'Prepare and deliver lectures to undergraduate or graduate students on topics such as programming, data structures, and software design.'), ('14730', 'Develop system interaction or sequence diagrams.')]</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrate an understanding of computer science fundamentals, including data structures, algorithms, and AI/machine learning concepts.', 'A6.A.9.e.26712'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Strong problem identification and problem-solving skills.', 'A6.B.0.y.15226')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Possesses expert knowledge of human-computer interaction principles.', 'A6.A.3.c.25588'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Knowledge of machine learning and data science concepts and principles.', 'A6.A.16.a.29474'), ('Demonstrate an understanding of computer science fundamentals, including data structures, algorithms, and AI/machine learning concepts.', 'A6.A.9.e.26712'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Strong problem identification and problem-solving skills.', 'A6.B.0.y.15226'), ('Implement and apply Bayesian modeling techniques in multimodal data analysis, including feature selection and hierarchical Bayesian techniques.', 'A6.C.4.k.28775')]</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2786,25 +2786,25 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S12" t="n">
         <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>0.612</v>
+        <v>0.656</v>
       </c>
       <c r="U12" t="n">
-        <v>0.744</v>
+        <v>0.796</v>
       </c>
       <c r="V12" t="n">
-        <v>0.703</v>
+        <v>0.707</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('20238', 'Apply relevant laws, regulations, policies, or precedents to reach conclusions.'), ('21708', 'Register Web sites with search engines to increase Web site traffic.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('20327', 'Improve search-related activities through ongoing analysis, experimentation, or optimization tests, using A/B or multivariate methods.'), ('16208', 'Devise missions, challenges, or puzzles to be encountered in game play.')]</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Implement and apply Bayesian modeling techniques in multimodal data analysis, including feature selection and hierarchical Bayesian techniques.', 'A6.C.4.k.28775'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Design and implement evaluation frameworks and metrics for agentic AI systems.', 'A6.J.4.d.29858'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Demonstrates excellent reasoning, analytical, troubleshooting, and problem-solving skills.', 'A6.B.0.c.15752'), ('Proficient in uncertainty quantification, including methods applied to statistical analysis, multi-modal deep learning, risk analysis, and computational models.', 'A6.A.12.c.21622'), ('Implement and apply Bayesian modeling techniques in multimodal data analysis, including feature selection and hierarchical Bayesian techniques.', 'A6.C.4.k.28775'), ('Proficient in training and inference of large-scale AI models, including large language models (LLMs), multimodal models, and reasoning models.', 'A6.J.10.b.28488'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Design and implement evaluation frameworks and metrics for agentic AI systems.', 'A6.J.4.d.29858'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Design and implement advanced machine learning algorithms and models for classification, regression, clustering, recommendation, and natural language processing tasks.', 'A6.J.11.b.28592'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Ability to utilize and conduct problem-solving techniques effectively.', 'A6.B.0.f.14814'), ('Support the development, testing, and deployment of AI algorithms and models.', 'A6.J.5.c.29846')]</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>0.709</v>
+        <v>0.648</v>
       </c>
       <c r="U13" t="n">
-        <v>0.821</v>
+        <v>0.703</v>
       </c>
       <c r="V13" t="n">
-        <v>0.717</v>
+        <v>0.699</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>[('7549', 'Conduct research to gather information about survey topics.'), ('17183', 'Conduct research and present scientific findings.'), ('333', 'Write research reports and other publications to document and communicate research findings.')]</t>
+          <t>[('16208', 'Devise missions, challenges, or puzzles to be encountered in game play.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('14293', 'Collaborate with other operators to solve unit problems.'), ('16518', 'Plan mobile robot paths and teach path plans to robots.'), ('7549', 'Conduct research to gather information about survey topics.'), ('2667', 'Assist in the preparation of book displays.'), ('16827', 'Attend clinical and research conferences and read scientific literature to keep abreast of technological advances and current genetic research findings.'), ('18831', 'Conduct market research and analyze industry trends.'), ('3719', 'Trace historical development in a particular field, such as social, cultural, political, or diplomatic history.'), ('1649', 'Plan and conduct special research projects in area of interest or expertise.'), ('17438', 'Participate in research projects, conferences, or technical meetings.'), ('7386', 'Specify manipulative or computational methods to be applied to models.'), ('1281', 'Train subordinates in programming and program coding.'), ('17183', 'Conduct research and present scientific findings.'), ('10955', 'Lead discussion sections, tutorials, or laboratory sections.'), ('333', 'Write research reports and other publications to document and communicate research findings.'), ('20064', 'Review papers for publication in journals.'), ('7277', 'Analyze data gathered and develop solutions or alternative methods of proceeding.')]</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Develop expertise and conduct research in areas such as algorithmic game theory, artificial general intelligence, automated theorem proving, program synthesis, and machine learning.', 'A6.J.0.b.24974'), ('Conduct research to identify emerging trends and technologies in AI, machine learning, and data science.', 'A6.J.0.d.29174'), ('Develop and maintain documentation for AI systems and applications, including models, governance, and lifecycle management.', 'A6.J.2.h.23443'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Excellent interpersonal and verbal and written communication skills for effective research dissemination.', 'A6.H.4.k.10648'), ('Demonstrated experience in software development, including automation, scripting, object-oriented techniques, and integration methodologies.', 'A6.G.5.l.16685'), ('Experience in effectively communicating complex scientific research findings and concepts to diverse audiences through various formats, including verbal presentations and written reports.', 'A6.H.2.e.11016'), ('Contribute to open-source AI or machine learning projects and research publications.', 'A6.I.0.a.29237')]</t>
+          <t>[('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('The field has expanded to encompass video games, movie production, product design, medical diagnosis, and scientific research.', 'A6.A.18.f.11267'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Knowledge of machine learning and AI applications across various domains including automation, search and personalization, workforce planning, database management, network management, ADAS, and mechatronics.', 'A6.A.16.a.29158'), ('Develop expertise and conduct research in areas such as algorithmic game theory, artificial general intelligence, automated theorem proving, program synthesis, and machine learning.', 'A6.J.0.b.24974'), ('Stay current with relevant scientific literature and apply new methodologies and techniques to ongoing projects.', 'A6.J.2.s.15523'), ('Conduct research to identify emerging trends and technologies in AI, machine learning, and data science.', 'A6.J.0.d.29174'), ('Develop and maintain documentation for AI systems and applications, including models, governance, and lifecycle management.', 'A6.J.2.h.23443'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Excellent interpersonal and verbal and written communication skills for effective research dissemination.', 'A6.H.4.k.10648'), ('Demonstrated experience in software development, including automation, scripting, object-oriented techniques, and integration methodologies.', 'A6.G.5.l.16685'), ('Experience in effectively communicating complex scientific research findings and concepts to diverse audiences through various formats, including verbal presentations and written reports.', 'A6.H.2.e.11016'), ('Make publications or significant contributions to the machine learning research community.', 'A6.A.16.b.27558'), ('Apply and supervise data analysis techniques and tools to solve problems and identify trends.', 'A6.J.1.b.26767'), ('Contribute to open-source AI or machine learning projects and research publications.', 'A6.I.0.a.29237')]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -3110,25 +3110,25 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>0.524</v>
+        <v>0.554</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.713</v>
       </c>
       <c r="V14" t="n">
-        <v>0.667</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('752', 'Analyze data to determine answers to questions from customers or members of the public.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('1522', 'Determine data collection methods to be employed in research projects or surveys.'), ('752', 'Analyze data to determine answers to questions from customers or members of the public.'), ('21798', 'Perform web service network traffic analysis or waveform analysis to detect anomalies, such as unusual events or trends.'), ('16257', 'Develop or implement data analysis algorithms.')]</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Expertise in big data analysis, large-scale data analytics, and machine learning algorithms.', 'A6.B.0.p.29701'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Build and apply regression, decision tree, and clustering models for data analysis.', 'A6.J.14.a.28626'), ('Model and implement optimization algorithms for solving linear and non-linear optimization problems using mathematical optimization techniques.', 'A6.J.11.c.17766'), ('Design, collect, and analyze data for user study protocols and research projects.', 'A6.B.2.f.24755'), ('Develop and implement Python programming and scripting solutions for automation, data science, and backend development.', 'A6.K.0.b.17771'), ('Utilize Python and its libraries, such as Pandas, NumPy, and SciPy, for data manipulation, analysis, and modeling tasks.', 'A6.B.8.u.23683'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Transform data and utilize anomaly detection methods for machine learning applications.', 'A6.J.14.d.29662'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Apply machine learning techniques including classification, clustering, regressions, and deep learning models.', 'A6.G.0.n.29857'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Implement and apply various supervised and unsupervised machine learning techniques, including decision trees, neural networks, clustering algorithms, and regression models.', 'A6.J.11.j.29598'), ('Familiarize with various machine learning models and techniques, including supervised and unsupervised algorithms for classification, regression, and clustering.', 'A6.A.16.b.29493'), ('Experiment with various algorithms and techniques to optimize model performance and improve prediction accuracy.', 'A6.J.10.d.28400')]</t>
+          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Expertise in big data analysis, large-scale data analytics, and machine learning algorithms.', 'A6.B.0.p.29701'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop and optimize algorithms tailored to business needs, tested on large data sets.', 'A6.F.1.e.26950'), ('Build and apply regression, decision tree, and clustering models for data analysis.', 'A6.J.14.a.28626'), ('Model and implement optimization algorithms for solving linear and non-linear optimization problems using mathematical optimization techniques.', 'A6.J.11.c.17766'), ('Develop data collection methods, databases, and queries for various database systems.', 'A6.E.4.g.27516'), ('Design, collect, and analyze data for user study protocols and research projects.', 'A6.B.2.f.24755'), ('Develop and implement Python programming and scripting solutions for automation, data science, and backend development.', 'A6.K.0.b.17771'), ('Utilize Python and its libraries, such as Pandas, NumPy, and SciPy, for data manipulation, analysis, and modeling tasks.', 'A6.B.8.u.23683'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Implement algorithms for data analysis and processing.', 'A6.J.8.f.29898'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Transform data and utilize anomaly detection methods for machine learning applications.', 'A6.J.14.d.29662'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Apply machine learning techniques including classification, clustering, regressions, and deep learning models.', 'A6.G.0.n.29857'), ('Develop algorithms and models using scripting languages such as MATLAB and Python.', 'A6.J.5.a.26317'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Implement and apply various supervised and unsupervised machine learning techniques, including decision trees, neural networks, clustering algorithms, and regression models.', 'A6.J.11.j.29598'), ('Familiarize with various machine learning models and techniques, including supervised and unsupervised algorithms for classification, regression, and clustering.', 'A6.A.16.b.29493'), ('Experiment with various algorithms and techniques to optimize model performance and improve prediction accuracy.', 'A6.J.10.d.28400')]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -3281,25 +3281,25 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="S15" t="n">
         <v>17</v>
       </c>
       <c r="T15" t="n">
-        <v>0.659</v>
+        <v>0.657</v>
       </c>
       <c r="U15" t="n">
         <v>0.616</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.668</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>[('16515', 'Write algorithms or programming code for ad hoc robotic applications.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16515', 'Write algorithms or programming code for ad hoc robotic applications.')]</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Strong interest in artificial intelligence and machine learning, including concepts, algorithms, applications in various fields, and continuous learning in emerging technologies.', 'A6.A.16.a.28899'), ('Design and develop algorithms for generative models using deep learning techniques and natural language processing (NLP).', 'A6.J.10.a.29664'), ('Expertise in responsible AI practices, including ethical considerations, safety evaluations, compliance with data protection regulations, bias mitigation, and AI governance frameworks.', 'A6.G.2.g.28971'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Ability to evaluate and refine algorithms using relevant data.', 'A6.J.10.d.29188'), ('Hold a PhD in computer science, robotics, AI, or a related field with a focus on natural language processing, machine learning, or computer vision.', 'A6.A.16.c.23953'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Design and deploy machine learning models using Scikit-Learn, TensorFlow, and PyTorch.', 'A6.J.11.a.29173')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Strong interest in artificial intelligence and machine learning, including concepts, algorithms, applications in various fields, and continuous learning in emerging technologies.', 'A6.A.16.a.28899'), ('Experience in deep learning algorithms for search and recommendation systems.', 'A6.A.16.c.27070'), ('Design and develop algorithms for generative models using deep learning techniques and natural language processing (NLP).', 'A6.J.10.a.29664'), ('Expertise in responsible AI practices, including ethical considerations, safety evaluations, compliance with data protection regulations, bias mitigation, and AI governance frameworks.', 'A6.G.2.g.28971'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Ability to evaluate and refine algorithms using relevant data.', 'A6.J.10.d.29188'), ('Hold a PhD in computer science, robotics, AI, or a related field with a focus on natural language processing, machine learning, or computer vision.', 'A6.A.16.c.23953'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Design and deploy machine learning models using Scikit-Learn, TensorFlow, and PyTorch.', 'A6.J.11.a.29173')]</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -3438,25 +3438,25 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S16" t="n">
         <v>14</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.744</v>
+        <v>0.738</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('6836', 'Observe students to determine qualifications, limitations, abilities, interests, and other individual characteristics.'), ('16375', 'Provide human factors technical expertise on topics, such as advanced user-interface technology development or the role of human users in automated or autonomous sub-systems in advanced vehicle systems.'), ('16208', 'Devise missions, challenges, or puzzles to be encountered in game play.'), ('7276', 'Gather and organize information on problems or procedures.'), ('19971', 'Examine societal issues and their relationship with both technical systems and the environment.')]</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Ability to identify, evaluate, and refine methods, models, and algorithms for developing accurate and anticipatory intelligence analysis solutions.', 'A6.J.11.e.22676'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596')]</t>
+          <t>[('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrate familiarity with agentic AI frameworks, concepts, and orchestration tools for building AI agent-based applications.', 'A6.A.15.l.29608'), ('Ability to identify, evaluate, and refine methods, models, and algorithms for developing accurate and anticipatory intelligence analysis solutions.', 'A6.J.11.e.22676'), ('Ability to assist in programming, scripting, data ETL, data analysis, and web development while monitoring and ensuring system parameters within specifications using intelligent systems.', 'A6.F.2.d.19597'), ('Provide software structure and validation direction for AI software solutions that integrate AI algorithms to solve applied problems.', 'A6.J.4.d.26074'), ('Ability to define machine learning and data mining strategies and determine when to utilize machine learning services versus simpler heuristics.', 'A6.J.12.e.23723'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185')]</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -3564,25 +3564,25 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>0.701</v>
+        <v>0.644</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.655</v>
       </c>
       <c r="V17" t="n">
-        <v>0.701</v>
+        <v>0.668</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -3669,17 +3669,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>[('17559', 'Study communication code languages or foreign languages to translate intelligence.'), ('16115', 'Develop and document database architectures.'), ('16036', 'Train others in fraud detection and prevention techniques.'), ('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>[('Create and maintain neural networks using proven technologies or develop new methods tailored to specific research needs.', 'A6.J.11.e.27928'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Familiarity with reinforcement learning techniques, applications, and advanced optimization methods in various contexts.', 'A6.A.16.b.28784'), ('Optimize model performance through hyperparameter tuning, feature engineering, and algorithm selection.', 'A6.E.5.e.29725'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687')]</t>
+          <t>[('Ability to apply sophisticated machine learning methods to complex tasks, including natural language processing, speech analytics, time series analysis, reinforcement learning, and recommendation systems.', 'A6.A.16.c.27819'), ('Create and maintain neural networks using proven technologies or develop new methods tailored to specific research needs.', 'A6.J.11.e.27928'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Familiarity with reinforcement learning techniques, applications, and advanced optimization methods in various contexts.', 'A6.A.16.b.28784'), ('Develop and deploy machine learning models for fraud detection and risk assessment.', 'A6.J.11.e.26375'), ('Optimize model performance through hyperparameter tuning, feature engineering, and algorithm selection.', 'A6.E.5.e.29725'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687')]</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -3688,25 +3688,25 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S18" t="n">
         <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>0.707</v>
+        <v>0.68</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="V18" t="n">
-        <v>0.707</v>
+        <v>0.68</v>
       </c>
       <c r="W18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('17709', 'Analyze or manipulate bioinformatics data using software packages, statistical applications, or data mining techniques.')]</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develops highly scalable classifiers and tools utilizing machine learning, data regression, and rules-based models for various applications.', 'A6.C.4.p.28339'), ('Build and train statistical and machine learning models and algorithms using programming languages such as Python, R, and Scala.', 'A6.J.11.a.28281'), ('Develop and apply statistical models and algorithms to identify patterns, trends, and anomalies in data.', 'A6.C.4.r.24570'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Program machine learning models using R or Python.', 'A6.J.3.b.29706'), ('Design, implement, and validate machine learning models and techniques for real-world applications.', 'A6.J.11.b.29549'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Proven experience in developing and applying supervised, unsupervised, and semi-supervised machine learning techniques and algorithms, including regression, classification, and clustering, for data curation and real-world problem solving.', 'A6.J.11.j.28285'), ('Familiarity with knowledge graphs, graph databases, and related algorithms for organizing and analyzing complex data.', 'A6.B.5.c.20195'), ('Strong data mining, aggregation, and analytical skills.', 'A6.A.14.r.27209')]</t>
+          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develops highly scalable classifiers and tools utilizing machine learning, data regression, and rules-based models for various applications.', 'A6.C.4.p.28339'), ('Build and train statistical and machine learning models and algorithms using programming languages such as Python, R, and Scala.', 'A6.J.11.a.28281'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Develop and apply statistical models and algorithms to identify patterns, trends, and anomalies in data.', 'A6.C.4.r.24570'), ('Applies advanced data algorithms and modeling techniques to derive insights that drive improvement initiatives.', 'A6.C.4.r.24282'), ('Develop statistical and machine learning models using techniques such as neural networks, graphical models, ensemble methods, and natural language processing to address business questions and make predictions.', 'A6.J.12.d.27228'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Program machine learning models using R or Python.', 'A6.J.3.b.29706'), ('Design, implement, and validate machine learning models and techniques for real-world applications.', 'A6.J.11.b.29549'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Proven experience in developing and applying supervised, unsupervised, and semi-supervised machine learning techniques and algorithms, including regression, classification, and clustering, for data curation and real-world problem solving.', 'A6.J.11.j.28285'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Familiarity with knowledge graphs, graph databases, and related algorithms for organizing and analyzing complex data.', 'A6.B.5.c.20195'), ('Strong data mining, aggregation, and analytical skills.', 'A6.A.14.r.27209'), ('Collect, preprocess, and analyze large datasets to train and evaluate machine learning models.', 'A6.J.11.g.28410')]</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="S19" t="n">
         <v>7</v>
@@ -3828,16 +3828,16 @@
         <v>0.658</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="V19" t="n">
-        <v>0.675</v>
+        <v>0.654</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('23695', 'Plan and establish schedules.'), ('7367', 'Apply mathematical theories and techniques to the solution of practical problems in business, engineering, the sciences, or other fields.'), ('21834', 'Propose solutions in engineering, the sciences, and other fields using mathematical theories and techniques.'), ('16257', 'Develop or implement data analysis algorithms.')]</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Ability to utilize and conduct problem-solving techniques effectively.', 'A6.B.0.f.14814'), ('Construct and search Knowledge Graphs using vector similarity search and vector databases.', 'A6.E.4.g.24174'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899')]</t>
+          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Ability to utilize and conduct problem-solving techniques effectively.', 'A6.B.0.f.14814'), ('Construct and search Knowledge Graphs using vector similarity search and vector databases.', 'A6.E.4.g.24174'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504'), ('Strong problem identification and problem-solving skills.', 'A6.B.0.y.15226'), ('Ability to develop custom algorithms for solving complex real estate business problems using both structured and unstructured data from multiple sources.', 'A6.J.8.d.19007'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Implement and optimize data structures and algorithms to solve complex problems.', 'A6.J.8.f.28567'), ('Conduct penetration testing and threat hunting activities.', 'A6.B.2.z.14231'), ('Design, develop, and implement knowledge-based systems, including ontologies, taxonomies, and knowledge graphs to support data integration and semantic search.', 'A6.G.0.j.27688'), ('Ability to draw sound scientific conclusions and logical inferences based on data analysis.', 'A6.D.0.k.23435'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Demonstrates independent and strategic problem-solving skills in planning and decision making.', 'A6.B.3.b.13430'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Understand, implement, and codify algorithms while evaluating their performance and suitability for problem-solving in various applications.', 'A6.G.0.e.26376'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Understand and apply knowledge of artificial intelligence and GenAI tools.', 'A6.A.16.c.29444')]</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3982,25 +3982,25 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="S20" t="n">
         <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>0.651</v>
+        <v>0.582</v>
       </c>
       <c r="U20" t="n">
-        <v>0.796</v>
+        <v>0.775</v>
       </c>
       <c r="V20" t="n">
-        <v>0.698</v>
+        <v>0.61</v>
       </c>
       <c r="W20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>[('7368', 'Develop computational methods for solving problems that occur in areas of science and engineering or that come from applications in business or industry.')]</t>
+          <t>[('217', "Study different tree species' classification, life history, light and soil requirements, adaptation to new environmental conditions and resistance to disease and insects."), ('219', 'Develop techniques for measuring and identifying trees.'), ('7368', 'Develop computational methods for solving problems that occur in areas of science and engineering or that come from applications in business or industry.'), ('20325', 'Execute or manage social media campaigns to inform search marketing tactics.'), ('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Design and develop AI algorithms and solutions for various applications, including conversational systems, intelligent agents, and generative AI tools.', 'A6.J.4.d.29651'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Design, develop, and implement advanced machine learning models and algorithms for various applications.', 'A6.J.6.b.29753'), ('Develop and implement object detection, classification, and segmentation algorithms for image and video analysis.', 'A6.G.0.g.28401'), ('Demonstrates strong analytical thinking and problem-solving skills, applying algorithms and data science methods to develop effective solutions.', 'A6.B.0.a.23816'), ('Demonstrate proficiency in search algorithms and their evaluation metrics for information retrieval, as well as understanding search engine functions including crawling, indexing, and ranking processes.', 'A6.K.3.b.15378'), ('Has basic knowledge and understanding of machine learning techniques and concepts.', 'A6.A.16.b.29712'), ('Demonstrate familiarity with image processing and computer vision techniques, algorithms, and software.', 'A6.A.22.a.28652'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706')]</t>
+          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Design and develop AI algorithms and solutions for various applications, including conversational systems, intelligent agents, and generative AI tools.', 'A6.J.4.d.29651'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Utilize graph data in a machine learning environment.', 'A6.J.1.h.29665'), ('Understand and apply search engine algorithms and ranking factors to enhance organic search results.', 'A6.E.5.l.14614'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Knowledge of reinforcement learning algorithms and unsupervised learning techniques, including understanding of regularization, embeddings, loss functions, and optimization strategies.', 'A6.A.16.b.29272'), ('Experience in deep learning algorithms for search and recommendation systems.', 'A6.A.16.c.27070'), ('Design, develop, and implement advanced machine learning models and algorithms for various applications.', 'A6.J.6.b.29753'), ('Develop and implement object detection, classification, and segmentation algorithms for image and video analysis.', 'A6.G.0.g.28401'), ('Demonstrates strong analytical thinking and problem-solving skills, applying algorithms and data science methods to develop effective solutions.', 'A6.B.0.a.23816'), ('Demonstrate proficiency in search algorithms and their evaluation metrics for information retrieval, as well as understanding search engine functions including crawling, indexing, and ranking processes.', 'A6.K.3.b.15378'), ('Ability to solve complex problems in machine learning, information retrieval, natural language processing, and computer vision.', 'A6.A.16.b.25437'), ('Has basic knowledge and understanding of machine learning techniques and concepts.', 'A6.A.16.b.29712'), ('Demonstrate familiarity with image processing and computer vision techniques, algorithms, and software.', 'A6.A.22.a.28652'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706')]</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -4135,25 +4135,25 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.649</v>
+        <v>0.632</v>
       </c>
       <c r="U21" t="n">
         <v>0.742</v>
       </c>
       <c r="V21" t="n">
-        <v>0.659</v>
+        <v>0.637</v>
       </c>
       <c r="W21" t="n">
         <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('14623', 'Analyze problems to develop solutions involving computer hardware and software.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('14758', 'Correct testing-identified problems, or recommend actions for their resolution.'), ('14293', 'Collaborate with other operators to solve unit problems.'), ('18965', 'Develop and implement solutions for network problems.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.')]</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>[('Develop computer algorithms using linear algebra, calculus, differential equations, and numerical methods.', 'A6.G.0.e.28013'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Design, develop, and implement knowledge-based systems, including ontologies, taxonomies, and knowledge graphs to support data integration and semantic search.', 'A6.G.0.j.27688'), ('Perform fuzzy matching, text mining, and data reduction.', 'A6.D.1.k.28989'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Ability to identify, investigate, and resolve problems by determining logical solutions and recommending corrective actions.', 'A6.G.6.a.15328'), ('Develop and implement computer vision algorithms for object detection, feature tracking, and image processing using relevant hardware and software technologies.', 'A6.G.0.g.29612'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience in modifying and applying advanced algorithms to solve practical problems.', 'A6.J.8.g.25748'), ('Implement and optimize data structures and algorithms to solve complex problems.', 'A6.J.8.f.28567'), ('Ability to accurately explain the functioning of a decision tree and code it from scratch.', 'A6.H.2.d.29644'), ('Use machine learning, deep learning, and neural networks to model data and solve problems.', 'A6.A.16.b.29445'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Ability to develop machine learning and artificial intelligence techniques and algorithms to solve complex business problems using both supervised and unsupervised methodologies.', 'A6.J.6.i.26996'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Develop and apply expertise in artificial intelligence and machine learning algorithms.', 'A6.J.4.h.29758')]</t>
+          <t>[('Develop computer algorithms using linear algebra, calculus, differential equations, and numerical methods.', 'A6.G.0.e.28013'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Design, develop, and implement knowledge-based systems, including ontologies, taxonomies, and knowledge graphs to support data integration and semantic search.', 'A6.G.0.j.27688'), ('Perform fuzzy matching, text mining, and data reduction.', 'A6.D.1.k.28989'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Deep understanding of mathematics and the theoretical foundations of machine learning, AI, and NLP algorithms.', 'A6.J.14.d.22501'), ('Design and create logical and physical databases using relational database principles.', 'A6.E.3.f.18280'), ('Ability to identify, investigate, and resolve problems by determining logical solutions and recommending corrective actions.', 'A6.G.6.a.15328'), ('Possesses expert knowledge of human-computer interaction principles.', 'A6.A.3.c.25588'), ('Develop and maintain analytical and semantic models for language processing.', 'A6.J.6.b.28881'), ('Develop and implement computer vision algorithms for object detection, feature tracking, and image processing using relevant hardware and software technologies.', 'A6.G.0.g.29612'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience in modifying and applying advanced algorithms to solve practical problems.', 'A6.J.8.g.25748'), ('Implement and optimize data structures and algorithms to solve complex problems.', 'A6.J.8.f.28567'), ('Design and implement control algorithms and software programs for intelligent robot behaviors and machine control systems.', 'A6.J.5.e.25702'), ('Ability to accurately explain the functioning of a decision tree and code it from scratch.', 'A6.H.2.d.29644'), ('Use machine learning, deep learning, and neural networks to model data and solve problems.', 'A6.A.16.b.29445'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Ability to develop machine learning and artificial intelligence techniques and algorithms to solve complex business problems using both supervised and unsupervised methodologies.', 'A6.J.6.i.26996'), ('Provide software structure and validation direction for AI software solutions that integrate AI algorithms to solve applied problems.', 'A6.J.4.d.26074'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Develop and apply expertise in artificial intelligence and machine learning algorithms.', 'A6.J.4.h.29758')]</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -4338,25 +4338,25 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
       </c>
       <c r="T22" t="n">
-        <v>0.694</v>
+        <v>0.669</v>
       </c>
       <c r="U22" t="n">
-        <v>0.698</v>
+        <v>0.649</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.663</v>
       </c>
       <c r="W22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('6340', 'Prepare and deliver lectures to undergraduate or graduate students on topics such as how to speak and write a foreign language and the cultural aspects of areas where a particular language is used.'), ('7368', 'Develop computational methods for solving problems that occur in areas of science and engineering or that come from applications in business or industry.')]</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>[('Knowledge of machine learning techniques, algorithms, and applications in artificial intelligence.', 'A6.A.16.c.29833'), ('Knowledge of machine learning and AI applications across various domains including automation, search and personalization, workforce planning, database management, network management, ADAS, and mechatronics.', 'A6.A.16.a.29158'), ('Proficiency in multiple higher-level programming languages, including Python, C, C++, Fortran, Java, and MATLAB, commonly used in scientific computing.', 'A6.B.8.r.19154'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124')]</t>
+          <t>[('Knowledge of machine learning techniques, algorithms, and applications in artificial intelligence.', 'A6.A.16.c.29833'), ('Develop and implement algorithms and data structures to solve problems using web technologies and object-oriented programming.', 'A6.G.0.e.18538'), ('Knowledge of machine learning and AI applications across various domains including automation, search and personalization, workforce planning, database management, network management, ADAS, and mechatronics.', 'A6.A.16.a.29158'), ('Proficiency in multiple higher-level programming languages, including Python, C, C++, Fortran, Java, and MATLAB, commonly used in scientific computing.', 'A6.B.8.r.19154'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Develop software solutions and scripts using C++, Python, and other programming languages.', 'A6.K.2.d.19737')]</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -4590,25 +4590,25 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>0.671</v>
+        <v>0.605</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0.728</v>
+        <v>0.668</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('14629', 'Conduct logical analyses of business, scientific, engineering, and other technical problems, formulating mathematical models of problems for solution by computers.'), ('10901', 'Train others to install, use, or maintain robots.'), ('1269', 'Compile and write documentation of program development and subsequent revisions, inserting comments in the coded instructions so others can understand the program.')]</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Advance AI techniques in computer vision, robotics, and natural language processing, including contributions to open source libraries and frameworks.', 'A6.J.0.j.28641'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Use machine learning, deep learning, and neural networks to model data and solve problems.', 'A6.A.16.b.29445'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Ability to apply strong knowledge of algorithms and data structures to solve complex business and technical problems.', 'A6.B.0.d.20576')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Design and develop AI algorithms and solutions for various applications, including conversational systems, intelligent agents, and generative AI tools.', 'A6.J.4.d.29651'), ('Stay current on AI and machine learning trends, tools, technologies, and regulations to enhance systems and inform strategy.', 'A6.J.2.s.27326'), ('Knowledge of AI technologies and their applications in customer care, scientific research, marketing, decision-making systems, and innovative solutions.', 'A6.D.1.e.28844'), ('Continuously improve and refine AI models and algorithms based on real-world data and performance feedback.', 'A6.J.10.d.25935'), ('Advance AI techniques in computer vision, robotics, and natural language processing, including contributions to open source libraries and frameworks.', 'A6.J.0.j.28641'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Use machine learning, deep learning, and neural networks to model data and solve problems.', 'A6.A.16.b.29445'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Design, implement, and validate machine learning models and techniques for real-world applications.', 'A6.J.11.b.29549'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Ability to apply strong knowledge of algorithms and data structures to solve complex business and technical problems.', 'A6.B.0.d.20576'), ('Ability to quickly learn and evaluate new guidelines, software, technical concepts, and programming languages.', 'A6.H.0.a.19465'), ('Has an excellent understanding of coding methods, best practices, structure, and techniques.', 'A6.K.3.c.19889')]</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -4714,25 +4714,25 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="S25" t="n">
         <v>14</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.658</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.709</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.658</v>
       </c>
       <c r="W25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and test statistical models and machine learning algorithms.', 'A6.C.4.p.29508'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Proficient in designing, implementing, and optimizing computer vision algorithms, including hearing enhancement and real-time image processing, using Python, MATLAB, C++, and C#.', 'A6.J.9.d.25863'), ('Train machine learning algorithms for data classification and speech recognition.', 'A6.J.11.f.29893')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and test statistical models and machine learning algorithms.', 'A6.C.4.p.29508'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Build and optimize classifiers using machine learning techniques and prototype data pipelines for model deployment and analytics.', 'A6.J.11.j.27737'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Proficient in designing, implementing, and optimizing computer vision algorithms, including hearing enhancement and real-time image processing, using Python, MATLAB, C++, and C#.', 'A6.J.9.d.25863'), ('Train machine learning algorithms for data classification and speech recognition.', 'A6.J.11.f.29893'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892')]</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -4877,25 +4877,25 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>0.749</v>
+        <v>0.747</v>
       </c>
       <c r="U26" t="n">
         <v>0.87</v>
       </c>
       <c r="V26" t="n">
-        <v>0.782</v>
+        <v>0.757</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('20327', 'Improve search-related activities through ongoing analysis, experimentation, or optimization tests, using A/B or multivariate methods.'), ('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>[('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Experience in deep learning algorithms for search and recommendation systems.', 'A6.A.16.c.27070'), ('Ability to accurately explain the functioning of a decision tree and code it from scratch.', 'A6.H.2.d.29644')]</t>
+          <t>[('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Experience in deep learning algorithms for search and recommendation systems.', 'A6.A.16.c.27070'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Ability to accurately explain the functioning of a decision tree and code it from scratch.', 'A6.H.2.d.29644')]</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -4997,25 +4997,25 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
       </c>
       <c r="T27" t="n">
-        <v>0.663</v>
+        <v>0.698</v>
       </c>
       <c r="U27" t="n">
-        <v>0.849</v>
+        <v>0.778</v>
       </c>
       <c r="V27" t="n">
-        <v>0.663</v>
+        <v>0.698</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -5107,17 +5107,17 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
+          <t>[('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.'), ('20105', 'Write articles and books.')]</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>[('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Experience with graph databases, semantic layers, and data ontologies.', 'A6.E.3.f.21813'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504')]</t>
+          <t>[('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Experience with graph databases, semantic layers, and data ontologies.', 'A6.E.3.f.21813'), ('Design, develop, and implement knowledge-based systems, including ontologies, taxonomies, and knowledge graphs to support data integration and semantic search.', 'A6.G.0.j.27688'), ('Apply natural language processing (NLP) techniques for tasks such as sentiment analysis, text classification, entity recognition, and topic modeling to analyze and interpret textual data.', 'A6.G.0.n.27966'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504'), ('Possesses in-depth knowledge of AI, machine learning, and data science concepts, including algorithmic biases, tools, and techniques for effective application and collaboration in related fields.', 'A6.A.16.b.28709')]</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -5126,25 +5126,25 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
       </c>
       <c r="T28" t="n">
-        <v>0.678</v>
+        <v>0.665</v>
       </c>
       <c r="U28" t="n">
         <v>0.761</v>
       </c>
       <c r="V28" t="n">
-        <v>0.678</v>
+        <v>0.67</v>
       </c>
       <c r="W28" t="n">
         <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17559', 'Study communication code languages or foreign languages to translate intelligence.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('9261', 'Develop designs using specialized computer software.'), ('17086', 'Conduct clinical or basic research.')]</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ("Possesses a Bachelor's degree in Computer Science, Data Science, or a related technical field, including areas such as Computer Engineering, Artificial Intelligence, Mathematics, Information Technology, or Information Systems.", 'A6.A.3.h.20061'), ('Proficient in programming with Python and related languages, demonstrating strong skills in data structures, algorithms, and scripting.', 'A6.K.1.b.17623'), ('Apply machine learning techniques such as clustering, logistic regression, CART, random forests, SVM, and neural networks to solve regression and classification problems.', 'A6.J.14.e.29739'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Research and implement state-of-the-art AI algorithms and techniques to enhance model performance and optimize accuracy, speed, and robustness.', 'A6.J.2.m.28729'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Perform state of the art research to advance the science and technology of machine learning and artificial intelligence.', 'A6.J.3.d.29776')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ("Possesses a Bachelor's degree in Computer Science, Data Science, or a related technical field, including areas such as Computer Engineering, Artificial Intelligence, Mathematics, Information Technology, or Information Systems.", 'A6.A.3.h.20061'), ('Proficient in programming with Python and related languages, demonstrating strong skills in data structures, algorithms, and scripting.', 'A6.K.1.b.17623'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Apply machine learning techniques such as clustering, logistic regression, CART, random forests, SVM, and neural networks to solve regression and classification problems.', 'A6.J.14.e.29739'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Research and implement state-of-the-art AI algorithms and techniques to enhance model performance and optimize accuracy, speed, and robustness.', 'A6.J.2.m.28729'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Ability to design and code efficient algorithms and leverage computer science skills to solve mechanical engineering problems and advance Earth science knowledge.', 'A6.J.9.h.18462'), ('Perform state of the art research to advance the science and technology of machine learning and artificial intelligence.', 'A6.J.3.d.29776')]</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -5279,25 +5279,25 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
       </c>
       <c r="T29" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.658</v>
       </c>
       <c r="U29" t="n">
         <v>0.743</v>
       </c>
       <c r="V29" t="n">
-        <v>0.756</v>
+        <v>0.743</v>
       </c>
       <c r="W29" t="n">
         <v>3</v>
       </c>
       <c r="X29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16122', 'Select methods, techniques, or criteria for data warehousing evaluative procedures.'), ('9788', 'Compute and analyze data, using statistical formulas and computers or calculators.'), ('16787', 'Develop data models and databases.'), ('5711', 'Prepare and deliver lectures to undergraduate or graduate students on topics such as linear algebra, differential equations, and discrete mathematics.')]</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Knowledge of machine learning and AI applications across various domains including automation, search and personalization, workforce planning, database management, network management, ADAS, and mechatronics.', 'A6.A.16.a.29158'), ('Design, develop, and implement advanced machine learning models and algorithms for various applications.', 'A6.J.6.b.29753'), ('Demonstrate strong theoretical understanding of machine learning algorithms and techniques.', 'A6.A.16.b.29709'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Employ machine learning, deep learning, and data mining techniques.', 'A6.J.14.d.29750'), ('Develop and implement machine learning algorithms using Python and its associated libraries for data analysis and processing.', 'A6.J.3.b.29721'), ('Develop, write, and automate tasks using Python scripts.', 'A6.K.0.b.23854'), ('Build and train deep learning models using TensorFlow or PyTorch frameworks.', 'A6.J.11.a.29567'), ('Utilize TensorFlow for applications in artificial intelligence, deep learning, or natural language processing.', 'A6.J.1.h.29891'), ('Use Python and libraries like Pandas and NumPy for data manipulation and automation.', 'A6.B.8.u.26549'), ('Develop and deploy machine learning models using frameworks and tools including TensorFlow, PyTorch, Scikit-learn, and Keras.', 'A6.J.11.a.28257'), ('Design, train, and deploy machine learning models, including neural networks for tasks such as image and time series data processing.', 'A6.J.6.b.29483'), ('Deep understanding of mathematics and the theoretical foundations of machine learning, AI, and NLP algorithms.', 'A6.J.14.d.22501'), ('Knowledge of machine learning, artificial intelligence, and statistical modeling fundamentals.', 'A6.A.16.a.29030')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Knowledge of machine learning and AI applications across various domains including automation, search and personalization, workforce planning, database management, network management, ADAS, and mechatronics.', 'A6.A.16.a.29158'), ('Design, develop, and implement advanced machine learning models and algorithms for various applications.', 'A6.J.6.b.29753'), ('Demonstrate strong theoretical understanding of machine learning algorithms and techniques.', 'A6.A.16.b.29709'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Strong understanding of feature engineering, model evaluation, performance optimization, and monitoring, including metrics related to precision, recall, bias, robustness, and scalability.', 'A6.J.6.b.29129'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Employ machine learning, deep learning, and data mining techniques.', 'A6.J.14.d.29750'), ('Develop and implement machine learning algorithms using Python and its associated libraries for data analysis and processing.', 'A6.J.3.b.29721'), ('Develop, write, and automate tasks using Python scripts.', 'A6.K.0.b.23854'), ('Generate, debug, and maintain Python scripts for data manipulation, automation, testing, and reporting.', 'A6.B.8.a.20279'), ('Proficient understanding of data structures, algorithms, object-oriented programming, and their applications in data solutions and indexing.', 'A6.A.15.d.23833'), ('Build and train deep learning models using TensorFlow or PyTorch frameworks.', 'A6.J.11.a.29567'), ('Utilize TensorFlow for applications in artificial intelligence, deep learning, or natural language processing.', 'A6.J.1.h.29891'), ('Use Python and libraries like Pandas and NumPy for data manipulation and automation.', 'A6.B.8.u.26549'), ('Develop and deploy machine learning models using frameworks and tools including TensorFlow, PyTorch, Scikit-learn, and Keras.', 'A6.J.11.a.28257'), ('Design, train, and deploy machine learning models, including neural networks for tasks such as image and time series data processing.', 'A6.J.6.b.29483'), ('Deep understanding of mathematics and the theoretical foundations of machine learning, AI, and NLP algorithms.', 'A6.J.14.d.22501'), ('Knowledge of machine learning, artificial intelligence, and statistical modeling fundamentals.', 'A6.A.16.a.29030'), ('Develop and fine-tune large neural networks using deep learning frameworks and training methodologies.', 'A6.J.12.d.28404')]</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -5455,25 +5455,25 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="S30" t="n">
         <v>14</v>
       </c>
       <c r="T30" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.671</v>
       </c>
       <c r="U30" t="n">
-        <v>0.665</v>
+        <v>0.661</v>
       </c>
       <c r="V30" t="n">
-        <v>0.708</v>
+        <v>0.703</v>
       </c>
       <c r="W30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>[('Deep understanding of mathematics and the theoretical foundations of machine learning, AI, and NLP algorithms.', 'A6.J.14.d.22501'), ('Understand and implement architectures and technologies in distributed computing systems.', 'A6.A.15.g.19928'), ('Advanced experience in pattern recognition and predictive modeling.', 'A6.J.11.g.29880'), ('Design, verify, and integrate wireless systems and algorithms.', 'A6.J.5.k.17722'), ('Develop and implement data warehouse design, modeling, and data integration techniques.', 'A6.F.8.b.23847')]</t>
+          <t>[('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Deep understanding of mathematics and the theoretical foundations of machine learning, AI, and NLP algorithms.', 'A6.J.14.d.22501'), ('Understand and implement architectures and technologies in distributed computing systems.', 'A6.A.15.g.19928'), ('Advanced experience in pattern recognition and predictive modeling.', 'A6.J.11.g.29880'), ('Design, verify, and integrate wireless systems and algorithms.', 'A6.J.5.k.17722'), ('Develop and implement data warehouse design, modeling, and data integration techniques.', 'A6.F.8.b.23847'), ('Address security issues associated with distributed systems and internet services.', 'A6.A.15.g.16260')]</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -5573,25 +5573,25 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
       </c>
       <c r="T31" t="n">
-        <v>0.549</v>
+        <v>0.535</v>
       </c>
       <c r="U31" t="n">
         <v>0.513</v>
       </c>
       <c r="V31" t="n">
-        <v>0.549</v>
+        <v>0.535</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('6463', 'Arrange for lectures by experts in designated fields.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16037', 'Research or evaluate new technologies for use in fraud detection systems.'), ('21595', 'Monitor developments in the fields of industrial technology, business, finance, and economic theory.'), ('19637', 'Research computerized automotive applications, such as telemetrics, intelligent transportation systems, artificial intelligence, or automatic control.')]</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Deep understanding of machine learning algorithms and concepts, including supervised, unsupervised, semi-supervised, and reinforcement learning techniques.', 'A6.A.16.b.29090'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Experience with machine learning and artificial intelligence algorithms in healthcare data applications.', 'A6.A.16.c.28463'), ('Develop and deploy machine learning models for fraud detection and risk assessment.', 'A6.J.11.e.26375'), ('Build and optimize algorithms and models to enhance the marketplace impact and operational efficiency of autonomous vehicles.', 'A6.E.1.f.28214'), ('Leverage advanced technologies such as machine learning and AI to develop innovative customer services and enhance data-driven decision-making processes.', 'A6.J.2.o.27625'), ('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185'), ('Develop and implement innovative solutions using artificial intelligence and Generative AI to enhance productivity and improve business functions.', 'A6.J.4.e.28950'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Integrate and leverage generative AI models and technologies in applications and workflows.', 'A6.J.0.m.29765'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Create and implement applications using artificial intelligence solutions across various sectors, including medicine and construction.', 'A6.J.4.d.29737'), ('Research and apply modern AI capabilities in machine learning, algorithms, and ethical considerations while assisting with robotic solutions.', 'A6.A.10.a.28513'), ('Ability to stay current with emerging AI technologies and methodologies, integrating them to enhance business operations and drive innovation.', 'A6.J.2.s.26286'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Deep understanding of machine learning algorithms and concepts, including supervised, unsupervised, semi-supervised, and reinforcement learning techniques.', 'A6.A.16.b.29090'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Experience with machine learning and artificial intelligence algorithms in healthcare data applications.', 'A6.A.16.c.28463'), ('Develop and deploy machine learning models for fraud detection and risk assessment.', 'A6.J.11.e.26375'), ('Build and optimize algorithms and models to enhance the marketplace impact and operational efficiency of autonomous vehicles.', 'A6.E.1.f.28214'), ('Leverage advanced technologies such as machine learning and AI to develop innovative customer services and enhance data-driven decision-making processes.', 'A6.J.2.o.27625'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589'), ('Design and implement evaluation frameworks and metrics for agentic AI systems.', 'A6.J.4.d.29858'), ('Expertise in establishing consumer privacy-focused data collection processes while ensuring compliance with privacy laws and regulations such as GDPR and CCPA.', 'A6.A.14.d.15612'), ('Ability to evaluate and explore emerging technologies, specifically AI and machine learning, to enhance workforce analytics and assess their impact on financial services.', 'A6.J.7.j.22410'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185'), ('Develop and implement innovative solutions using artificial intelligence and Generative AI to enhance productivity and improve business functions.', 'A6.J.4.e.28950'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Integrate and leverage generative AI models and technologies in applications and workflows.', 'A6.J.0.m.29765'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Create and implement applications using artificial intelligence solutions across various sectors, including medicine and construction.', 'A6.J.4.d.29737'), ('Research and apply modern AI capabilities in machine learning, algorithms, and ethical considerations while assisting with robotic solutions.', 'A6.A.10.a.28513'), ('Ability to stay current with emerging AI technologies and methodologies, integrating them to enhance business operations and drive innovation.', 'A6.J.2.s.26286'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610')]</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -5740,25 +5740,25 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="S32" t="n">
         <v>11</v>
       </c>
       <c r="T32" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="U32" t="n">
-        <v>0.704</v>
+        <v>0.722</v>
       </c>
       <c r="V32" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16789', 'Design and apply bioinformatics algorithms including unsupervised and supervised machine learning, dynamic programming, or graphic algorithms.'), ('17559', 'Study communication code languages or foreign languages to translate intelligence.')]</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and implement machine learning models and algorithms, including feature engineering and model evaluation.', 'A6.J.11.h.29580'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Design and implement advanced machine learning algorithms and models for classification, regression, clustering, recommendation, and natural language processing tasks.', 'A6.J.11.b.28592'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Develop and optimize computer vision algorithms and models, including convolutional neural networks, for tasks such as image classification, speech recognition, and time series forecasting.', 'A6.G.0.g.28003'), ('Demonstrate familiarity with agentic AI frameworks, concepts, and orchestration tools for building AI agent-based applications.', 'A6.A.15.l.29608'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Apply machine learning techniques and statistical modeling to large datasets.', 'A6.J.14.f.29871')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and implement machine learning models and algorithms, including feature engineering and model evaluation.', 'A6.J.11.h.29580'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Design and implement advanced machine learning algorithms and models for classification, regression, clustering, recommendation, and natural language processing tasks.', 'A6.J.11.b.28592'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Develop and optimize computer vision algorithms and models, including convolutional neural networks, for tasks such as image classification, speech recognition, and time series forecasting.', 'A6.G.0.g.28003'), ('Demonstrate familiarity with agentic AI frameworks, concepts, and orchestration tools for building AI agent-based applications.', 'A6.A.15.l.29608'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Apply machine learning techniques and statistical modeling to large datasets.', 'A6.J.14.f.29871'), ('Develop and apply expertise in artificial intelligence and machine learning algorithms.', 'A6.J.4.h.29758')]</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5873,25 +5873,25 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S33" t="n">
         <v>18</v>
       </c>
       <c r="T33" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="U33" t="n">
         <v>0.717</v>
       </c>
-      <c r="U33" t="n">
-        <v>0.705</v>
-      </c>
       <c r="V33" t="n">
-        <v>0.717</v>
+        <v>0.721</v>
       </c>
       <c r="W33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('21487', 'Develop conceptual designs of security systems.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('14623', 'Analyze problems to develop solutions involving computer hardware and software.')]</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>[('Develop and implement statistical models and algorithms for data-driven decision-making and business challenges.', 'A6.F.6.j.25884'), ('Research and develop state-of-the-art machine learning algorithms for camera imaging and multimedia applications.', 'A6.J.2.m.28114'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Train machine learning algorithms for data classification and speech recognition.', 'A6.J.11.f.29893'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Work on robotics-related topics such as computer vision, deep learning, machine learning, planning, human-machine teaming, and multi-robot systems.', 'A6.A.10.c.26884')]</t>
+          <t>[('Demonstrate an understanding of computer science fundamentals, including data structures, algorithms, and AI/machine learning concepts.', 'A6.A.9.e.26712'), ('Develop and implement statistical models and algorithms for data-driven decision-making and business challenges.', 'A6.F.6.j.25884'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Research and develop state-of-the-art machine learning algorithms for camera imaging and multimedia applications.', 'A6.J.2.m.28114'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Train machine learning algorithms for data classification and speech recognition.', 'A6.J.11.f.29893'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Work on robotics-related topics such as computer vision, deep learning, machine learning, planning, human-machine teaming, and multi-robot systems.', 'A6.A.10.c.26884')]</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -6007,25 +6007,25 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S34" t="n">
         <v>13</v>
       </c>
       <c r="T34" t="n">
-        <v>0.694</v>
+        <v>0.678</v>
       </c>
       <c r="U34" t="n">
-        <v>0.645</v>
+        <v>0.651</v>
       </c>
       <c r="V34" t="n">
-        <v>0.694</v>
+        <v>0.678</v>
       </c>
       <c r="W34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X34" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
+          <t>[('16530', 'Design robotic systems, such as automatic vehicle control, autonomous vehicles, advanced displays, advanced sensing, robotic platforms, computer vision, or telematics systems.')]</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>[('Strong interest in artificial intelligence and machine learning, including concepts, algorithms, applications in various fields, and continuous learning in emerging technologies.', 'A6.A.16.a.28899'), ('Work on robotics-related topics such as computer vision, deep learning, machine learning, planning, human-machine teaming, and multi-robot systems.', 'A6.A.10.c.26884'), ('Understand, implement, and codify algorithms while evaluating their performance and suitability for problem-solving in various applications.', 'A6.G.0.e.26376'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Knowledge of machine learning, artificial intelligence, and statistical modeling fundamentals.', 'A6.A.16.a.29030'), ('Develop and implement robotic algorithms for navigation, perception, planning, and sensor processing.', 'A6.G.0.z.29153'), ('Develop and optimize algorithms for robotics perception, navigation, planning, and control systems.', 'A6.G.0.z.28415'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749')]</t>
+          <t>[('Strong interest in artificial intelligence and machine learning, including concepts, algorithms, applications in various fields, and continuous learning in emerging technologies.', 'A6.A.16.a.28899'), ('Work on robotics-related topics such as computer vision, deep learning, machine learning, planning, human-machine teaming, and multi-robot systems.', 'A6.A.10.c.26884'), ('Understand, implement, and codify algorithms while evaluating their performance and suitability for problem-solving in various applications.', 'A6.G.0.e.26376'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Knowledge of machine learning, artificial intelligence, and statistical modeling fundamentals.', 'A6.A.16.a.29030'), ('Develop and implement robotic algorithms for navigation, perception, planning, and sensor processing.', 'A6.G.0.z.29153'), ('Develop and optimize algorithms for robotics perception, navigation, planning, and control systems.', 'A6.G.0.z.28415'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Research and apply modern AI capabilities in machine learning, algorithms, and ethical considerations while assisting with robotic solutions.', 'A6.A.10.a.28513')]</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S35" t="n">
         <v>14</v>
@@ -6187,16 +6187,16 @@
         <v>0.66</v>
       </c>
       <c r="U35" t="n">
-        <v>0.672</v>
+        <v>0.669</v>
       </c>
       <c r="V35" t="n">
         <v>0.66</v>
       </c>
       <c r="W35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('1450', 'Compute mathematical formulas to develop and design detailed specifications for components or machinery, using computer-assisted equipment.'), ('7529', 'Raise funds for scientific research.')]</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>[('Engage in coursework or projects related to machine learning, data mining, or artificial intelligence.', 'A6.A.16.a.29014'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Ability to solve a wide range of problems using data collection and analysis techniques, including data mining and machine learning.', 'A6.J.1.c.25124'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Expertise in selecting, manipulating, and transforming data into features for machine learning algorithms using dimensionality reduction, feature importance, and feature selection techniques.', 'A6.A.16.b.29068'), ('Implement and apply machine learning methodologies for clustering, classification, regression, and anomaly detection, including training and validating predictive models.', 'A6.D.1.k.28888'), ('Develop and deploy statistical and machine learning models for predictive analysis and signal processing.', 'A6.J.3.a.29779'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('Perform large-scale model training using distributed training and optimization techniques for machine learning models.', 'A6.G.0.f.29874'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Strong knowledge of machine learning concepts and techniques, including supervised and unsupervised learning, regression, classification, clustering, and various advanced methods.', 'A6.J.11.j.29574'), ('Demonstrates a proven ability to rapidly learn, adapt, and apply new mathematical theories, technologies, procedures, and systems effectively in various technical environments.', 'A6.H.0.a.14753')]</t>
+          <t>[('Engage in coursework or projects related to machine learning, data mining, or artificial intelligence.', 'A6.A.16.a.29014'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Strong understanding of machine learning concepts, algorithms, and workflows, including supervised/unsupervised learning, deep learning, reinforcement learning, and statistical modeling.', 'A6.J.3.c.29389'), ('Possesses a solid math background along with a strong understanding of algorithms and data structures.', 'A6.A.9.d.23472'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Ability to solve a wide range of problems using data collection and analysis techniques, including data mining and machine learning.', 'A6.J.1.c.25124'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Expertise in selecting, manipulating, and transforming data into features for machine learning algorithms using dimensionality reduction, feature importance, and feature selection techniques.', 'A6.A.16.b.29068'), ('Implement and apply machine learning methodologies for clustering, classification, regression, and anomaly detection, including training and validating predictive models.', 'A6.D.1.k.28888'), ('Develop and deploy statistical and machine learning models for predictive analysis and signal processing.', 'A6.J.3.a.29779'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Experiment with various algorithms and techniques to optimize model performance and improve prediction accuracy.', 'A6.J.10.d.28400'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('Implement and develop numerical methods and optimization algorithms.', 'A6.J.11.c.24578'), ('Utilize graph data in a machine learning environment.', 'A6.J.1.h.29665'), ('Perform large-scale model training using distributed training and optimization techniques for machine learning models.', 'A6.G.0.f.29874'), ('Experience with neural deep learning methods and machine learning.', 'A6.A.16.c.29894'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Strong knowledge of machine learning concepts and techniques, including supervised and unsupervised learning, regression, classification, clustering, and various advanced methods.', 'A6.J.11.j.29574'), ('Demonstrates a proven ability to rapidly learn, adapt, and apply new mathematical theories, technologies, procedures, and systems effectively in various technical environments.', 'A6.H.0.a.14753')]</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6360,25 +6360,25 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="S36" t="n">
         <v>17</v>
       </c>
       <c r="T36" t="n">
-        <v>0.674</v>
+        <v>0.681</v>
       </c>
       <c r="U36" t="n">
         <v>0.777</v>
       </c>
       <c r="V36" t="n">
-        <v>0.662</v>
+        <v>0.673</v>
       </c>
       <c r="W36" t="n">
         <v>2</v>
       </c>
       <c r="X36" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
@@ -6500,17 +6500,17 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
+          <t>[('22389', "Answer students' questions."), ('22444', 'Develop instructional materials, such as lesson plans, handouts, or examinations.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('102', 'Develop alternative training methods if expected improvements are not seen.'), ('16837', 'Create or use statistical models for the analysis of genetic data.')]</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>[('Research, experiment with, and implement appropriate machine learning and artificial intelligence algorithms and tools.', 'A6.J.3.d.28225'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Develop and evaluate machine learning and deep learning algorithms for crop management and medical image analysis.', 'A6.J.4.e.27368'), ('Experience with neural deep learning methods and machine learning.', 'A6.A.16.c.29894'), ('Develop and optimize deep neural network models and architectures for predictive applications.', 'A6.J.12.d.29199'), ('Develop and optimize computer vision algorithms and models, including convolutional neural networks, for tasks such as image classification, speech recognition, and time series forecasting.', 'A6.G.0.g.28003'), ('Build and develop neural network architectures using deep learning methods and techniques such as transformers and uncertainty quantification.', 'A6.J.11.e.29337'), ('Utilize TensorFlow for applications in artificial intelligence, deep learning, or natural language processing.', 'A6.J.1.h.29891'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504')]</t>
+          <t>[('Research, experiment with, and implement appropriate machine learning and artificial intelligence algorithms and tools.', 'A6.J.3.d.28225'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Develop and evaluate machine learning and deep learning algorithms for crop management and medical image analysis.', 'A6.J.4.e.27368'), ('Experience with neural deep learning methods and machine learning.', 'A6.A.16.c.29894'), ('Develop and optimize deep neural network models and architectures for predictive applications.', 'A6.J.12.d.29199'), ('Understand and apply model evaluation metrics and techniques for model training and validation.', 'A6.J.11.g.28405'), ('Proficient in machine learning fundamentals, including supervised and unsupervised learning, model training, validation, feature engineering, and debug common issues such as overfitting and leakage.', 'A6.A.16.b.28732'), ('Model complex problems and build algorithms using statistical models, machine learning, and visualization techniques to improve operational efficiency and reduce monetary losses.', 'A6.J.6.f.18695'), ('Expertise in developing computational, machine learning, and statistical analysis methods for integrating and analyzing large-scale genomic data using state-of-the-art technologies in bioinformatics.', 'A6.B.0.p.16498'), ('Develop and optimize computer vision algorithms and models, including convolutional neural networks, for tasks such as image classification, speech recognition, and time series forecasting.', 'A6.G.0.g.28003'), ('Build and develop neural network architectures using deep learning methods and techniques such as transformers and uncertainty quantification.', 'A6.J.11.e.29337'), ('Develop, validate, and deploy predictive models using machine learning frameworks such as PyTorch and TensorFlow.', 'A6.J.11.a.29451'), ('Utilize TensorFlow for applications in artificial intelligence, deep learning, or natural language processing.', 'A6.J.1.h.29891'), ('Utilize machine learning libraries and packages such as PyTorch, Caffe2, TensorFlow, Keras, or Theano.', 'A6.J.1.h.28856'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504'), ('Develop and implement predictive models and algorithms for various applications, including rare genetic diseases and member-based interventions.', 'A6.J.11.h.20976')]</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6519,25 +6519,25 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="S37" t="n">
         <v>7</v>
       </c>
       <c r="T37" t="n">
-        <v>0.704</v>
+        <v>0.644</v>
       </c>
       <c r="U37" t="n">
-        <v>0.672</v>
+        <v>0.622</v>
       </c>
       <c r="V37" t="n">
-        <v>0.704</v>
+        <v>0.644</v>
       </c>
       <c r="W37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X37" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -6613,17 +6613,17 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
+          <t>[('22248', 'Develop and test theories concerning the origin and development of past cultures.'), ('5465', 'Analyze and interpret data to increase the understanding of human social behavior.'), ('9366', 'Develop visual aids and charts for use in lectures or to present evidence in court.'), ('22255', 'Study archival collections of primary historical sources to help explain the origins and development of cultural patterns.')]</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrate experience and expertise in artificial intelligence and machine learning technologies in social work and research contexts.', 'A6.A.16.c.25661')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Strong understanding of robotics systems, including kinematics, dynamics, control algorithms, and principles.', 'A6.A.15.o.28206'), ('Knowledge of AI technologies and their applications in customer care, scientific research, marketing, decision-making systems, and innovative solutions.', 'A6.D.1.e.28844'), ('Demonstrate experience and expertise in artificial intelligence and machine learning technologies in social work and research contexts.', 'A6.A.16.c.25661'), ('Ability to draw concise and logical written conclusions from experiments and data analysis.', 'A6.D.2.e.17894')]</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6632,25 +6632,25 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>0.67</v>
+        <v>0.613</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0.67</v>
+        <v>0.613</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>[('21217', 'Analyze marketing or sales trends to forecast future conditions.'), ('291', 'Work with creative directors to develop design solutions.')]</t>
+          <t>[('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.'), ('22113', 'Analyze aerial photographs to detect and interpret significant military, industrial, resource, or topographical data.'), ('7206', 'Prepare project proposals.'), ('4864', 'Cut pipe and lift up to fitters.'), ('11542', 'Tap and drill holes into pipes to introduce auxiliary lines or devices.'), ('21217', 'Analyze marketing or sales trends to forecast future conditions.'), ('291', 'Work with creative directors to develop design solutions.'), ('2153', 'Analyze operational problems, such as theft and wastage, and establish procedures to alleviate these problems.'), ('14742', 'Collaborate with Web developers to create and operate internal and external Web sites, or to manage projects, such as e-marketing campaigns.')]</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>[('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Gain hands-on experience with AI and machine learning technologies, tools, frameworks, and applications in various domains including project management, medical devices, and security integration.', 'A6.J.4.d.27082'), ('Possesses a strong understanding of computer vision technologies, including image processing, object detection, and machine learning concepts.', 'A6.A.10.c.29285'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develop and implement computer vision algorithms for object detection, feature tracking, and image processing using relevant hardware and software technologies.', 'A6.G.0.g.29612'), ('Model vision problems in the areas of object detection, facial recognition, and temporal machine learning.', 'A6.A.10.c.26684'), ('Research and develop state-of-the-art machine learning algorithms for camera imaging and multimedia applications.', 'A6.J.2.m.28114'), ('Analyze and interpret marketing data to support strategy and performance optimization.', 'A6.D.0.ae.26763'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504'), ('Ability to implement and architect creative technical solutions to complex problems.', 'A6.F.6.l.18972'), ('Demonstrate familiarity with agentic AI frameworks, concepts, and orchestration tools for building AI agent-based applications.', 'A6.A.15.l.29608')]</t>
+          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Gain hands-on experience with AI and machine learning technologies, tools, frameworks, and applications in various domains including project management, medical devices, and security integration.', 'A6.J.4.d.27082'), ('Possesses a strong understanding of computer vision technologies, including image processing, object detection, and machine learning concepts.', 'A6.A.10.c.29285'), ('Develop and deploy AI and ML models and applications, including inference pipelines for medical devices and solutions for edge devices.', 'A6.J.4.e.28510'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Research and develop state-of-the-art machine learning algorithms for camera imaging and multimedia applications.', 'A6.J.2.m.28114'), ('Demonstrated ability to process training data using modern classification techniques and effectively present and tell stories.', 'A6.A.5.c.24123'), ('Develop and implement object detection, classification, and segmentation algorithms for image and video analysis.', 'A6.G.0.g.28401'), ('Develop and implement computer vision algorithms for object detection, feature tracking, and image processing using relevant hardware and software technologies.', 'A6.G.0.g.29612'), ('Participate in the implementation and optimization of algorithms for object detection, tracking, and scene understanding.', 'A6.G.0.e.29798'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Model vision problems in the areas of object detection, facial recognition, and temporal machine learning.', 'A6.A.10.c.26684'), ('Develop and optimize advanced computer vision algorithms and pipelines for real-time performance in production environments.', 'A6.G.0.g.28559'), ('Design and implement robust and scalable data pipelines for pre-processing, feature engineering, and training data augmentation in NLP tasks.', 'A6.G.0.p.28124'), ('Demonstrate expertise in NLP or text mining techniques.', 'A6.J.14.d.28734'), ('Implement state-of-the-art natural language processing models and pipelines.', 'A6.J.2.n.29856'), ('Design and implement scalable data pipelines for data ingestion, processing, and storage from multiple sources.', 'A6.G.0.o.27101'), ('Design and implement scalable and efficient data pipelines and infrastructure to support AI and machine learning initiatives and workflows.', 'A6.J.11.b.29699'), ('Analyze and interpret marketing data to support strategy and performance optimization.', 'A6.D.0.ae.26763'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504'), ('Ability to implement and architect creative technical solutions to complex problems.', 'A6.F.6.l.18972'), ('Demonstrate familiarity with agentic AI frameworks, concepts, and orchestration tools for building AI agent-based applications.', 'A6.A.15.l.29608'), ('Ability to independently manage products end-to-end while effectively collaborating with stakeholders in clinical, business, engineering, and UX design/research.', 'A6.H.6.c.11436')]</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6840,25 +6840,25 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
       </c>
       <c r="T39" t="n">
-        <v>0.645</v>
+        <v>0.646</v>
       </c>
       <c r="U39" t="n">
-        <v>0.669</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="V39" t="n">
-        <v>0.666</v>
+        <v>0.675</v>
       </c>
       <c r="W39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X39" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('21128', 'Schedule courses.'), ('19698', 'Participate in research or testing of computerized automotive applications, such as telemetrics, intelligent transportation systems, artificial intelligence, or automatic control.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('17069', 'Educate patients about diagnoses, prognoses, or treatments.'), ('18088', 'Design, develop, select, test, implement, and evaluate new or modified informatics solutions, data structures, and decision-support mechanisms to support patients, health care professionals, and their information management and human-computer and human-technology interactions within health care contexts.'), ('16789', 'Design and apply bioinformatics algorithms including unsupervised and supervised machine learning, dynamic programming, or graphic algorithms.'), ('19971', 'Examine societal issues and their relationship with both technical systems and the environment.')]</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Conduct research to design, implement, and evaluate AI algorithms for various applications, including medical imaging and cost optimization.', 'A6.J.0.n.29689'), ('Experience with machine learning and artificial intelligence algorithms in healthcare data applications.', 'A6.A.16.c.28463'), ('Apply machine learning algorithms for pattern recognition and predictive modeling in biological data.', 'A6.J.14.f.29796'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop, train, and optimize machine learning models using techniques such as regression and logistic regression.', 'A6.J.11.g.29477'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Experience with neural deep learning methods and machine learning.', 'A6.A.16.c.29894'), ('Develop and deploy AI and ML algorithms and technologies for various applications, including intelligent agents, healthcare, and generative AI solutions.', 'A6.J.2.h.29605'), ('Leverage big data analytics tools to process and analyze large datasets, enhancing the accuracy and effectiveness of generative AI models.', 'A6.J.13.c.28216'), ('Demonstrate knowledge of machine learning and AI algorithms, including graph-based techniques and deep learning methods.', 'A6.A.16.c.29523'), ('Knowledge of data governance, security, privacy, and ethical practices in AI development, including addressing issues like data poisoning and model theft.', 'A6.G.2.k.27697')]</t>
+          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Create and implement applications using artificial intelligence solutions across various sectors, including medicine and construction.', 'A6.J.4.d.29737'), ('Apply machine learning and deep learning techniques, including neural networks and classification algorithms, specifically for advertising, recommendation, and search applications.', 'A6.G.0.n.27074'), ('Knowledge of data governance, security, privacy, and ethical practices in AI development, including addressing issues like data poisoning and model theft.', 'A6.G.2.k.27697'), ('Conduct research to design, implement, and evaluate AI algorithms for various applications, including medical imaging and cost optimization.', 'A6.J.0.n.29689'), ('Develop artificial intelligence or machine learning models using radiology and pathology data while monitoring and interpreting clinical imaging studies.', 'A6.G.0.f.23159'), ('Understand and apply knowledge of artificial intelligence and GenAI tools.', 'A6.A.16.c.29444'), ('Experience with machine learning and artificial intelligence algorithms in healthcare data applications.', 'A6.A.16.c.28463'), ('Apply machine learning algorithms for pattern recognition and predictive modeling in biological data.', 'A6.J.14.f.29796'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Understand and apply search engine algorithms and ranking factors to enhance organic search results.', 'A6.E.5.l.14614'), ('Develop, train, and optimize machine learning models using techniques such as regression and logistic regression.', 'A6.J.11.g.29477'), ('Experience with recommender systems in production.', 'A6.E.5.l.29838'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Proficient in transfer learning and the use of deep learning and neural network frameworks.', 'A6.A.16.c.29802'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Experience with neural deep learning methods and machine learning.', 'A6.A.16.c.29894'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Develop and deploy AI and ML algorithms and technologies for various applications, including intelligent agents, healthcare, and generative AI solutions.', 'A6.J.2.h.29605'), ('Leverage big data analytics tools to process and analyze large datasets, enhancing the accuracy and effectiveness of generative AI models.', 'A6.J.13.c.28216'), ('Demonstrate knowledge of machine learning and AI algorithms, including graph-based techniques and deep learning methods.', 'A6.A.16.c.29523')]</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -7002,25 +7002,25 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="S40" t="n">
         <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>0.728</v>
+        <v>0.697</v>
       </c>
       <c r="U40" t="n">
-        <v>0.728</v>
+        <v>0.721</v>
       </c>
       <c r="V40" t="n">
-        <v>0.728</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="W40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X40" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>[('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Trained in data collection and experimental methods involving neuroimaging techniques (EEG, fNIRS, MRI), eye-tracking, and psychophysiological and behavioral assessments.', 'A6.C.2.b.17594')]</t>
+          <t>[('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ("Possess a Master's or Doctoral degree in biology, neuroscience, engineering, physics, computer science, or a closely related field.", 'A6.A.2.a.11063'), ('Trained in data collection and experimental methods involving neuroimaging techniques (EEG, fNIRS, MRI), eye-tracking, and psychophysiological and behavioral assessments.', 'A6.C.2.b.17594'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Develop and implement machine learning algorithms and data pipelines for biomedical applications, including neuroimaging and image analysis.', 'A6.J.11.h.26427')]</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -7149,25 +7149,25 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S41" t="n">
         <v>7</v>
       </c>
       <c r="T41" t="n">
-        <v>0.624</v>
+        <v>0.55</v>
       </c>
       <c r="U41" t="n">
         <v>0.731</v>
       </c>
       <c r="V41" t="n">
-        <v>0.734</v>
+        <v>0.652</v>
       </c>
       <c r="W41" t="n">
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>[('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Develop, train, and optimize machine learning models using techniques such as regression and logistic regression.', 'A6.J.11.g.29477')]</t>
+          <t>[('Knowledge of machine learning and data science concepts and principles.', 'A6.A.16.a.29474'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Develop, train, and optimize machine learning models using techniques such as regression and logistic regression.', 'A6.J.11.g.29477')]</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>0.729</v>
+        <v>0.722</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>[('6235', 'Assign cases for students to hear and try.')]</t>
+          <t>[('21279', 'Participate in architectural and engineering planning and design, including space and installation management.'), ('6235', 'Assign cases for students to hear and try.'), ('16376', 'Investigate theoretical or conceptual issues, such as the human design considerations of lunar landers or habitats.'), ('19637', 'Research computerized automotive applications, such as telemetrics, intelligent transportation systems, artificial intelligence, or automatic control.'), ('22367', 'Establish and communicate clear objectives for all lessons, units, and projects to students.'), ('5518', 'Develop and test theories, using information from interviews, newspapers, periodicals, case law, historical papers, polls, or statistical sources.'), ('13021', "Adapt other designers' ideas for the mass market."), ('6882', 'Design complex graphics and animation, using independent judgment, creativity, and computer equipment.'), ('16474', 'Design engineering systems for the automation of industrial tasks.'), ('9261', 'Develop designs using specialized computer software.')]</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>[('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589'), ('Conduct research and development in various aspects of artificial intelligence, including interpretability, visualization, generative AI, and health applications.', 'A6.J.0.d.29793'), ('Ability to creatively and quickly solve complex problems.', 'A6.B.0.l.18369'), ('Design, develop, and deploy AI and machine learning models and algorithms for various applications.', 'A6.J.4.d.29855'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Design and implement AI-powered products and solutions, including evaluation pipelines and orchestration approaches.', 'A6.J.4.d.29250'), ('Expert in state-of-the-art methodologies and technologies in AI/ML subdomains, including computer vision and natural language processing, to solve complex business problems in diverse applications such as healthcare and autonomous systems.', 'A6.A.16.a.28962'), ('Evaluate and integrate emerging AI technologies and tools to enhance platform capabilities and solve complex problems.', 'A6.J.0.m.27726'), ('Integrate AI services and algorithms with advanced data solutions and enterprise infrastructure.', 'A6.J.2.g.29674'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('Demonstrate familiarity with TensorFlow and PyTorch.', 'A6.A.22.e.29693'), ('Research and develop state-of-the-art machine learning algorithms for camera imaging and multimedia applications.', 'A6.J.2.m.28114')]</t>
+          <t>[('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Apply deep learning methodologies and neural network architectures, including convolutional and recurrent neural networks, in various contexts such as utility space.', 'A6.G.0.n.29597'), ('Demonstrate a solid grasp of technical concepts and practices in chemical testing, metadata management, aseptic techniques, database technologies, database engineering, and networking fundamentals.', 'A6.G.6.g.13067'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589'), ('Conduct research and development in various aspects of artificial intelligence, including interpretability, visualization, generative AI, and health applications.', 'A6.J.0.d.29793'), ('Understand and apply knowledge of artificial intelligence and GenAI tools.', 'A6.A.16.c.29444'), ('Implement machine learning and big data solutions to impact all areas of the business.', 'A6.J.2.p.24269'), ('Ability to creatively and quickly solve complex problems.', 'A6.B.0.l.18369'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Design, develop, and deploy AI and machine learning models and algorithms for various applications.', 'A6.J.4.d.29855'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Design and implement AI-powered products and solutions, including evaluation pipelines and orchestration approaches.', 'A6.J.4.d.29250'), ('Design and implement evaluation frameworks and metrics for agentic AI systems.', 'A6.J.4.d.29858'), ('Continuously improve and refine AI models and algorithms based on real-world data and performance feedback.', 'A6.J.10.d.25935'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Expert in state-of-the-art methodologies and technologies in AI/ML subdomains, including computer vision and natural language processing, to solve complex business problems in diverse applications such as healthcare and autonomous systems.', 'A6.A.16.a.28962'), ('Evaluate and integrate emerging AI technologies and tools to enhance platform capabilities and solve complex problems.', 'A6.J.0.m.27726'), ('Integrate AI services and algorithms with advanced data solutions and enterprise infrastructure.', 'A6.J.2.g.29674'), ('Develop and implement scalable machine learning models and platform strategies, with a focus on explainable AI and ML pipelines.', 'A6.J.13.a.27405'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('Demonstrate familiarity with TensorFlow and PyTorch.', 'A6.A.22.e.29693'), ('Analyze data and build and deploy machine learning models within cloud infrastructures such as AWS, Azure, and GCP.', 'A6.J.11.j.29688'), ('Experience in applying machine learning techniques and algorithms, including TensorFlow, to solve user and programmatic problems.', 'A6.J.14.d.29630'), ('Research and develop state-of-the-art machine learning algorithms for camera imaging and multimedia applications.', 'A6.J.2.m.28114')]</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -7477,25 +7477,25 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
       </c>
       <c r="T43" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="U43" t="n">
         <v>0.719</v>
       </c>
       <c r="V43" t="n">
-        <v>0.721</v>
+        <v>0.71</v>
       </c>
       <c r="W43" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="X43" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>[('18974', 'Estimate time and materials needed to complete projects.'), ('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('18974', 'Estimate time and materials needed to complete projects.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('20327', 'Improve search-related activities through ongoing analysis, experimentation, or optimization tests, using A/B or multivariate methods.'), ('19637', 'Research computerized automotive applications, such as telemetrics, intelligent transportation systems, artificial intelligence, or automatic control.'), ('7378', 'Collaborate with others in the organization to ensure successful implementation of chosen problem solutions.')]</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Design, develop, and implement advanced AI and ML models and algorithms to solve complex business problems.', 'A6.J.7.g.27605'), ('Understand and apply machine learning algorithms, including supervised, unsupervised, reinforcement learning, and natural language processing techniques.', 'A6.A.16.b.29696'), ('Familiarity with knowledge graphs, graph databases, and related algorithms for organizing and analyzing complex data.', 'A6.B.5.c.20195'), ('Apply natural language processing (NLP) techniques for tasks such as sentiment analysis, text classification, entity recognition, and topic modeling to analyze and interpret textual data.', 'A6.G.0.n.27966'), ('Develop and maintain analytical and semantic models for language processing.', 'A6.J.6.b.28881'), ('Demonstrate proficiency in search algorithms and their evaluation metrics for information retrieval, as well as understanding search engine functions including crawling, indexing, and ranking processes.', 'A6.K.3.b.15378'), ('Awareness of ethical considerations and regulatory compliance related to data privacy, bias detection, and responsible AI usage in data science and machine learning.', 'A6.G.2.k.28414'), ('Expertise in Responsible AI practices, governance, and technical solutions, ensuring transparency and safety in AI innovations.', 'A6.G.2.g.28708'), ('Develop and deploy AI and ML algorithms and technologies for various applications, including intelligent agents, healthcare, and generative AI solutions.', 'A6.J.2.h.29605'), ('Develop and apply expertise in artificial intelligence and machine learning algorithms.', 'A6.J.4.h.29758')]</t>
+          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Strong understanding of machine learning concepts, including algorithms, natural language processing, deep learning, and their applications in various contexts such as code generation and information retrieval.', 'A6.A.16.a.29375'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Design, develop, and implement advanced AI and ML models and algorithms to solve complex business problems.', 'A6.J.7.g.27605'), ('Understand and apply machine learning algorithms, including supervised, unsupervised, reinforcement learning, and natural language processing techniques.', 'A6.A.16.b.29696'), ('Familiarity with knowledge graphs, graph databases, and related algorithms for organizing and analyzing complex data.', 'A6.B.5.c.20195'), ('Apply natural language processing (NLP) techniques for tasks such as sentiment analysis, text classification, entity recognition, and topic modeling to analyze and interpret textual data.', 'A6.G.0.n.27966'), ('Develop and maintain analytical and semantic models for language processing.', 'A6.J.6.b.28881'), ('Demonstrate proficiency in search algorithms and their evaluation metrics for information retrieval, as well as understanding search engine functions including crawling, indexing, and ranking processes.', 'A6.K.3.b.15378'), ('Awareness of ethical considerations and regulatory compliance related to data privacy, bias detection, and responsible AI usage in data science and machine learning.', 'A6.G.2.k.28414'), ('Expertise in Responsible AI practices, governance, and technical solutions, ensuring transparency and safety in AI innovations.', 'A6.G.2.g.28708'), ('Develop and deploy AI and ML algorithms and technologies for various applications, including intelligent agents, healthcare, and generative AI solutions.', 'A6.J.2.h.29605'), ('Develop and apply expertise in artificial intelligence and machine learning algorithms.', 'A6.J.4.h.29758'), ('Strong interpersonal and communication skills to effectively explain machine learning concepts and foster collaboration across technical and non-technical teams.', 'A6.J.3.c.20294')]</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -7676,25 +7676,25 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
       </c>
       <c r="T44" t="n">
-        <v>0.643</v>
+        <v>0.64</v>
       </c>
       <c r="U44" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.675</v>
       </c>
       <c r="V44" t="n">
-        <v>0.643</v>
+        <v>0.64</v>
       </c>
       <c r="W44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X44" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>[('16787', 'Develop data models and databases.')]</t>
+          <t>[('21823', 'Analyze, manipulate, or process large sets of data using statistical software.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16787', 'Develop data models and databases.'), ('18961', 'Coordinate network or design activities with designers of associated networks.')]</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>[('Work with Python and its machine learning libraries and frameworks for data processing and orchestration.', 'A6.B.8.a.27410'), ('Implement advanced data analysis and data visualization methods using Python and pandas.', 'A6.B.8.l.25665'), ('Utilize data visualization tools and libraries such as Matplotlib, Seaborn, Plotly, and GGplot.', 'A6.B.8.a.15438'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Proficient in performing exploratory data analysis (EDA).', 'A6.A.14.ak.29395'), ('Knowledge of supervised, unsupervised, and deep learning techniques, including their real-world applications, advantages, and drawbacks.', 'A6.A.16.b.27805'), ('Identify and engineer relevant features from raw data to enhance the performance and accuracy of machine learning models.', 'A6.J.13.h.27975'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Develop and deploy machine learning models and algorithms using Python or R.', 'A6.J.3.b.29653'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Apply natural language processing (NLP) techniques for tasks such as sentiment analysis, text classification, entity recognition, and topic modeling to analyze and interpret textual data.', 'A6.G.0.n.27966'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Develop and implement computer vision algorithms for object detection, feature tracking, and image processing using relevant hardware and software technologies.', 'A6.G.0.g.29612')]</t>
+          <t>[('Work with Python and its machine learning libraries and frameworks for data processing and orchestration.', 'A6.B.8.a.27410'), ('Utilize Python and its scientific libraries for hardware programming and data analysis.', 'A6.B.8.a.26156'), ('Develop and maintain applications using Python and other scripting languages in a development environment.', 'A6.K.0.b.18316'), ('Implement advanced data analysis and data visualization methods using Python and pandas.', 'A6.B.8.l.25665'), ('Use Python and libraries like Pandas and NumPy for data manipulation and automation.', 'A6.B.8.u.26549'), ('Utilize data visualization tools and libraries such as Matplotlib, Seaborn, Plotly, and GGplot.', 'A6.B.8.a.15438'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Proficient in performing exploratory data analysis (EDA).', 'A6.A.14.ak.29395'), ('Knowledge of supervised, unsupervised, and deep learning techniques, including their real-world applications, advantages, and drawbacks.', 'A6.A.16.b.27805'), ('Identify and engineer relevant features from raw data to enhance the performance and accuracy of machine learning models.', 'A6.J.13.h.27975'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Perform dimensional data modeling and set up dimensional/tabular data models.', 'A6.B.2.o.29654'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Develop and deploy machine learning models and algorithms using Python or R.', 'A6.J.3.b.29653'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Apply natural language processing (NLP) techniques for tasks such as sentiment analysis, text classification, entity recognition, and topic modeling to analyze and interpret textual data.', 'A6.G.0.n.27966'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Develop and implement computer vision algorithms for object detection, feature tracking, and image processing using relevant hardware and software technologies.', 'A6.G.0.g.29612')]</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7984,25 +7984,25 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S45" t="n">
         <v>34</v>
       </c>
       <c r="T45" t="n">
-        <v>0.673</v>
+        <v>0.654</v>
       </c>
       <c r="U45" t="n">
         <v>0.745</v>
       </c>
       <c r="V45" t="n">
-        <v>0.706</v>
+        <v>0.708</v>
       </c>
       <c r="W45" t="n">
         <v>5</v>
       </c>
       <c r="X45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>[('solve problems', 'T2.3'), ('making models', 'S6.6')]</t>
+          <t>[('solving problems', 'S1.9'), ('making models', 'S6.6')]</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Develop and implement machine learning algorithms, including supervised, unsupervised, and reinforcement learning.', 'A6.J.11.h.29852'), ('Knowledge and application of machine learning techniques, algorithms, and their implementation across various fields.', 'A6.A.16.a.29819'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Expertise in Responsible AI practices, governance, and technical solutions, ensuring transparency and safety in AI innovations.', 'A6.G.2.g.28708'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Invent and develop AI algorithms and neural models for program generation and problem-solving on large-scale hardware systems.', 'A6.J.11.b.27446'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Develop and implement machine learning algorithms, including supervised, unsupervised, and reinforcement learning.', 'A6.J.11.h.29852'), ('Knowledge and application of machine learning techniques, algorithms, and their implementation across various fields.', 'A6.A.16.a.29819'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Expertise in Responsible AI practices, governance, and technical solutions, ensuring transparency and safety in AI innovations.', 'A6.G.2.g.28708'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Understand and apply knowledge of artificial intelligence and GenAI tools.', 'A6.A.16.c.29444')]</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -8116,25 +8116,25 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
       </c>
       <c r="T46" t="n">
-        <v>0.761</v>
+        <v>0.754</v>
       </c>
       <c r="U46" t="n">
-        <v>0.792</v>
+        <v>0.769</v>
       </c>
       <c r="V46" t="n">
-        <v>0.761</v>
+        <v>0.754</v>
       </c>
       <c r="W46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X46" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -8262,17 +8262,17 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('A strong grasp of algorithms, data structures, software design principles, design patterns, and object-oriented programming concepts for efficient, scalable data processing and problem-solving.', 'A6.A.9.a.22140'), ('Understand and apply search engine algorithms and ranking factors to enhance organic search results.', 'A6.E.5.l.14614'), ('Possess an in-depth understanding of search/ranking, recommender systems, graph techniques, and advanced methodologies.', 'A6.A.16.b.23049'), ('Possess expert knowledge of machine learning algorithms and techniques.', 'A6.A.16.b.29834')]</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -8281,25 +8281,25 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>0.763</v>
+        <v>0.573</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="V47" t="n">
-        <v>0.763</v>
+        <v>0.584</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>[('14663', 'Evaluate or recommend software for testing or bug tracking.')]</t>
+          <t>[('16424', 'Develop or implement operating methods or procedures.'), ('7386', 'Specify manipulative or computational methods to be applied to models.'), ('16515', 'Write algorithms or programming code for ad hoc robotic applications.'), ('16122', 'Select methods, techniques, or criteria for data warehousing evaluative procedures.'), ('14663', 'Evaluate or recommend software for testing or bug tracking.'), ('7377', 'Formulate mathematical or simulation models of problems, relating constants and variables, restrictions, alternatives, conflicting objectives, and their numerical parameters.'), ('11967', 'Modify existing programs to enhance efficiency.'), ('21317', 'Examine, evaluate, or process loan applications.')]</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>[('Develop and implement advanced machine learning and generative AI techniques in enterprise applications.', 'A6.J.0.b.29439'), ('Investigate new technologies, methodologies, and data sources for potential applications and algorithm development.', 'A6.J.2.q.23085'), ('Manage and improve existing codebases and algorithms.', 'A6.F.2.h.24466')]</t>
+          <t>[('Develop and implement advanced machine learning and generative AI techniques in enterprise applications.', 'A6.J.0.b.29439'), ('Design and create logical and physical databases using relational database principles.', 'A6.E.3.f.18280'), ('Knowledge of project management principles, processes, techniques, and scheduling.', 'A6.L.1.j.13532'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Investigate new technologies, methodologies, and data sources for potential applications and algorithm development.', 'A6.J.2.q.23085'), ('Ability to develop machine learning and artificial intelligence techniques and algorithms to solve complex business problems using both supervised and unsupervised methodologies.', 'A6.J.6.i.26996'), ('Manage and improve existing codebases and algorithms.', 'A6.F.2.h.24466'), ('Develop, implement, and validate algorithms for various applications, including customer-facing solutions, time-series data, and biological analysis.', 'A6.G.0.e.24341')]</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -8401,25 +8401,25 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
       </c>
       <c r="T48" t="n">
-        <v>0.595</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="U48" t="n">
-        <v>0.615</v>
+        <v>0.662</v>
       </c>
       <c r="V48" t="n">
-        <v>0.595</v>
+        <v>0.596</v>
       </c>
       <c r="W48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16577', 'Program complex robotic systems, such as vision systems.'), ('9261', 'Develop designs using specialized computer software.')]</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>[('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Advance AI techniques in computer vision, robotics, and natural language processing, including contributions to open source libraries and frameworks.', 'A6.J.0.j.28641'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Design machine learning systems and algorithms to generate accurate predictions.', 'A6.J.2.h.29884'), ('Design, develop, and deploy AI and machine learning models and algorithms for various applications.', 'A6.J.4.d.29855')]</t>
+          <t>[('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Perform data exploration and analysis using machine learning algorithms, linear algebra, probability theory, statistics, and optimization theory.', 'A6.J.1.k.26876'), ('Advance AI techniques in computer vision, robotics, and natural language processing, including contributions to open source libraries and frameworks.', 'A6.J.0.j.28641'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Design machine learning systems and algorithms to generate accurate predictions.', 'A6.J.2.h.29884'), ('Develop and implement robotic algorithms for navigation, perception, planning, and sensor processing.', 'A6.G.0.z.29153'), ('Design, develop, and deploy AI and machine learning models and algorithms for various applications.', 'A6.J.4.d.29855'), ('Generate software design artifacts and implement software design and development, including hardware interface design and validation of software designs.', 'A6.G.0.c.19111')]</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -8539,25 +8539,25 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S49" t="n">
         <v>13</v>
       </c>
       <c r="T49" t="n">
-        <v>0.745</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="U49" t="n">
-        <v>0.76</v>
+        <v>0.716</v>
       </c>
       <c r="V49" t="n">
-        <v>0.745</v>
+        <v>0.712</v>
       </c>
       <c r="W49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>[('21676', 'Store, retrieve, and manipulate data for analysis of system capabilities and requirements.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('7380', 'Perform validation and testing of models to ensure adequacy, and reformulate models, as necessary.'), ('14623', 'Analyze problems to develop solutions involving computer hardware and software.'), ('22232', 'Collect information and make judgments through observation, interviews, and review of documents.'), ('21462', 'Assign duties or responsibilities to project personnel.'), ('9695', 'Write technical documentation for products.')]</t>
+          <t>[('6575', 'Instruct through lectures, discussions, and demonstrations in one or more subjects, such as English, mathematics, or social studies.'), ('1740', 'Render design ideas in form of paste-ups or drawings.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.'), ('11021', 'Serve as liaisons between directors, actors, and agents.'), ('20879', 'Attend lectures given by the supervising instructor.'), ('16955', 'Train other analysts to perform laboratory procedures and assays.'), ('16257', 'Develop or implement data analysis algorithms.'), ('21676', 'Store, retrieve, and manipulate data for analysis of system capabilities and requirements.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('7380', 'Perform validation and testing of models to ensure adequacy, and reformulate models, as necessary.'), ('21128', 'Schedule courses.'), ('16126', 'Develop and implement data extraction procedures from other systems, such as administration, billing, or claims.'), ('21050', 'Train users on the use and function of computer programs.'), ('14623', 'Analyze problems to develop solutions involving computer hardware and software.'), ('22232', 'Collect information and make judgments through observation, interviews, and review of documents.'), ('21462', 'Assign duties or responsibilities to project personnel.'), ('14666', 'Communicate with staff or clients to understand specific system requirements.'), ('9695', 'Write technical documentation for products.'), ('15948', 'Maintain and update organization information technology applications and network systems blueprints.')]</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>[('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Combines machine learning, software development, and engineering expertise, particularly in physics, mechanical, electrical, or materials engineering, to innovate and implement AI solutions.', 'A6.A.16.a.24897'), ('Apply a range of statistical and modeling techniques including hypothesis testing, dimensionality reduction, supervised learning, forecasting, and unsupervised clustering.', 'A6.C.4.p.24609'), ('Analyze and process large, complex datasets using data science techniques and tools.', 'A6.D.0.e.29400'), ('Analyze data to identify trends and discrepancies across various activities and reports.', 'A6.C.4.w.27952'), ('Develop and apply machine learning algorithms for predictive modeling, including techniques such as classification, clustering, and dimensionality reduction.', 'A6.J.11.g.29705'), ('Build and apply regression, decision tree, and clustering models for data analysis.', 'A6.J.14.a.28626'), ('Ability to select appropriate algorithms, design model architecture, train and validate models, and evaluate their performance for deployment in production environments.', 'A6.F.6.g.21569'), ('Ability to develop and implement predictive models, as well as identify and score classification approaches.', 'A6.J.6.g.26510'), ('Use Python libraries such as pandas, numpy, and scikit-learn for data manipulation and analysis.', 'A6.B.8.u.22868'), ('Engage in coursework or projects related to machine learning, data mining, or artificial intelligence.', 'A6.A.16.a.29014'), ('Develop and integrate applications utilizing cloud data science tools for data analysis and software integration.', 'A6.F.4.b.22015'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Possess knowledge of machine learning and artificial intelligence concepts and technologies.', 'A6.A.16.a.29660'), ('Ability to apply best practices for artificial intelligence and machine learning.', 'A6.A.16.c.29427'), ('Strong computer science fundamentals coupled with problem-solving and analytical skills.', 'A6.B.0.t.27163'), ('Ability to research, evaluate, and implement innovative machine learning methods and technologies to enhance existing infrastructure and workflows.', 'A6.J.7.i.26803'), ('Design and implement data models and integrations for structured and unstructured data.', 'A6.G.0.j.27803'), ('Ability to collect, organize, analyze, and interpret various types of data to generate actionable insights and reports.', 'A6.D.0.s.23160'), ('Ability to quickly learn and adapt to new technologies, tools, systems, and processes.', 'A6.H.0.a.15479')]</t>
+          <t>[('Possesses intermediate to advanced knowledge in computational modeling, data science, and computational intelligence, along with experience in teaching related courses.', 'A6.A.11.d.21411'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Ability to develop advanced intelligent agent-based systems that autonomously manage complex goals and optimize real-time performance to enhance user experience and business promises.', 'A6.J.13.d.28921'), ('Develop and evaluate AI systems for robotics and automation in fulfillment processes.', 'A6.F.7.e.26643'), ('Combines machine learning, software development, and engineering expertise, particularly in physics, mechanical, electrical, or materials engineering, to innovate and implement AI solutions.', 'A6.A.16.a.24897'), ('Ability to work independently and accurately within defined limits, constraints, and deadlines.', 'A6.H.7.e.14094'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Apply a range of statistical and modeling techniques including hypothesis testing, dimensionality reduction, supervised learning, forecasting, and unsupervised clustering.', 'A6.C.4.p.24609'), ('Analyze and process large, complex datasets using data science techniques and tools.', 'A6.D.0.e.29400'), ('Analyze data to identify trends and discrepancies across various activities and reports.', 'A6.C.4.w.27952'), ('Develop and apply machine learning algorithms for predictive modeling, including techniques such as classification, clustering, and dimensionality reduction.', 'A6.J.11.g.29705'), ('Build and apply regression, decision tree, and clustering models for data analysis.', 'A6.J.14.a.28626'), ('Ability to select appropriate algorithms, design model architecture, train and validate models, and evaluate their performance for deployment in production environments.', 'A6.F.6.g.21569'), ('Analyze existing data structures and apply data modeling and normalization techniques.', 'A6.B.7.c.29464'), ('Ability to develop and implement predictive models, as well as identify and score classification approaches.', 'A6.J.6.g.26510'), ('Use Python libraries such as pandas, numpy, and scikit-learn for data manipulation and analysis.', 'A6.B.8.u.22868'), ('Engage in coursework or projects related to machine learning, data mining, or artificial intelligence.', 'A6.A.16.a.29014'), ('Develop and integrate applications utilizing cloud data science tools for data analysis and software integration.', 'A6.F.4.b.22015'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Possess knowledge of machine learning and artificial intelligence concepts and technologies.', 'A6.A.16.a.29660'), ('Design, develop, and deploy AI and machine learning models and algorithms for various applications.', 'A6.J.4.d.29855'), ('Ability to apply best practices for artificial intelligence and machine learning.', 'A6.A.16.c.29427'), ('Strong computer science fundamentals coupled with problem-solving and analytical skills.', 'A6.B.0.t.27163'), ('Ability to research, evaluate, and implement innovative machine learning methods and technologies to enhance existing infrastructure and workflows.', 'A6.J.7.i.26803'), ('Design and implement data models and integrations for structured and unstructured data.', 'A6.G.0.j.27803'), ('Ability to collect, organize, analyze, and interpret various types of data to generate actionable insights and reports.', 'A6.D.0.s.23160'), ('Possesses knowledge in learning and development processes, demonstrating intellectual curiosity and the ability to independently seek out and engage with new information.', 'A6.H.7.c.13131'), ('Ability to quickly learn and adapt to new technologies, tools, systems, and processes.', 'A6.H.0.a.15479'), ('Ability to work with cutting-edge technologies in dynamic and collaborative environments.', 'A6.H.6.c.16499')]</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -8799,25 +8799,25 @@
         </is>
       </c>
       <c r="R50" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="S50" t="n">
         <v>14</v>
       </c>
       <c r="T50" t="n">
-        <v>0.624</v>
+        <v>0.601</v>
       </c>
       <c r="U50" t="n">
-        <v>0.681</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="V50" t="n">
-        <v>0.644</v>
+        <v>0.618</v>
       </c>
       <c r="W50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X50" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('7021', 'Use telephone to deliver verbal messages.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.'), ('7367', 'Apply mathematical theories and techniques to the solution of practical problems in business, engineering, the sciences, or other fields.')]</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>[('Stay up to date with the latest research and advancements in machine learning, data science, and AI to improve methodologies and drive innovation.', 'A6.J.2.s.27471'), ('Develop and apply expertise in artificial intelligence and machine learning algorithms.', 'A6.J.4.h.29758'), ('Apply advanced machine learning techniques, including deep learning, reinforcement learning, and optimization algorithms.', 'A6.J.1.d.29484'), ('Proficient in Natural Language Processing and Computer Vision techniques.', 'A6.A.16.c.29866'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Deep understanding of machine learning algorithms and concepts, including supervised, unsupervised, semi-supervised, and reinforcement learning techniques.', 'A6.A.16.b.29090'), ('Develop and enhance conversational AI solutions such as chatbots and virtual assistants, utilizing natural language processing and digital messaging strategies.', 'A6.J.2.h.29414'), ('Develop and implement object detection, classification, and segmentation algorithms for image and video analysis.', 'A6.G.0.g.28401'), ('Possesses creativity and autonomy with a genuine passion for technology and developing solutions for autonomous driving.', 'A6.F.5.g.24819'), ('Design, analyze, and implement guidance, navigation, and control algorithms for autonomous systems to meet stability, performance, and mission objectives.', 'A6.J.5.e.28123'), ('Research and develop advanced techniques for image and video generation using models such as diffusion models and generative adversarial networks (GANs) to enhance realism, controllability, and diversity in synthetic images.', 'A6.J.3.d.25683'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Develops advanced machine learning algorithms and techniques by leveraging the latest trends in artificial intelligence to train models on new data sets.', 'A6.J.11.h.28883'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Practical experience in solving complex real-world problems using techniques such as deep learning, AI, robotics, graphics, computer vision, and cloud computing.', 'A6.D.1.e.23146')]</t>
+          <t>[('Stay up to date with the latest research and advancements in machine learning, data science, and AI to improve methodologies and drive innovation.', 'A6.J.2.s.27471'), ('Develop and apply expertise in artificial intelligence and machine learning algorithms.', 'A6.J.4.h.29758'), ('Apply advanced machine learning techniques, including deep learning, reinforcement learning, and optimization algorithms.', 'A6.J.1.d.29484'), ('Proficient in Natural Language Processing and Computer Vision techniques.', 'A6.A.16.c.29866'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Deep understanding of machine learning algorithms and concepts, including supervised, unsupervised, semi-supervised, and reinforcement learning techniques.', 'A6.A.16.b.29090'), ('Develop, implement, and optimize speech recognition and natural language processing systems, including handling voice command recognition, speech-to-text functionality, and related algorithms.', 'A6.J.11.e.28355'), ('Develop and enhance conversational AI solutions such as chatbots and virtual assistants, utilizing natural language processing and digital messaging strategies.', 'A6.J.2.h.29414'), ('Develop and implement object detection, classification, and segmentation algorithms for image and video analysis.', 'A6.G.0.g.28401'), ('Possesses creativity and autonomy with a genuine passion for technology and developing solutions for autonomous driving.', 'A6.F.5.g.24819'), ('Design, analyze, and implement guidance, navigation, and control algorithms for autonomous systems to meet stability, performance, and mission objectives.', 'A6.J.5.e.28123'), ('Research and develop advanced techniques for image and video generation using models such as diffusion models and generative adversarial networks (GANs) to enhance realism, controllability, and diversity in synthetic images.', 'A6.J.3.d.25683'), ('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Develops advanced machine learning algorithms and techniques by leveraging the latest trends in artificial intelligence to train models on new data sets.', 'A6.J.11.h.28883'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Practical experience in solving complex real-world problems using techniques such as deep learning, AI, robotics, graphics, computer vision, and cloud computing.', 'A6.D.1.e.23146'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719')]</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -9094,25 +9094,25 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S52" t="n">
         <v>23</v>
       </c>
       <c r="T52" t="n">
-        <v>0.676</v>
+        <v>0.678</v>
       </c>
       <c r="U52" t="n">
-        <v>0.66</v>
+        <v>0.674</v>
       </c>
       <c r="V52" t="n">
-        <v>0.676</v>
+        <v>0.678</v>
       </c>
       <c r="W52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X52" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>[('8292', 'Discuss the design with the client.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('22468', "Observe students' performance, and record relevant data to assess progress.")]</t>
+          <t>[('22449', 'Present and make recommendations regarding course design, technology, and instruction delivery options.'), ('5453', 'Counsel children and families to help solve conflicts and problems in learning and adjustment.'), ('20089', 'Develop and teach online courses.'), ('6582', 'Assign lessons and correct homework.'), ('22094', 'Draw plans for developing jigs, fixtures, instruments, or other devices.'), ('14623', 'Analyze problems to develop solutions involving computer hardware and software.'), ('8671', 'Prepare students for further development by encouraging them to explore learning opportunities and to persevere with challenging tasks.'), ('11826', 'Demonstrate equipment functions and features to machine operators.'), ('19245', 'Conduct visual field tests to measure field of vision.'), ('20488', 'Create three-dimensional or interactive representations of designs, using computer-assisted design software.'), ('8292', 'Discuss the design with the client.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('7993', 'Talk to or interact with animals to familiarize them to human voices or contact.'), ('8955', 'Identify relationships and trends in data, as well as any factors that could affect the results of research.'), ('22468', "Observe students' performance, and record relevant data to assess progress."), ('288', 'Present final layouts to clients for approval.'), ('2435', 'Discuss use and features of various parts, based on knowledge of machines or equipment.'), ('8947', 'Support the development of training materials and technical manuals.'), ('16790', 'Create novel computational approaches and analytical tools as required by research goals.'), ('22389', "Answer students' questions.")]</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Engages in projects utilizing advanced computer science techniques developed by skilled software developers and research scientists to promote accessible and high-quality computer science education.', 'A6.A.3.a.26976'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Research and develop speech and audio algorithms using machine learning and signal processing.', 'A6.J.2.m.28535'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Configure and maintain chatbot functionality for various business applications.', 'A6.F.2.a.29411'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Support the implementation, analysis, and development of machine learning models and artificial intelligence tools.', 'A6.J.6.b.29043'), ('Strong academic performance and intellectual creativity in Computer Science, STEM disciplines, and relevant technical coursework.', 'A6.A.3.c.18633')]</t>
+          <t>[('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Design and develop AI algorithms and solutions for various applications, including conversational systems, intelligent agents, and generative AI tools.', 'A6.J.4.d.29651'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Engages in projects utilizing advanced computer science techniques developed by skilled software developers and research scientists to promote accessible and high-quality computer science education.', 'A6.A.3.a.26976'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Configure, train, and optimize AI models, including chatbots and autonomous agents, with a focus on prompt engineering and operationalization.', 'A6.J.11.b.28862'), ('Build and maintain predictive models and software modules using machine learning techniques in areas such as computer vision, natural language processing, and deep learning.', 'A6.J.11.d.29044'), ('Research and develop speech and audio algorithms using machine learning and signal processing.', 'A6.J.2.m.28535'), ('Ability to apply design and system thinking, showcasing innovative, creative, and abstract thinking skills.', 'A6.B.0.g.15082'), ('Demonstrate familiarity with agentic AI frameworks, concepts, and orchestration tools for building AI agent-based applications.', 'A6.A.15.l.29608'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Inform infrastructure decisions using your understanding of machine learning techniques and issues, including model selection, data choice, feature selection, training, hyperparameter tuning, and validation.', 'A6.J.11.g.26908'), ('Ability to share and apply knowledge, experience, and skills effectively.', 'A6.A.4.b.13239'), ('Develop and implement chatbots and conversational interfaces with a focus on user engagement and design principles.', 'A6.J.5.c.27699'), ('Contribute to study design, data collection methods, and analysis for research projects related to AI adoption and instructional design in K-12 classrooms.', 'A6.B.2.t.21359'), ('Configure and maintain chatbot functionality for various business applications.', 'A6.F.2.a.29411'), ('Understanding data is essential for effective data science.', 'A6.D.0.w.29780'), ('Ability to stay informed about and integrate emerging trends in AI, machine learning, data science, and analytics tools into product improvements and business applications.', 'A6.J.2.s.22984'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Knowledge of data governance, security, privacy, and ethical practices in AI development, including addressing issues like data poisoning and model theft.', 'A6.G.2.k.27697'), ('Support the implementation, analysis, and development of machine learning models and artificial intelligence tools.', 'A6.J.6.b.29043'), ('Strong academic performance and intellectual creativity in Computer Science, STEM disciplines, and relevant technical coursework.', 'A6.A.3.c.18633')]</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -9295,25 +9295,25 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="S53" t="n">
         <v>6</v>
       </c>
       <c r="T53" t="n">
-        <v>0.678</v>
+        <v>0.645</v>
       </c>
       <c r="U53" t="n">
-        <v>0.667</v>
+        <v>0.696</v>
       </c>
       <c r="V53" t="n">
-        <v>0.71</v>
+        <v>0.675</v>
       </c>
       <c r="W53" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="X53" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16395', 'Analyze complex systems to determine potential for further development, production, interoperability, compatibility, or usefulness in a particular area, such as aviation.'), ('14623', 'Analyze problems to develop solutions involving computer hardware and software.')]</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>[('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Invent and develop AI algorithms and neural models for program generation and problem-solving on large-scale hardware systems.', 'A6.J.11.b.27446'), ('Develop and apply machine learning and artificial intelligence techniques in robotics and computer vision.', 'A6.J.12.d.28754'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868')]</t>
+          <t>[('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Design, develop, and implement knowledge-based systems, including ontologies, taxonomies, and knowledge graphs to support data integration and semantic search.', 'A6.G.0.j.27688'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Invent and develop AI algorithms and neural models for program generation and problem-solving on large-scale hardware systems.', 'A6.J.11.b.27446'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Develop and apply machine learning and artificial intelligence techniques in robotics and computer vision.', 'A6.J.12.d.28754'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Ability to collaborate with multidisciplinary teams to design, develop, and implement AI algorithms and models for various applications.', 'A6.J.0.n.27661')]</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -9441,25 +9441,25 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="S54" t="n">
         <v>14</v>
       </c>
       <c r="T54" t="n">
-        <v>0.717</v>
+        <v>0.709</v>
       </c>
       <c r="U54" t="n">
-        <v>0.651</v>
+        <v>0.673</v>
       </c>
       <c r="V54" t="n">
-        <v>0.696</v>
+        <v>0.703</v>
       </c>
       <c r="W54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X54" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Develop and apply machine learning and statistical modeling data analysis tools and techniques.', 'A6.C.4.p.27333'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Apply machine learning techniques including classification, clustering, regressions, and deep learning models.', 'A6.G.0.n.29857'), ('Monitor and analyze performance metrics of systems, identifying areas for improvement and implementing optimization strategies.', 'A6.E.5.k.17391')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Proficient in utilizing instructional technologies and educational media for training, assessment, and distance learning support.', 'A6.F.6.c.16230'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Develop and apply machine learning and statistical modeling data analysis tools and techniques.', 'A6.C.4.p.27333'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Apply machine learning techniques including classification, clustering, regressions, and deep learning models.', 'A6.G.0.n.29857'), ('Proficient in both supervised and unsupervised machine learning techniques, including model training, evaluation, feature engineering, and application to diverse datasets.', 'A6.J.11.j.29543'), ('Proven experience in developing and applying supervised, unsupervised, and semi-supervised machine learning techniques and algorithms, including regression, classification, and clustering, for data curation and real-world problem solving.', 'A6.J.11.j.28285'), ('Train large-scale machine learning models from scratch at web scale.', 'A6.G.0.f.29789'), ('Monitor and analyze performance metrics of systems, identifying areas for improvement and implementing optimization strategies.', 'A6.E.5.k.17391')]</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -9640,25 +9640,25 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S55" t="n">
         <v>14</v>
       </c>
       <c r="T55" t="n">
-        <v>0.742</v>
+        <v>0.713</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="V55" t="n">
-        <v>0.728</v>
+        <v>0.702</v>
       </c>
       <c r="W55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X55" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Familiarity with data structures, data modeling, and software architecture.', 'A6.B.5.c.27010')]</t>
+          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Applies mathematical, problem-solving, and coding skills to manage big data and extract valuable insights.', 'A6.G.6.a.28396'), ('Design and develop AI algorithms and solutions for various applications, including conversational systems, intelligent agents, and generative AI tools.', 'A6.J.4.d.29651'), ('Familiarity with data structures, data modeling, and software architecture.', 'A6.B.5.c.27010'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841')]</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -9859,25 +9859,25 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S57" t="n">
         <v>2</v>
       </c>
       <c r="T57" t="n">
-        <v>0.665</v>
+        <v>0.676</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="V57" t="n">
-        <v>0.722</v>
+        <v>0.707</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -9991,17 +9991,17 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Invent and develop AI algorithms and neural models for program generation and problem-solving on large-scale hardware systems.', 'A6.J.11.b.27446'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Ability to communicate complex and abstract ideas clearly and concisely, while providing solutions.', 'A6.H.2.d.14547'), ('Invent and develop AI algorithms and neural models for program generation and problem-solving on large-scale hardware systems.', 'A6.J.11.b.27446'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895')]</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -10010,13 +10010,13 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S58" t="n">
         <v>13</v>
       </c>
       <c r="T58" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.593</v>
       </c>
       <c r="U58" t="n">
         <v>0.621</v>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>[('6456', 'Integrate academic and vocational curricula so that students can obtain a variety of skills.'), ('7205', 'Plan or direct research, development, or production activities.')]</t>
+          <t>[('6781', 'Provide additional instruction in vocational areas.'), ('6456', 'Integrate academic and vocational curricula so that students can obtain a variety of skills.'), ('11052', 'Develop factors such as themes, plots, characterizations, psychological analyses, historical environments, action, and dialogue to create material.'), ('6491', "Meet with other professionals to discuss individual students' needs and progress."), ('7205', 'Plan or direct research, development, or production activities.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('23695', 'Plan and establish schedules.'), ('1010', 'Develop testing and evaluation procedures.')]</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Model and implement optimization algorithms for solving linear and non-linear optimization problems using mathematical optimization techniques.', 'A6.J.11.c.17766'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185'), ('Develop and implement artificial intelligence and machine learning techniques for various applications and data analyses.', 'A6.J.11.h.29491')]</t>
+          <t>[('Possesses knowledge in learning and development processes, demonstrating intellectual curiosity and the ability to independently seek out and engage with new information.', 'A6.H.7.c.13131'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and implement algorithms and data structures to solve problems using web technologies and object-oriented programming.', 'A6.G.0.e.18538'), ('Strong problem identification and problem-solving skills.', 'A6.B.0.y.15226'), ('Model and implement optimization algorithms for solving linear and non-linear optimization problems using mathematical optimization techniques.', 'A6.J.11.c.17766'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Develop and implement semantic technologies and ontologies for knowledge graphs and informatics workflows.', 'A6.E.0.j.25194'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185'), ('Ability to utilize and conduct problem-solving techniques effectively.', 'A6.B.0.f.14814'), ('Develop and implement artificial intelligence and machine learning techniques for various applications and data analyses.', 'A6.J.11.h.29491'), ('Model complex business and engineering problems using machine learning and feature engineering techniques.', 'A6.J.7.k.29518')]</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -10156,25 +10156,25 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
       </c>
       <c r="T59" t="n">
-        <v>0.674</v>
+        <v>0.545</v>
       </c>
       <c r="U59" t="n">
         <v>0.711</v>
       </c>
       <c r="V59" t="n">
-        <v>0.674</v>
+        <v>0.588</v>
       </c>
       <c r="W59" t="n">
         <v>1</v>
       </c>
       <c r="X59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('22467', 'Maintain computers in classrooms and laboratories, and assist students with hardware and software use.')]</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>[('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Develop and implement machine learning algorithms, including supervised, unsupervised, and reinforcement learning.', 'A6.J.11.h.29852'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895')]</t>
+          <t>[('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Develop and implement machine learning algorithms, including supervised, unsupervised, and reinforcement learning.', 'A6.J.11.h.29852'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Ability to teach a comprehensive curriculum in computer science, covering topics such as artificial intelligence, machine learning, programming, data science, and cybersecurity at various educational levels.', 'A6.A.3.i.24119'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('Configure, train, and optimize AI models, including chatbots and autonomous agents, with a focus on prompt engineering and operationalization.', 'A6.J.11.b.28862')]</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -10298,25 +10298,25 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S60" t="n">
         <v>6</v>
       </c>
       <c r="T60" t="n">
-        <v>0.727</v>
+        <v>0.719</v>
       </c>
       <c r="U60" t="n">
-        <v>0.735</v>
+        <v>0.749</v>
       </c>
       <c r="V60" t="n">
-        <v>0.727</v>
+        <v>0.719</v>
       </c>
       <c r="W60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X60" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17542', 'Predict future gang, organized crime, or terrorist activity, using analyses of intelligence data.'), ('20930', 'Input specifications into computers to assist with pattern design and pattern cutting.'), ('7386', 'Specify manipulative or computational methods to be applied to models.'), ('9327', 'Identify and resolve conflicts related to the meanings of words, concepts, practices, or behaviors.'), ('7207', 'Design or coordinate successive phases of problem analysis, solution proposals, or testing.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16257', 'Develop or implement data analysis algorithms.')]</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>[('Demonstrates excellent planning, organizational, analytical, communication, and problem-solving skills.', 'A6.H.7.h.11594'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Ability to utilize and conduct problem-solving techniques effectively.', 'A6.B.0.f.14814'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892')]</t>
+          <t>[('Demonstrates excellent planning, organizational, analytical, communication, and problem-solving skills.', 'A6.H.7.h.11594'), ('Ability to identify, evaluate, and refine methods, models, and algorithms for developing accurate and anticipatory intelligence analysis solutions.', 'A6.J.11.e.22676'), ('Apply computer science methods and techniques to store, manipulate, transform, or present information using computer systems.', 'A6.A.3.b.25374'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Apply conversational search and semantic search techniques, along with reinforcement learning and prompt engineering, to mitigate hallucination in algorithms.', 'A6.J.0.j.20547'), ('Ability to draw sound scientific conclusions and logical inferences based on data analysis.', 'A6.D.0.k.23435'), ('Ability to utilize and conduct problem-solving techniques effectively.', 'A6.B.0.f.14814'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Possess knowledge of AI concepts, including machine learning, deep learning, natural language processing, and computer vision.', 'A6.A.16.c.29475'), ('Ability to manipulate and analyze data using SQL or equivalent data manipulation languages.', 'A6.B.8.e.29037'), ('Possesses advanced knowledge of intelligence production, collection methodologies, operations, and the intelligence cycle, including security guidelines and analytical techniques.', 'A6.F.6.c.18239'), ('Develop and perform analysis of tracking and state estimation algorithms.', 'A6.G.0.e.23045'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Program and prototype algorithms using MATLAB, Python, and other engineering tools.', 'A6.B.8.q.26434'), ('Design and implement systems for data collection, storage, and analysis, ensuring data quality and integrity across various data types.', 'A6.C.9.f.27072')]</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -10538,25 +10538,25 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
       </c>
       <c r="T61" t="n">
-        <v>0.613</v>
+        <v>0.58</v>
       </c>
       <c r="U61" t="n">
-        <v>0.87</v>
+        <v>0.672</v>
       </c>
       <c r="V61" t="n">
-        <v>0.836</v>
+        <v>0.612</v>
       </c>
       <c r="W61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X61" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('8642', 'Measure and record the speed of vehicular traffic, using electrical timing devices or radar equipment.')]</t>
+          <t>[('8947', 'Support the development of training materials and technical manuals.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('5981', 'Incorporate experiential or site visit components into courses.'), ('22279', 'Participate in the evaluation of possible mining locations.'), ('21828', 'Create graphs, charts, or other visualizations to convey the results of data analysis using specialized software.'), ('7374', 'Develop new principles and new relationships between existing mathematical principles to advance mathematical science.'), ('20229', 'Coach senior executives and managers on leadership and performance.'), ('8954', 'Process large amounts of data for statistical modeling and graphic analysis, using computers.'), ('16111', 'Demonstrate database technical functionality, such as performance, security and reliability.'), ('21128', 'Schedule courses.'), ('21971', 'Train students to use drafting machines and to prepare schematic diagrams, block diagrams, control drawings, logic diagrams, integrated circuit drawings, or interconnection diagrams.'), ('8642', 'Measure and record the speed of vehicular traffic, using electrical timing devices or radar equipment.')]</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>[('Build, manage, and optimize AI-powered applications, including chatbots, agents, and generative AI models for various platforms.', 'A6.J.4.d.28660'), ('Integrate machine learning algorithms into business systems and analytical pipelines for enhanced decision-making and predictive analytics.', 'A6.J.11.e.24691'), ('Continuously improve and update skills in machine learning and artificial intelligence to enhance capabilities.', 'A6.A.16.c.26005'), ('Demonstrate experience with Machine Learning and Deep Learning concepts, algorithms, and models.', 'A6.A.16.a.29352'), ('Develop and implement machine learning and artificial intelligence solutions and algorithms.', 'A6.J.0.b.29816'), ('Proficient in machine learning (ML) and artificial intelligence (AI) concepts, including their application in data analytics, and capable of educating team members on these topics.', 'A6.J.6.b.29018'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Demonstrate proficiency in coding and software development in Python, with a strong focus on machine learning frameworks and libraries.', 'A6.B.8.g.23532'), ('Utilize Python for data analysis, manipulation, and modeling.', 'A6.B.8.a.29743'), ('Strong understanding of data modeling, visualization principles, and related techniques, including Power BI and Power Query.', 'A6.A.7.d.19356'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Complete coursework in statistics, data analysis, or econometrics.', 'A6.B.5.f.16462'), ('Strong understanding of machine learning concepts, algorithms, and workflows, including supervised/unsupervised learning, deep learning, reinforcement learning, and statistical modeling.', 'A6.J.3.c.29389'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Proficient in machine learning and AI techniques as a machine learning engineer.', 'A6.J.0.c.29386'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Familiarity with machine learning is an advantageous skill.', 'A6.J.11.h.29131'), ('Develop software in Python and execute machine learning experiments.', 'A6.J.3.b.29448'), ('Work with Python and its machine learning libraries and frameworks for data processing and orchestration.', 'A6.B.8.a.27410'), ('Experience with common machine learning techniques, including data pre-processing, training, and evaluation of classification and regression models.', 'A6.J.14.d.29005'), ('Utilize TensorFlow for applications in artificial intelligence, deep learning, or natural language processing.', 'A6.J.1.h.29891'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Develop and optimize deep neural network models and architectures for predictive applications.', 'A6.J.12.d.29199'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Knowledge of reinforcement learning algorithms and unsupervised learning techniques, including understanding of regularization, embeddings, loss functions, and optimization strategies.', 'A6.A.16.b.29272'), ('Demonstrate a solid understanding of SQL, relational and NoSQL databases, data modeling principles, and database management processes.', 'A6.A.14.f.18252'), ('Develop and implement machine learning models and workflows for deployment in production environments.', 'A6.J.13.k.28009')]</t>
+          <t>[('Build, manage, and optimize AI-powered applications, including chatbots, agents, and generative AI models for various platforms.', 'A6.J.4.d.28660'), ('Integrate machine learning algorithms into business systems and analytical pipelines for enhanced decision-making and predictive analytics.', 'A6.J.11.e.24691'), ('Continuously improve and update skills in machine learning and artificial intelligence to enhance capabilities.', 'A6.A.16.c.26005'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('Demonstrate experience with Machine Learning and Deep Learning concepts, algorithms, and models.', 'A6.A.16.a.29352'), ('Develop and implement machine learning and artificial intelligence solutions and algorithms.', 'A6.J.0.b.29816'), ('Proficient in machine learning (ML) and artificial intelligence (AI) concepts, including their application in data analytics, and capable of educating team members on these topics.', 'A6.J.6.b.29018'), ('Demonstrate familiarity with Python and relevant tools and libraries for data science and analytics.', 'A6.B.8.u.25776'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Demonstrate proficiency in coding and software development in Python, with a strong focus on machine learning frameworks and libraries.', 'A6.B.8.g.23532'), ('Demonstrate strong understanding of statistical modeling, data mining, and machine learning techniques.', 'A6.A.12.d.27138'), ('Utilize Python for data analysis, manipulation, and modeling.', 'A6.B.8.a.29743'), ('Strong understanding of data modeling, visualization principles, and related techniques, including Power BI and Power Query.', 'A6.A.7.d.19356'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Complete coursework in statistics, data analysis, or econometrics.', 'A6.B.5.f.16462'), ('Generate and process large amounts of data from sensors, onboard models, and control algorithms in real-time to create real-world machine usage information.', 'A6.G.0.z.19250'), ('Strong understanding of machine learning concepts, algorithms, and workflows, including supervised/unsupervised learning, deep learning, reinforcement learning, and statistical modeling.', 'A6.J.3.c.29389'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Proficient in machine learning and AI techniques as a machine learning engineer.', 'A6.J.0.c.29386'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Demonstrates mathematical aptitude in machine learning, computer vision, formal methods, and related advanced topics such as graph neural networks and causal discovery.', 'A6.A.16.c.24938'), ('Familiarity with machine learning is an advantageous skill.', 'A6.J.11.h.29131'), ('Use machine learning, deep learning, and neural networks to model data and solve problems.', 'A6.A.16.b.29445'), ('Develop software in Python and execute machine learning experiments.', 'A6.J.3.b.29448'), ('Work with Python and its machine learning libraries and frameworks for data processing and orchestration.', 'A6.B.8.a.27410'), ('Experience with common machine learning techniques, including data pre-processing, training, and evaluation of classification and regression models.', 'A6.J.14.d.29005'), ('Utilize TensorFlow for applications in artificial intelligence, deep learning, or natural language processing.', 'A6.J.1.h.29891'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Develop and optimize deep neural network models and architectures for predictive applications.', 'A6.J.12.d.29199'), ('Implement, train, and evaluate deep neural networks and their associated compute workloads.', 'A6.J.11.e.28239'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Design, develop, and implement large language models (LLMs) using advanced machine learning techniques and optimize their performance for various applications.', 'A6.J.11.e.29854'), ('Knowledge of reinforcement learning algorithms and unsupervised learning techniques, including understanding of regularization, embeddings, loss functions, and optimization strategies.', 'A6.A.16.b.29272'), ('Work with machine learning algorithms using SQL and Python, and employ frameworks such as TensorFlow and MLlib.', 'A6.J.11.a.27622'), ('Demonstrate a solid understanding of SQL, relational and NoSQL databases, data modeling principles, and database management processes.', 'A6.A.14.f.18252'), ('Develop and implement machine learning models and workflows for deployment in production environments.', 'A6.J.13.k.28009'), ('Design and implement AI algorithms and generative AI applications while collaborating with business teams to identify use cases and enhance workflows.', 'A6.J.4.d.27811'), ('Provide technical support and troubleshooting for chatbot solutions, while generating performance reports, training users, and continuously optimizing chatbot interactions and functionalities.', 'A6.J.4.d.26412'), ('Perform data cleaning and data pipeline engineering, analyze textual and numerical data, and deploy generative AI, natural language processing, and machine learning workflows using tools in Azure and AWS cloud environments.', 'A6.A.16.c.27758'), ('Build and optimize algorithms and models to enhance the marketplace impact and operational efficiency of autonomous vehicles.', 'A6.E.1.f.28214'), ('Develop and implement machine learning and AI models, including those for natural language processing and computer vision, to meet business requirements.', 'A6.J.4.h.28909')]</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -10774,25 +10774,25 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="S62" t="n">
         <v>18</v>
       </c>
       <c r="T62" t="n">
-        <v>0.673</v>
+        <v>0.661</v>
       </c>
       <c r="U62" t="n">
-        <v>0.781</v>
+        <v>0.712</v>
       </c>
       <c r="V62" t="n">
-        <v>0.701</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="W62" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="X62" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>[('20879', 'Attend lectures given by the supervising instructor.')]</t>
+          <t>[('14623', 'Analyze problems to develop solutions involving computer hardware and software.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('20879', 'Attend lectures given by the supervising instructor.'), ('11407', 'Select materials needed to complete work assignments.')]</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>[('Demonstrate familiarity with agentic AI frameworks, concepts, and orchestration tools for building AI agent-based applications.', 'A6.A.15.l.29608'), ('Research and develop state-of-the-art machine learning algorithms for camera imaging and multimedia applications.', 'A6.J.2.m.28114'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646')]</t>
+          <t>[('Demonstrate familiarity with agentic AI frameworks, concepts, and orchestration tools for building AI agent-based applications.', 'A6.A.15.l.29608'), ('Use machine learning, deep learning, and neural networks to model data and solve problems.', 'A6.A.16.b.29445'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Research and develop state-of-the-art machine learning algorithms for camera imaging and multimedia applications.', 'A6.J.2.m.28114'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Implement and apply Bayesian modeling techniques in multimodal data analysis, including feature selection and hierarchical Bayesian techniques.', 'A6.C.4.k.28775'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646')]</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -10940,25 +10940,25 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S63" t="n">
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>0.697</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="U63" t="n">
-        <v>0.697</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="V63" t="n">
-        <v>0.697</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="W63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X63" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -11055,17 +11055,17 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>[('22024', 'Assist engineers in developing, building, or testing prototypes or new products, processes, or procedures.')]</t>
+          <t>[('22024', 'Assist engineers in developing, building, or testing prototypes or new products, processes, or procedures.'), ('8840', 'Serve as liaisons between organizations, shareholders, and outside organizations.'), ('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>[('demonstrate technical abilities', 'T6.6'), ('driving vehicles', 'S8.2'), ('identify opportunities', 'T6.5'), ('analyse environmental data', 'S2.7')]</t>
+          <t>[('demonstrate technical abilities', 'T6.6'), ('driving vehicles', 'S8.2'), ('identifying opportunities', 'S4.1'), ('analyse environmental data', 'S2.7')]</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>[('Demonstrate familiarity with agentic AI frameworks, concepts, and orchestration tools for building AI agent-based applications.', 'A6.A.15.l.29608')]</t>
+          <t>[('Lead machine learning algorithm development and implement machine learning capabilities into production across various projects and therapeutic areas.', 'A6.J.11.g.24794'), ('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Demonstrate familiarity with agentic AI frameworks, concepts, and orchestration tools for building AI agent-based applications.', 'A6.A.15.l.29608'), ('Ability to evaluate and refine algorithms using relevant data.', 'A6.J.10.d.29188'), ('Implement and conduct statistical signal processing and data analysis.', 'A6.G.0.e.28029')]</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -11074,25 +11074,25 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
       </c>
       <c r="T64" t="n">
-        <v>0.725</v>
+        <v>0.648</v>
       </c>
       <c r="U64" t="n">
-        <v>0.725</v>
+        <v>0.642</v>
       </c>
       <c r="V64" t="n">
-        <v>0.725</v>
+        <v>0.648</v>
       </c>
       <c r="W64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>[('15997', 'Apply mathematical or statistical techniques to address practical issues in finance, such as derivative valuation, securities trading, risk management, or financial market regulation.')]</t>
+          <t>[('6468', 'Read books to entire classes or to small groups.'), ('15997', 'Apply mathematical or statistical techniques to address practical issues in finance, such as derivative valuation, securities trading, risk management, or financial market regulation.')]</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>[('Research, design, implement, and evaluate machine learning and deep learning algorithms to address various applications.', 'A6.J.6.b.29200'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('Develop and apply deep learning optimization and acceleration techniques.', 'A6.G.0.f.29603'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244')]</t>
+          <t>[('Research, design, implement, and evaluate machine learning and deep learning algorithms to address various applications.', 'A6.J.6.b.29200'), ('Create and maintain neural networks using proven technologies or develop new methods tailored to specific research needs.', 'A6.J.11.e.27928'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('Develop and apply deep learning optimization and acceleration techniques.', 'A6.G.0.f.29603'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Apply advanced statistical and predictive modeling techniques to build, maintain, and improve multiple real-time decision systems.', 'A6.C.11.d.27773')]</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -11227,25 +11227,25 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S65" t="n">
         <v>7</v>
       </c>
       <c r="T65" t="n">
-        <v>0.712</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="U65" t="n">
-        <v>0.708</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="V65" t="n">
-        <v>0.712</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="W65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Expertise in machine learning and deep learning techniques, including supervised and unsupervised learning algorithms such as regression, classification, clustering, and dimensionality reduction.', 'A6.J.11.j.29274'), ('Develop state-of-the-art algorithms and models for applications in computer vision, object recognition, and generative AI.', 'A6.J.11.b.29718'), ('Demonstrate an understanding of computer science fundamentals, including data structures, algorithms, and AI/machine learning concepts.', 'A6.A.9.e.26712'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Support the creation and training of autoencoder models and other neural methods using Pytorch.', 'A6.G.0.f.29784'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Implement and optimize Generative AI solutions, including prompt engineering, data modeling, and automation in various applications.', 'A6.J.2.h.29848'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Understand and apply knowledge of artificial intelligence and GenAI tools.', 'A6.A.16.c.29444'), ('Ability to develop algorithms and analyze programming problems to create solutions and automate processes.', 'A6.J.8.d.23623')]</t>
+          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Apply computer science methods and techniques to store, manipulate, transform, or present information using computer systems.', 'A6.A.3.b.25374'), ('Ability to fine-tune, optimize, and ensure the scalability and high performance of AI models and algorithms.', 'A6.J.2.m.28452'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Expertise in machine learning and deep learning techniques, including supervised and unsupervised learning algorithms such as regression, classification, clustering, and dimensionality reduction.', 'A6.J.11.j.29274'), ('Develop state-of-the-art algorithms and models for applications in computer vision, object recognition, and generative AI.', 'A6.J.11.b.29718'), ('Demonstrate an understanding of computer science fundamentals, including data structures, algorithms, and AI/machine learning concepts.', 'A6.A.9.e.26712'), ('Implement algorithms for data analysis and processing.', 'A6.J.8.f.29898'), ('Extensive experience in designing and developing machine learning and computer vision algorithms using the PyTorch framework in Python.', 'A6.J.7.b.28797'), ('Proficient in performing statistical analysis and applying various dimensionality reduction techniques such as PCA, t-SNE, and UMAP to analyze and visualize data.', 'A6.B.5.f.26365'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Support the creation and training of autoencoder models and other neural methods using Pytorch.', 'A6.G.0.f.29784'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Implement and optimize Generative AI solutions, including prompt engineering, data modeling, and automation in various applications.', 'A6.J.2.h.29848'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Demonstrate strong theoretical understanding of machine learning algorithms and techniques.', 'A6.A.16.b.29709'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Ability to creatively and quickly solve complex problems.', 'A6.B.0.l.18369'), ('Understand and apply knowledge of artificial intelligence and GenAI tools.', 'A6.A.16.c.29444'), ('Ability to develop algorithms and analyze programming problems to create solutions and automate processes.', 'A6.J.8.d.23623')]</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -11439,25 +11439,25 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="S66" t="n">
         <v>24</v>
       </c>
       <c r="T66" t="n">
-        <v>0.707</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="U66" t="n">
-        <v>0.754</v>
+        <v>0.737</v>
       </c>
       <c r="V66" t="n">
-        <v>0.707</v>
+        <v>0.703</v>
       </c>
       <c r="W66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X66" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
@@ -11598,17 +11598,17 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
+          <t>[('7276', 'Gather and organize information on problems or procedures.')]</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>[('Demonstrate an understanding of computer science fundamentals, including data structures, algorithms, and AI/machine learning concepts.', 'A6.A.9.e.26712'), ('Solid understanding of machine learning concepts, algorithms, techniques, and their practical applications.', 'A6.J.3.c.29814')]</t>
+          <t>[('Demonstrate an understanding of computer science fundamentals, including data structures, algorithms, and AI/machine learning concepts.', 'A6.A.9.e.26712'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Solid understanding of machine learning concepts, algorithms, techniques, and their practical applications.', 'A6.J.3.c.29814')]</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -11617,25 +11617,25 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S67" t="n">
         <v>7</v>
       </c>
       <c r="T67" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>0.701</v>
       </c>
       <c r="V67" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>[('16596', 'Build or assemble robotic devices or systems.')]</t>
+          <t>[('22469', 'Operate and maintain audio-visual equipment.'), ('16596', 'Build or assemble robotic devices or systems.'), ('16518', 'Plan mobile robot paths and teach path plans to robots.')]</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Research and develop machine learning and deep learning methodologies.', 'A6.J.2.m.29845'), ('Advanced knowledge and experience utilizing a variety of machine learning techniques such as clustering, decision tree learning, and neural networks, including their real-world advantages and drawbacks in supervised and unsupervised learning applications.', 'A6.A.16.b.28737'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Solid understanding of robotics fundamentals, including motion planning, control systems, perception, and navigation methods.', 'A6.A.18.c.26310'), ('Design and implement control algorithms and software programs for intelligent robot behaviors and machine control systems.', 'A6.J.5.e.25702')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Ability to navigate and solve problems in ambiguous and complex situations.', 'A6.B.0.l.18508'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Research and develop machine learning and deep learning methodologies.', 'A6.J.2.m.29845'), ('Advanced knowledge and experience utilizing a variety of machine learning techniques such as clustering, decision tree learning, and neural networks, including their real-world advantages and drawbacks in supervised and unsupervised learning applications.', 'A6.A.16.b.28737'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Develop, implement, and optimize speech recognition and natural language processing systems, including handling voice command recognition, speech-to-text functionality, and related algorithms.', 'A6.J.11.e.28355'), ('Solid understanding of robotics fundamentals, including motion planning, control systems, perception, and navigation methods.', 'A6.A.18.c.26310'), ('Design and implement control algorithms and software programs for intelligent robot behaviors and machine control systems.', 'A6.J.5.e.25702')]</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -11740,25 +11740,25 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S68" t="n">
         <v>9</v>
       </c>
       <c r="T68" t="n">
-        <v>0.711</v>
+        <v>0.673</v>
       </c>
       <c r="U68" t="n">
         <v>0.74</v>
       </c>
       <c r="V68" t="n">
-        <v>0.711</v>
+        <v>0.703</v>
       </c>
       <c r="W68" t="n">
         <v>4</v>
       </c>
       <c r="X68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -11822,17 +11822,17 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
+          <t>[('18470', 'Prepare graphic representations or drawings of proposed plans or designs.')]</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>[('Construct and search Knowledge Graphs using vector similarity search and vector databases.', 'A6.E.4.g.24174'), ('Knowledge of machine learning techniques, algorithms, and applications in artificial intelligence.', 'A6.A.16.c.29833')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Proficient in using data visualization tools and frameworks, such as D3.js and Plotly, to create effective visual representations of data.', 'A6.A.7.d.18583'), ('Construct and search Knowledge Graphs using vector similarity search and vector databases.', 'A6.E.4.g.24174'), ('Knowledge of machine learning techniques, algorithms, and applications in artificial intelligence.', 'A6.A.16.c.29833')]</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -11841,25 +11841,25 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
       </c>
       <c r="T69" t="n">
-        <v>0.663</v>
+        <v>0.63</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0.663</v>
+        <v>0.697</v>
       </c>
       <c r="W69" t="n">
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('10902', 'Develop, test, or program new robots.'), ('21828', 'Create graphs, charts, or other visualizations to convey the results of data analysis using specialized software.'), ('20981', 'Input data into databases.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16430', 'Develop or integrate control feature requirements.')]</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>[('Develop and apply expertise in artificial intelligence and machine learning algorithms.', 'A6.J.4.h.29758'), ('Work collaboratively on interdisciplinary projects involving reinforcement learning, deep learning, computer vision, motion planning, and human-robot cooperation for robotic applications in manufacturing and construction.', 'A6.J.0.e.24564'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Implement scalable machine learning systems and resource-efficient AI algorithms for real-time data analysis and decision automation.', 'A6.J.2.p.29431'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Utilize TensorFlow for applications in artificial intelligence, deep learning, or natural language processing.', 'A6.J.1.h.29891'), ('Familiarity with Power BI, SQL, and other data visualization and analysis tools.', 'A6.B.6.d.17473'), ('Understanding data is essential for effective data science.', 'A6.D.0.w.29780'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Conduct data analytics, mathematical or statistical modeling, and machine learning.', 'A6.J.1.k.29545'), ('Utilize Python for data analysis, manipulation, and modeling.', 'A6.B.8.a.29743'), ('Utilize Python and its libraries, such as Pandas, NumPy, and SciPy, for data manipulation, analysis, and modeling tasks.', 'A6.B.8.u.23683'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Apply natural language processing (NLP) techniques for tasks such as sentiment analysis, text classification, entity recognition, and topic modeling to analyze and interpret textual data.', 'A6.G.0.n.27966')]</t>
+          <t>[('Develop and apply expertise in artificial intelligence and machine learning algorithms.', 'A6.J.4.h.29758'), ('Work collaboratively on interdisciplinary projects involving reinforcement learning, deep learning, computer vision, motion planning, and human-robot cooperation for robotic applications in manufacturing and construction.', 'A6.J.0.e.24564'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Implement scalable machine learning systems and resource-efficient AI algorithms for real-time data analysis and decision automation.', 'A6.J.2.p.29431'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Utilize TensorFlow for applications in artificial intelligence, deep learning, or natural language processing.', 'A6.J.1.h.29891'), ('Familiarity with Power BI, SQL, and other data visualization and analysis tools.', 'A6.B.6.d.17473'), ('Proficient in applying AI and machine learning techniques to business use cases, implementing control strategies in robotics, and deploying machine learning models in production environments using languages such as Java, Scala, and Python.', 'A6.J.7.e.28569'), ('Understanding data is essential for effective data science.', 'A6.D.0.w.29780'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Conduct data analytics, mathematical or statistical modeling, and machine learning.', 'A6.J.1.k.29545'), ('Utilize Python for data analysis, manipulation, and modeling.', 'A6.B.8.a.29743'), ('Develop, write, and automate tasks using Python scripts.', 'A6.K.0.b.23854'), ('Utilize Python and its libraries, such as Pandas, NumPy, and SciPy, for data manipulation, analysis, and modeling tasks.', 'A6.B.8.u.23683'), ('Write and maintain Python scripts to automate and optimize data-related processes.', 'A6.B.8.a.26154'), ('Use Python and libraries like Pandas and NumPy for data manipulation and automation.', 'A6.B.8.u.26549'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Apply natural language processing (NLP) techniques for tasks such as sentiment analysis, text classification, entity recognition, and topic modeling to analyze and interpret textual data.', 'A6.G.0.n.27966'), ('Demonstrate a solid understanding of feature engineering and model evaluation techniques.', 'A6.B.7.c.29808'), ('Demonstrate expertise in NLP or text mining techniques.', 'A6.J.14.d.28734')]</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -12226,25 +12226,25 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="S70" t="n">
         <v>31</v>
       </c>
       <c r="T70" t="n">
-        <v>0.732</v>
+        <v>0.711</v>
       </c>
       <c r="U70" t="n">
-        <v>0.767</v>
+        <v>0.777</v>
       </c>
       <c r="V70" t="n">
-        <v>0.762</v>
+        <v>0.745</v>
       </c>
       <c r="W70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X70" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>[('21823', 'Analyze, manipulate, or process large sets of data using statistical software.'), ('21101', 'Prepare and structure data warehouses for storing data.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('7380', 'Perform validation and testing of models to ensure adequacy, and reformulate models, as necessary.'), ('16069', 'Monitor and analyze system performance, such as network traffic, security, and capacity.'), ('8114', "Recommend products to customers, based on customers' needs and interests."), ('16036', 'Train others in fraud detection and prevention techniques.'), ('21632', 'Recommend ways to control or reduce risk.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('1229', 'Develop event topics and choose featured speakers.'), ('12952', 'Prepare, manipulate, and manage extensive databases.'), ('22089', 'Attend conferences, workshops, or other training sessions to learn about new tools or methods.'), ('20871', 'Develop testing procedures.'), ('22350', 'Plan or supervise experiential learning activities, such as class projects, field trips, demonstrations, or visits by guest speakers.'), ('14639', 'Test system modifications to prepare for implementation.'), ('8956', 'Analyze and interpret statistical data to identify significant differences in relationships among sources of information.'), ('21816', 'Discuss data needs with engineers, product managers, or data scientists to identify blockchain requirements.'), ('21823', 'Analyze, manipulate, or process large sets of data using statistical software.'), ('21101', 'Prepare and structure data warehouses for storing data.'), ('23672', 'Separate models or patterns from molds and examine products for accuracy.'), ('7380', 'Perform validation and testing of models to ensure adequacy, and reformulate models, as necessary.'), ('4133', 'Prepare and position patients for testing.'), ('1356', "Investigate or test vendors' or competitors' products."), ('19068', 'Develop or implement strategies to meet the needs of students with a variety of disabilities.'), ('3123', 'Test experimental models under simulated operating conditions, for purposes such as development, standardization, or feasibility of design.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.'), ('18144', 'Maintain validation test equipment.'), ('5217', 'Teach classes or courses to students.'), ('16069', 'Monitor and analyze system performance, such as network traffic, security, and capacity.'), ('7388', 'Design, conduct, and evaluate experimental operational models in cases where models cannot be developed from existing data.'), ('11826', 'Demonstrate equipment functions and features to machine operators.'), ('8114', "Recommend products to customers, based on customers' needs and interests."), ('16036', 'Train others in fraud detection and prevention techniques.'), ('10902', 'Develop, test, or program new robots.'), ('995', 'Plan, organize, direct, control, or coordinate the personnel, training, or labor relations activities of an organization.'), ('21632', 'Recommend ways to control or reduce risk.'), ('4010', 'Regulate the fidelity, brightness, and contrast of video transmissions, using video console control panels.'), ('21332', 'Conduct site audits to ensure adherence to safety and environmental regulations.')]</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Strong understanding of digital technologies and trends in AI, machine learning, data analytics, and cloud computing, with a focus on large language models and generative AI applications.', 'A6.A.15.l.27132'), ('Interest in developing and applying machine learning and AI to create impactful, scalable solutions for businesses and customers.', 'A6.J.11.e.26799'), ('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Knowledgeable about the latest developments in data science, AI/ML techniques, and manufacturing technologies.', 'A6.J.2.s.23244'), ('Develop and manage big data technologies and pipelines for efficient data processing.', 'A6.E.0.d.29372'), ('Employ machine learning, deep learning, and data mining techniques.', 'A6.J.14.d.29750'), ('Conduct experiments and A/B testing to evaluate and optimize model performance and accuracy.', 'A6.B.2.m.22637'), ('Develop and implement A/B testing and multivariate testing strategies.', 'A6.C.4.t.19546'), ('Leverage big data technologies to analyze large datasets and derive insights for improving business outcomes and decision-making.', 'A6.D.0.ae.27944'), ('Leads and manages big data and analytics projects by gathering, integrating, and analyzing large volumes of data from multiple sources, including predictive and exploratory analytics.', 'A6.C.7.a.22296'), ('Interest and experience with big data platform tools and data management platforms.', 'A6.A.14.i.25970'), ('Analyze and process big data using scalable model training and supervised/unsupervised modeling techniques.', 'A6.D.1.k.29034'), ('Leverage big data and cloud computing technologies to address business questions.', 'A6.E.0.c.20994'), ('Analyze, manipulate, and manage large datasets using big data processing frameworks and data mining techniques.', 'A6.C.1.b.28532'), ('Analyzes big data to identify trends and patterns for hypothesis validation.', 'A6.D.0.h.27845'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Utilize machine learning techniques, including supervised, unsupervised, and self-supervised learning algorithms.', 'A6.J.1.h.29895'), ('Experience with machine learning algorithms and techniques, including supervised, unsupervised, and reinforcement learning, as well as model building and optimization.', 'A6.A.16.b.28886'), ('Develop ML algorithms to analyze large volumes of historical data to make predictions.', 'A6.G.0.f.29341'), ('Implement and apply various supervised and unsupervised machine learning techniques, including decision trees, neural networks, clustering algorithms, and regression models.', 'A6.J.11.j.29598'), ('Experiment with various algorithms and techniques to optimize model performance and improve prediction accuracy.', 'A6.J.10.d.28400'), ('Implement and validate machine learning models and statistical algorithms, ensuring their accuracy and efficiency.', 'A6.J.11.h.29344'), ('Apply machine learning techniques and statistical modeling to large datasets.', 'A6.J.14.f.29871'), ('Build and validate predictive models and machine learning algorithms.', 'A6.J.11.g.29806'), ('Solid understanding of supervised and unsupervised machine learning techniques, including evaluation and tuning methods.', 'A6.A.16.b.28830'), ('Develop and apply machine learning models and statistical data analysis using Python.', 'A6.J.3.b.29102'), ('Conduct model training, evaluation, and validation to ensure high performance and accuracy in various applications.', 'A6.B.2.m.28668'), ('Understanding data is essential for effective data science.', 'A6.D.0.w.29780'), ('Write clean, maintainable, and efficient code for AI/ML model training, evaluation, and serving.', 'A6.J.13.i.29457'), ('Participate in the design, implementation, and execution of machine learning models and tools, including MLOps workflows and statistical modeling methodologies.', 'A6.J.6.b.24987'), ('Manage and automate ML pipelines using MLOps practices and data science workflows.', 'A6.J.13.e.25125'), ('Strong understanding of current trends and best practices in data science and machine learning, with a focus on generative AI models.', 'A6.J.2.s.29111'), ('Develop and advance state-of-the-art recommender systems and advertising technologies.', 'A6.G.0.f.28167'), ('Develop and deploy machine learning models for fraud detection and risk assessment.', 'A6.J.11.e.26375'), ('Share insights and conduct quantitative financial research using statistical modeling and machine learning algorithms in the financial industry.', 'A6.D.1.k.21754'), ('Integrate AI services, algorithms, and tools into applications and data workflows.', 'A6.J.0.m.29618'), ('Ability to leverage advanced technology innovations, including machine learning and business process intelligence, to drive enterprise-wide business transformation.', 'A6.J.7.c.16659'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Ability to design, develop, and implement AI models and machine learning algorithms for various high-impact projects and applications.', 'A6.J.0.n.28204'), ('Stay current with industry trends and advancements in AI and machine learning to innovate and improve solutions.', 'A6.J.2.s.28075')]</t>
+          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Capable of leading projects focused on the AI development lifecycle, including the transformation of operations and integration of AI-driven solutions into clinical settings.', 'A6.I.2.c.24380'), ('Strong understanding of digital technologies and trends in AI, machine learning, data analytics, and cloud computing, with a focus on large language models and generative AI applications.', 'A6.A.15.l.27132'), ('Interest in developing and applying machine learning and AI to create impactful, scalable solutions for businesses and customers.', 'A6.J.11.e.26799'), ('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Strong grasp of AI ethics, data privacy, and responsible practices, including principles for minimizing bias and ensuring compliance with regulatory frameworks.', 'A6.G.2.k.29791'), ('Ability to identify and seek opportunities for adopting and applying innovative technologies.', 'A6.F.6.b.14520'), ('Conduct workshop sessions to identify opportunities for customers to deliver business value through generative AI or machine learning while collaborating with account teams, research scientists, and product engineering teams to implement advanced analytics algorithms and drive model implementations.', 'A6.J.7.h.21767'), ('Knowledgeable about the latest developments in data science, AI/ML techniques, and manufacturing technologies.', 'A6.J.2.s.23244'), ('Develop and manage big data technologies and pipelines for efficient data processing.', 'A6.E.0.d.29372'), ('Demonstrates a continuous learning mindset to stay updated with emerging technologies and best practices in data engineering and analytics.', 'A6.J.0.i.20960'), ('Employ machine learning, deep learning, and data mining techniques.', 'A6.J.14.d.29750'), ('Conduct experiments and A/B testing to evaluate and optimize model performance and accuracy.', 'A6.B.2.m.22637'), ('Implement reinforcement learning algorithms using Python.', 'A6.J.8.f.29896'), ('Maintain and operate AI technologies and machine learning algorithms in a production environment.', 'A6.J.11.j.28985'), ('Develop and implement A/B testing and multivariate testing strategies.', 'A6.C.4.t.19546'), ('Ability to translate big data into actionable insights and ideas.', 'A6.D.0.ai.27834'), ('Leverage big data technologies to analyze large datasets and derive insights for improving business outcomes and decision-making.', 'A6.D.0.ae.27944'), ('Leads and manages big data and analytics projects by gathering, integrating, and analyzing large volumes of data from multiple sources, including predictive and exploratory analytics.', 'A6.C.7.a.22296'), ('Interest and experience with big data platform tools and data management platforms.', 'A6.A.14.i.25970'), ('Analyze and process big data using scalable model training and supervised/unsupervised modeling techniques.', 'A6.D.1.k.29034'), ('Leverage big data and cloud computing technologies to address business questions.', 'A6.E.0.c.20994'), ('Possesses deep understanding of various data modeling techniques, including dimensional modeling, star and snowflake schemas, and data warehousing concepts.', 'A6.A.14.f.27285'), ('Analyze, manipulate, and manage large datasets using big data processing frameworks and data mining techniques.', 'A6.C.1.b.28532'), ('Analyzes big data to identify trends and patterns for hypothesis validation.', 'A6.D.0.h.27845'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Utilize machine learning techniques, including supervised, unsupervised, and self-supervised learning algorithms.', 'A6.J.1.h.29895'), ('Experience with machine learning algorithms and techniques, including supervised, unsupervised, and reinforcement learning, as well as model building and optimization.', 'A6.A.16.b.28886'), ('Conduct rigorous experimentation and performance evaluation of AI/ML models to optimize their accuracy and efficiency.', 'A6.B.2.m.27775'), ('Develop ML algorithms to analyze large volumes of historical data to make predictions.', 'A6.G.0.f.29341'), ('Implement and apply various supervised and unsupervised machine learning techniques, including decision trees, neural networks, clustering algorithms, and regression models.', 'A6.J.11.j.29598'), ('Experiment with various algorithms and techniques to optimize model performance and improve prediction accuracy.', 'A6.J.10.d.28400'), ('Implement and validate machine learning models and statistical algorithms, ensuring their accuracy and efficiency.', 'A6.J.11.h.29344'), ('Apply machine learning techniques and statistical modeling to large datasets.', 'A6.J.14.f.29871'), ('Build and validate predictive models and machine learning algorithms.', 'A6.J.11.g.29806'), ('Develops and innovates state-of-the-art machine learning models and conducts A/B tests to enhance product and shopper understanding for effective ad delivery and click-through prediction.', 'A6.J.2.m.20120'), ('Conduct simulations and tests to validate the performance and reliability of localization, mapping, perception, planning, motion planning, and DSP algorithms.', 'A6.B.2.m.20081'), ('Ability to automate and provide feedback loops for algorithms in production, including test result analysis.', 'A6.J.8.i.22674'), ('Knowledge of various machine learning techniques and algorithms, including their real-world advantages and drawbacks, for effective business decision-making.', 'A6.A.16.a.28018'), ('Develop and design simulations and games, including medical simulations and critical game studies.', 'A6.G.0.e.11524'), ('Ability to solve large-scale, end-to-end AI training and inference challenges throughout the full model lifecycle, including data curation, pre-processing, orchestrating model training and tuning, and model deployment.', 'A6.J.13.c.23809'), ('Develop and implement models with a focus on validation and performance optimization for large-scale and NLP applications.', 'A6.J.4.f.28843'), ('Solid understanding of supervised and unsupervised machine learning techniques, including evaluation and tuning methods.', 'A6.A.16.b.28830'), ('Develop and apply machine learning models and statistical data analysis using Python.', 'A6.J.3.b.29102'), ('Conduct model training, evaluation, and validation to ensure high performance and accuracy in various applications.', 'A6.B.2.m.28668'), ('Apply statistical methods and machine learning techniques in an industry or research environment.', 'A6.G.0.n.28836'), ('Understanding data is essential for effective data science.', 'A6.D.0.w.29780'), ('Write clean, maintainable, and efficient code for AI/ML model training, evaluation, and serving.', 'A6.J.13.i.29457'), ('Proficient in ML model development, deployment, monitoring, and lifecycle management using MLOps practices and tools like MLFlow.', 'A6.J.11.j.25426'), ('Contribute to MLOps and LLMOps by focusing on operational capabilities and infrastructure for deploying and managing machine learning models and large language models.', 'A6.J.13.e.26500'), ('Build and maintain automated ML pipelines incorporating DevOps principles for model training, testing, deployment, and monitoring.', 'A6.J.11.j.21033'), ('Collaborate with software and ML engineers to tackle challenging problems in building and deploying artificial intelligence and machine learning solutions.', 'A6.J.6.b.26383'), ('Participate in the design, implementation, and execution of machine learning models and tools, including MLOps workflows and statistical modeling methodologies.', 'A6.J.6.b.24987'), ('Manage and automate ML pipelines using MLOps practices and data science workflows.', 'A6.J.13.e.25125'), ('Familiarity with data science and machine learning concepts is beneficial, but not mandatory.', 'A6.A.22.f.21788'), ('Strong understanding of current trends and best practices in data science and machine learning, with a focus on generative AI models.', 'A6.J.2.s.29111'), ('Develop web-based applications and AI solutions utilizing generative AI large language models and prompt engineering strategies.', 'A6.J.5.c.28145'), ('Develop and evaluate recommender systems and personalization algorithms, including metrics and text mining.', 'A6.G.0.f.29191'), ('Develop and advance state-of-the-art recommender systems and advertising technologies.', 'A6.G.0.f.28167'), ('Apply machine learning approaches and algorithms to recommender systems.', 'A6.J.14.a.29818'), ('Ability to contribute to the development of innovative autonomous vehicles that enhance safety and connectivity in transportation.', 'A6.F.6.l.27294'), ('Develop and deploy machine learning models for fraud detection and risk assessment.', 'A6.J.11.e.26375'), ('Share insights and conduct quantitative financial research using statistical modeling and machine learning algorithms in the financial industry.', 'A6.D.1.k.21754'), ('Ability to develop and execute a comprehensive AI and data strategy that aligns with organizational goals and objectives.', 'A6.J.4.i.24754'), ('Integrate AI services, algorithms, and tools into applications and data workflows.', 'A6.J.0.m.29618'), ('Ability to leverage advanced technology innovations, including machine learning and business process intelligence, to drive enterprise-wide business transformation.', 'A6.J.7.c.16659'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Strong understanding of machine learning concepts, algorithms, and workflows, including supervised/unsupervised learning, deep learning, reinforcement learning, and statistical modeling.', 'A6.J.3.c.29389'), ('Promotes responsible AI practices, emphasizing transparency, fairness, accountability, and interpretability in machine learning initiatives.', 'A6.G.2.k.27674'), ('Ability to design, develop, and implement AI models and machine learning algorithms for various high-impact projects and applications.', 'A6.J.0.n.28204'), ('Stay current on AI and machine learning trends, tools, technologies, and regulations to enhance systems and inform strategy.', 'A6.J.2.s.27326'), ('Knowledge of data governance, security, privacy, and ethical practices in AI development, including addressing issues like data poisoning and model theft.', 'A6.G.2.k.27697'), ('Ability to coordinate regulatory programs and evaluate the use of big data, algorithms, and predictive models by insurers to prevent unfair discrimination.', 'A6.C.1.a.19206'), ('Ability to collaborate with security and risk leaders to identify, anticipate, and mitigate manipulation risks in AI systems, ensuring ethical implementation and restoring trust.', 'A6.J.9.g.24325'), ('Stay current with industry trends and advancements in AI and machine learning to innovate and improve solutions.', 'A6.J.2.s.28075')]</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -12633,25 +12633,25 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="S71" t="n">
         <v>22</v>
       </c>
       <c r="T71" t="n">
-        <v>0.658</v>
+        <v>0.624</v>
       </c>
       <c r="U71" t="n">
-        <v>0.707</v>
+        <v>0.669</v>
       </c>
       <c r="V71" t="n">
-        <v>0.661</v>
+        <v>0.631</v>
       </c>
       <c r="W71" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="X71" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72">
@@ -12719,17 +12719,17 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
+          <t>[('14623', 'Analyze problems to develop solutions involving computer hardware and software.')]</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590')]</t>
+          <t>[('Design and develop AI algorithms and solutions for various applications, including conversational systems, intelligent agents, and generative AI tools.', 'A6.J.4.d.29651'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590')]</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -12738,25 +12738,25 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
       </c>
       <c r="T72" t="n">
-        <v>0.722</v>
+        <v>0.727</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>0.732</v>
       </c>
       <c r="V72" t="n">
-        <v>0.722</v>
+        <v>0.727</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -12829,7 +12829,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('23695', 'Plan and establish schedules.')]</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>[('Develop and optimize algorithms for robotics perception, navigation, planning, and control systems.', 'A6.G.0.z.28415'), ('Understand and apply machine learning algorithms, including supervised, unsupervised, reinforcement learning, and natural language processing techniques.', 'A6.A.16.b.29696')]</t>
+          <t>[('Ability to navigate and solve problems in ambiguous and complex situations.', 'A6.B.0.l.18508'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Develop and optimize algorithms for robotics perception, navigation, planning, and control systems.', 'A6.G.0.z.28415'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Understand and apply machine learning algorithms, including supervised, unsupervised, reinforcement learning, and natural language processing techniques.', 'A6.A.16.b.29696')]</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -12848,7 +12848,7 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S73" t="n">
         <v>6</v>
@@ -12860,13 +12860,13 @@
         <v>0.65</v>
       </c>
       <c r="V73" t="n">
-        <v>0.695</v>
+        <v>0.73</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>[('21831', 'Identify business problems or management objectives that can be addressed through data analysis.'), ('20952', 'Present the results of mathematical modeling and data analysis to management or other end users.'), ('21823', 'Analyze, manipulate, or process large sets of data using statistical software.')]</t>
+          <t>[('7538', 'Compile, analyze, and report data to explain economic phenomena and forecast market trends, applying mathematical models and statistical techniques.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('21831', 'Identify business problems or management objectives that can be addressed through data analysis.'), ('15983', 'Provide application or analytical support to researchers or traders on issues such as valuations or data.'), ('20952', 'Present the results of mathematical modeling and data analysis to management or other end users.'), ('16132', 'Develop data warehouse process models, including sourcing, loading, transformation, and extraction.'), ('21823', 'Analyze, manipulate, or process large sets of data using statistical software.'), ('16976', 'Evaluate analytical methods and procedures to determine how they might be improved.')]</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>[('Demonstrates advanced analytics skills in statistics, data analysis, machine learning, and optimization techniques.', 'A6.A.12.d.27287'), ('Demonstrates advanced knowledge of business analytics and data mining solutions.', 'A6.A.14.e.21521'), ('Develop and implement predictive modeling and machine learning algorithms for various applications.', 'A6.J.11.h.29836'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Optimize model performance through hyperparameter tuning, feature engineering, and algorithm selection.', 'A6.E.5.e.29725'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Apply supervised and unsupervised machine learning techniques, including classification, regression, and clustering.', 'A6.J.14.e.29624'), ('Ability to collaborate with teams and stakeholders to translate business needs into data-driven solutions and execute analytics projects that address business challenges.', 'A6.F.10.e.15673'), ('Provides expertise in application data collection, analytics, and reporting.', 'A6.B.2.z.25791'), ('Ability to develop business cases and create complex models using big data analytics tools to enhance processes, financial outcomes, and business models.', 'A6.F.10.h.19540'), ('Leverage statistical and computational modeling techniques for predictive analytics and business analysis.', 'A6.A.14.f.29398'), ('Perform data preprocessing and transformation, including cleanup and quality assurance.', 'A6.B.2.o.29570'), ('Develop and apply statistical or machine learning methods using tools such as R, Python, SAS, or SPSS in a corporate environment.', 'A6.J.3.b.26072')]</t>
+          <t>[('Demonstrates advanced analytics skills in statistics, data analysis, machine learning, and optimization techniques.', 'A6.A.12.d.27287'), ('Utilize statistical and machine learning techniques with high-performance data architectures to analyze large, unstructured data sets and address business problems.', 'A6.A.11.d.28049'), ('Demonstrates advanced knowledge of business analytics and data mining solutions.', 'A6.A.14.e.21521'), ('Develop and implement predictive modeling and machine learning algorithms for various applications.', 'A6.J.11.h.29836'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Extensive experience in supervised and unsupervised machine learning techniques, including pattern recognition, classification, clustering, regression, and advanced deep learning architectures.', 'A6.J.11.j.27984'), ('Manage and develop pattern recognition and predictive modeling techniques.', 'A6.J.11.f.29584'), ('Optimize model performance through hyperparameter tuning, feature engineering, and algorithm selection.', 'A6.E.5.e.29725'), ('Develop machine learning algorithms and models.', 'A6.J.12.a.29904'), ('Apply supervised and unsupervised machine learning techniques, including classification, regression, and clustering.', 'A6.J.14.e.29624'), ('Ability to collaborate with teams and stakeholders to translate business needs into data-driven solutions and execute analytics projects that address business challenges.', 'A6.F.10.e.15673'), ('Provides expertise in application data collection, analytics, and reporting.', 'A6.B.2.z.25791'), ('Ability to identify options for addressing business problems through analytics, big data analytics, and automation.', 'A6.D.0.ah.21097'), ('Ability to work with large datasets and apply advanced data mining techniques and methodologies for data manipulation.', 'A6.C.1.b.29176'), ('Utilize data science methods for market research and performance analytics.', 'A6.B.2.g.27627'), ('Ability to develop business cases and create complex models using big data analytics tools to enhance processes, financial outcomes, and business models.', 'A6.F.10.h.19540'), ('Leverage statistical and computational modeling techniques for predictive analytics and business analysis.', 'A6.A.14.f.29398'), ('Compare models using statistical performance metrics, such as loss functions or proportion of explained variance.', 'A6.B.5.c.18008'), ('Perform data preprocessing and transformation, including cleanup and quality assurance.', 'A6.B.2.o.29570'), ('Develop and apply statistical or machine learning methods using tools such as R, Python, SAS, or SPSS in a corporate environment.', 'A6.J.3.b.26072')]</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -13024,25 +13024,25 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="S74" t="n">
         <v>14</v>
       </c>
       <c r="T74" t="n">
-        <v>0.655</v>
+        <v>0.637</v>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="V74" t="n">
-        <v>0.715</v>
+        <v>0.681</v>
       </c>
       <c r="W74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X74" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('17716', 'Maintain awareness of new and emerging computational methods and technologies.'), ('20327', 'Improve search-related activities through ongoing analysis, experimentation, or optimization tests, using A/B or multivariate methods.'), ('14623', 'Analyze problems to develop solutions involving computer hardware and software.'), ('14629', 'Conduct logical analyses of business, scientific, engineering, and other technical problems, formulating mathematical models of problems for solution by computers.'), ('8967', 'Examine theories, such as those of probability and inference, to discover mathematical bases for new or improved methods of obtaining and evaluating numerical data.')]</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Ability to develop machine learning and artificial intelligence techniques and algorithms to solve complex business problems using both supervised and unsupervised methodologies.', 'A6.J.6.i.26996')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Utilize graph data in a machine learning environment.', 'A6.J.1.h.29665'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Ability to apply strong knowledge of algorithms and data structures to solve complex business and technical problems.', 'A6.B.0.d.20576'), ('Develop computer algorithms using linear algebra, calculus, differential equations, and numerical methods.', 'A6.G.0.e.28013'), ('Provide expert supervision and guidance on causal inference methods and intricate machine learning feature engineering processes.', 'A6.A.16.b.24996'), ('Ability to develop machine learning and artificial intelligence techniques and algorithms to solve complex business problems using both supervised and unsupervised methodologies.', 'A6.J.6.i.26996'), ('Collect, clean, and analyze large datasets while developing and engineering high-reliability numerical code using advanced quantitative techniques in mathematics and statistics.', 'A6.J.1.b.19496')]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -13187,25 +13187,25 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
       </c>
       <c r="T75" t="n">
-        <v>0.708</v>
+        <v>0.64</v>
       </c>
       <c r="U75" t="n">
         <v>0.713</v>
       </c>
       <c r="V75" t="n">
-        <v>0.708</v>
+        <v>0.64</v>
       </c>
       <c r="W75" t="n">
         <v>2</v>
       </c>
       <c r="X75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('9087', 'Conduct research on the structures and properties of materials, such as metals, alloys, polymers, and ceramics, to obtain information that could be used to develop new products or enhance existing ones.'), ('14629', 'Conduct logical analyses of business, scientific, engineering, and other technical problems, formulating mathematical models of problems for solution by computers.'), ('19483', 'Review computer-processed digital images for quality.'), ('22271', 'Plot information from aerial photographs, well logs, section descriptions, or other databases.')]</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Proficient in uncertainty quantification, including methods applied to statistical analysis, multi-modal deep learning, risk analysis, and computational models.', 'A6.A.12.c.21622'), ('Strong interest in artificial intelligence and machine learning, including concepts, algorithms, applications in various fields, and continuous learning in emerging technologies.', 'A6.A.16.a.28899'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Strong programming skills in one or more languages, including Python, Java, C, C++, and MATLAB.', 'A6.K.1.f.19009'), ('Research, design, implement, and evaluate machine learning and deep learning algorithms to address various applications.', 'A6.J.6.b.29200'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Expertise in selecting, manipulating, and transforming data into features for machine learning algorithms using dimensionality reduction, feature importance, and feature selection techniques.', 'A6.A.16.b.29068'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Design and implement computer vision and 3D geometry related machine learning pipelines.', 'A6.J.11.b.28238'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Ability to accurately explain the functioning of a decision tree and code it from scratch.', 'A6.H.2.d.29644'), ('Demonstrate key sensor functions and understanding of sensor technology in computer vision and inertial sensors.', 'A6.A.22.a.18503')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Ability to identify, investigate, and resolve problems by determining logical solutions and recommending corrective actions.', 'A6.G.6.a.15328'), ('Proficient in uncertainty quantification, including methods applied to statistical analysis, multi-modal deep learning, risk analysis, and computational models.', 'A6.A.12.c.21622'), ('Design, develop, and implement knowledge-based systems, including ontologies, taxonomies, and knowledge graphs to support data integration and semantic search.', 'A6.G.0.j.27688'), ('Strong interest in artificial intelligence and machine learning, including concepts, algorithms, applications in various fields, and continuous learning in emerging technologies.', 'A6.A.16.a.28899'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Strong programming skills in one or more languages, including Python, Java, C, C++, and MATLAB.', 'A6.K.1.f.19009'), ('Research, design, implement, and evaluate machine learning and deep learning algorithms to address various applications.', 'A6.J.6.b.29200'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Ability to draw sound scientific conclusions and logical inferences based on data analysis.', 'A6.D.0.k.23435'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Constructs predictive models and algorithms, including probability engines.', 'A6.J.11.f.29585'), ('Expertise in selecting, manipulating, and transforming data into features for machine learning algorithms using dimensionality reduction, feature importance, and feature selection techniques.', 'A6.A.16.b.29068'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Possess expert knowledge of the theory, algorithms, and techniques in video and image coding and processing, including the latest standards such as HEVC and VVC.', 'A6.J.9.i.15761'), ('Develop and optimize computer vision algorithms and models, including convolutional neural networks, for tasks such as image classification, speech recognition, and time series forecasting.', 'A6.G.0.g.28003'), ('Develop and implement spatial models and algorithms to analyze patterns and trends within geographical datasets.', 'A6.F.1.c.20723'), ('Design and implement computer vision and 3D geometry related machine learning pipelines.', 'A6.J.11.b.28238'), ('Ability to accurately explain the functioning of a decision tree and code it from scratch.', 'A6.H.2.d.29644'), ('Research and develop improvements to existing and new signal processing algorithms.', 'A6.G.0.z.19221'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Demonstrate key sensor functions and understanding of sensor technology in computer vision and inertial sensors.', 'A6.A.22.a.18503')]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -13547,25 +13547,25 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="S77" t="n">
         <v>19</v>
       </c>
       <c r="T77" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="U77" t="n">
-        <v>0.678</v>
+        <v>0.719</v>
       </c>
       <c r="V77" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.655</v>
       </c>
       <c r="W77" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X77" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>[('21128', 'Schedule courses.')]</t>
+          <t>[('21128', 'Schedule courses.'), ('7386', 'Specify manipulative or computational methods to be applied to models.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.')]</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Build and optimize efficient, scalable information retrieval systems and search algorithms.', 'A6.E.6.l.24698'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Design, develop, and implement knowledge-based systems, including ontologies, taxonomies, and knowledge graphs to support data integration and semantic search.', 'A6.G.0.j.27688'), ('Build and optimize efficient, scalable information retrieval systems and search algorithms.', 'A6.E.6.l.24698'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873')]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -13696,19 +13696,19 @@
         <v>11</v>
       </c>
       <c r="T78" t="n">
-        <v>0.711</v>
+        <v>0.695</v>
       </c>
       <c r="U78" t="n">
-        <v>0.754</v>
+        <v>0.77</v>
       </c>
       <c r="V78" t="n">
-        <v>0.711</v>
+        <v>0.709</v>
       </c>
       <c r="W78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('6899', 'Coordinate the look and function of product lines.'), ('14293', 'Collaborate with other operators to solve unit problems.'), ('2815', 'Check preliminary and final proofs for errors and make necessary corrections.'), ('16787', 'Develop data models and databases.'), ('14805', "Analyze a script, noting events that affect each character's appearance, so that plans can be made for each scene."), ('20327', 'Improve search-related activities through ongoing analysis, experimentation, or optimization tests, using A/B or multivariate methods.'), ('10901', 'Train others to install, use, or maintain robots.'), ('9796', 'Select statistical tests for analyzing data.')]</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>[('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Ability to navigate and solve problems in ambiguous and complex situations.', 'A6.B.0.l.18508'), ('Construct and search Knowledge Graphs using vector similarity search and vector databases.', 'A6.E.4.g.24174'), ('Develop and maintain analytical and semantic models for language processing.', 'A6.J.6.b.28881'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Familiarity with reinforcement learning techniques, applications, and advanced optimization methods in various contexts.', 'A6.A.16.b.28784'), ('Apply causal inference and exploratory data analysis techniques in statistical analysis and model development.', 'A6.C.4.k.21007')]</t>
+          <t>[('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Develop and perform analysis of tracking and state estimation algorithms.', 'A6.G.0.e.23045'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Analyze and implement greedy algorithms and dynamic programming for graph-related problems.', 'A6.J.8.g.28931'), ('Ability to navigate and solve problems in ambiguous and complex situations.', 'A6.B.0.l.18508'), ('Develop algorithms and software using MATLAB, Python, and C/C++ through iterative processes, including control and prototype algorithms.', 'A6.J.8.h.22450'), ('Research and develop novel computer vision and machine learning algorithms for 3D scene reconstruction, object detection, motion tracking, and real-time scene understanding.', 'A6.A.10.c.26726'), ('Construct and search Knowledge Graphs using vector similarity search and vector databases.', 'A6.E.4.g.24174'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Ability to draw sound scientific conclusions and logical inferences based on data analysis.', 'A6.D.0.k.23435'), ('Design and create logical and physical databases using relational database principles.', 'A6.E.3.f.18280'), ('Support the development and management of knowledge graphs and semantic models using relevant technologies.', 'A6.E.0.j.24528'), ('Develop and implement semantic technologies and ontologies for knowledge graphs and informatics workflows.', 'A6.E.0.j.25194'), ('Develop and maintain analytical and semantic models for language processing.', 'A6.J.6.b.28881'), ('Constructs predictive models and algorithms, including probability engines.', 'A6.J.11.f.29585'), ('Implement and apply Bayesian modeling techniques in multimodal data analysis, including feature selection and hierarchical Bayesian techniques.', 'A6.C.4.k.28775'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Knowledge of machine learning and data science concepts and principles.', 'A6.A.16.a.29474'), ('Demonstrate strong theoretical understanding of machine learning algorithms and techniques.', 'A6.A.16.b.29709'), ('Apply optimization theory and statistical methods, including sampling and probability theory.', 'A6.B.5.c.27256'), ('Ability to identify and implement contingency plans when issues arise.', 'A6.F.3.d.12822'), ('Develop algorithms for planning, optimizing spacecraft maneuvers, and controlling hardware interactions.', 'A6.G.0.z.23382'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Familiarity with reinforcement learning techniques, applications, and advanced optimization methods in various contexts.', 'A6.A.16.b.28784'), ('Research and develop improvements to existing and new signal processing algorithms.', 'A6.G.0.z.19221'), ('Apply causal inference and exploratory data analysis techniques in statistical analysis and model development.', 'A6.C.4.k.21007'), ('Promotes responsible AI practices, emphasizing transparency, fairness, accountability, and interpretability in machine learning initiatives.', 'A6.G.2.k.27674')]</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -13845,25 +13845,25 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="S79" t="n">
         <v>8</v>
       </c>
       <c r="T79" t="n">
-        <v>0.67</v>
+        <v>0.619</v>
       </c>
       <c r="U79" t="n">
-        <v>0.739</v>
+        <v>0.726</v>
       </c>
       <c r="V79" t="n">
-        <v>0.706</v>
+        <v>0.642</v>
       </c>
       <c r="W79" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X79" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('14623', 'Analyze problems to develop solutions involving computer hardware and software.'), ('14682', 'Develop system engineering, software engineering, system integration, or distributed system architectures.')]</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Model vision problems in the areas of object detection, facial recognition, and temporal machine learning.', 'A6.A.10.c.26684'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Ability to develop algorithms and analyze programming problems to create solutions and automate processes.', 'A6.J.8.d.23623'), ('Knowledge and ability to develop software systems using machine learning, artificial intelligence, and data science principles.', 'A6.J.3.d.26335'), ('Ability to solve complex problems in machine learning, information retrieval, natural language processing, and computer vision.', 'A6.A.16.b.25437'), ('Ability to navigate and solve problems in ambiguous and complex situations.', 'A6.B.0.l.18508'), ('A strong grasp of algorithms, data structures, software design principles, design patterns, and object-oriented programming concepts for efficient, scalable data processing and problem-solving.', 'A6.A.9.a.22140'), ('Model vision problems in the areas of object detection, facial recognition, and temporal machine learning.', 'A6.A.10.c.26684'), ('Fluency in statistical and machine learning algorithms, including regression, decision trees, neural networks, clustering, and optimization techniques.', 'A6.A.10.b.29575'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Expertise in advancements and integration of multi-modal models, including text, image, audio, and video inputs, along with emergent AI behaviors.', 'A6.A.16.a.27381')]</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -13983,25 +13983,25 @@
         </is>
       </c>
       <c r="R80" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S80" t="n">
         <v>9</v>
       </c>
       <c r="T80" t="n">
-        <v>0.7</v>
+        <v>0.631</v>
       </c>
       <c r="U80" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="V80" t="n">
-        <v>0.7</v>
+        <v>0.668</v>
       </c>
       <c r="W80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X80" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('15376', 'Research environmental sustainability issues, concerns, or stakeholder interests.'), ('1751', 'Analyze the strengths and weaknesses of opposing teams to develop game strategies.'), ('14623', 'Analyze problems to develop solutions involving computer hardware and software.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('21058', 'Evaluate robotic systems or prototypes.')]</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>[('Analyze and implement greedy algorithms and dynamic programming for graph-related problems.', 'A6.J.8.g.28931'), ('Experience in data mining and machine learning techniques.', 'A6.D.1.k.29840'), ('Develop and implement machine learning algorithms and techniques, focusing on deep learning and neural networks.', 'A6.J.12.d.29076'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Invent and develop AI algorithms and neural models for program generation and problem-solving on large-scale hardware systems.', 'A6.J.11.b.27446'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Continuously improve and refine AI models and algorithms based on real-world data and performance feedback.', 'A6.J.10.d.25935')]</t>
+          <t>[('Demonstrates commitment to professional growth and development through continuous learning, training, and advancement opportunities in AI and related fields.', 'A6.H.1.f.23981'), ('Analyze and implement greedy algorithms and dynamic programming for graph-related problems.', 'A6.J.8.g.28931'), ('Experience in data mining and machine learning techniques.', 'A6.D.1.k.29840'), ('Develop and implement machine learning algorithms and techniques, focusing on deep learning and neural networks.', 'A6.J.12.d.29076'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Apply machine learning techniques and methodologies such as ensemble algorithms, neural networks, regression, and clustering to identify weaknesses, recommend improvements, and document findings.', 'A6.G.0.n.29746'), ('Provide software structure and validation direction for AI software solutions that integrate AI algorithms to solve applied problems.', 'A6.J.4.d.26074'), ('Invent and develop AI algorithms and neural models for program generation and problem-solving on large-scale hardware systems.', 'A6.J.11.b.27446'), ('Continuously improve and refine AI models and algorithms based on real-world data and performance feedback.', 'A6.J.10.d.25935')]</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -14140,25 +14140,25 @@
         </is>
       </c>
       <c r="R81" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S81" t="n">
         <v>8</v>
       </c>
       <c r="T81" t="n">
-        <v>0.706</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="U81" t="n">
-        <v>0.703</v>
+        <v>0.674</v>
       </c>
       <c r="V81" t="n">
-        <v>0.706</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="W81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X81" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('16208', 'Devise missions, challenges, or puzzles to be encountered in game play.'), ('23050', 'Examine records to locate links in chains of evidence or information.'), ('16395', 'Analyze complex systems to determine potential for further development, production, interoperability, compatibility, or usefulness in a particular area, such as aviation.')]</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>[('Advanced knowledge and experience utilizing a variety of machine learning techniques such as clustering, decision tree learning, and neural networks, including their real-world advantages and drawbacks in supervised and unsupervised learning applications.', 'A6.A.16.b.28737'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868')]</t>
+          <t>[('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Apply conversational search and semantic search techniques, along with reinforcement learning and prompt engineering, to mitigate hallucination in algorithms.', 'A6.J.0.j.20547'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Develop and implement semantic technologies and ontologies for knowledge graphs and informatics workflows.', 'A6.E.0.j.25194'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Advanced knowledge and experience utilizing a variety of machine learning techniques such as clustering, decision tree learning, and neural networks, including their real-world advantages and drawbacks in supervised and unsupervised learning applications.', 'A6.A.16.b.28737'), ('Knowledge of various functions and responsibilities related to systems, components, and methodologies in a specialized context.', 'A6.G.0.w.18982'), ('Possesses expert knowledge of human-computer interaction principles.', 'A6.A.3.c.25588'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868')]</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -14289,25 +14289,25 @@
         </is>
       </c>
       <c r="R82" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="S82" t="n">
         <v>7</v>
       </c>
       <c r="T82" t="n">
-        <v>0.733</v>
+        <v>0.653</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>0.734</v>
       </c>
       <c r="V82" t="n">
-        <v>0.733</v>
+        <v>0.654</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X82" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('16518', 'Plan mobile robot paths and teach path plans to robots.'), ('21058', 'Evaluate robotic systems or prototypes.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.')]</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Invent and develop AI algorithms and neural models for program generation and problem-solving on large-scale hardware systems.', 'A6.J.11.b.27446'), ('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Ability to identify, investigate, and resolve problems by determining logical solutions and recommending corrective actions.', 'A6.G.6.a.15328'), ('Develop automated techniques for the design and evaluation of AI agents and analyze usage data to improve the effectiveness of AI solutions.', 'A6.F.6.e.29441')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Invent and develop AI algorithms and neural models for program generation and problem-solving on large-scale hardware systems.', 'A6.J.11.b.27446'), ('Ability to collaborate with cross-functional teams to design, develop, and deploy innovative AI and machine learning solutions.', 'A6.I.0.b.24045'), ('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Stay up-to-date with emerging trends and technologies in AI, machine learning, robotics, autonomy, UAS technology, and ethical AI.', 'A6.J.2.s.25264'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Ability to identify, investigate, and resolve problems by determining logical solutions and recommending corrective actions.', 'A6.G.6.a.15328'), ('Develop automated techniques for the design and evaluation of AI agents and analyze usage data to improve the effectiveness of AI solutions.', 'A6.F.6.e.29441')]</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -14415,25 +14415,25 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S83" t="n">
         <v>7</v>
       </c>
       <c r="T83" t="n">
-        <v>0.658</v>
+        <v>0.65</v>
       </c>
       <c r="U83" t="n">
-        <v>0.663</v>
+        <v>0.661</v>
       </c>
       <c r="V83" t="n">
-        <v>0.658</v>
+        <v>0.65</v>
       </c>
       <c r="W83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X83" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>[('22367', 'Establish and communicate clear objectives for all lessons, units, and projects to students.'), ('14629', 'Conduct logical analyses of business, scientific, engineering, and other technical problems, formulating mathematical models of problems for solution by computers.'), ('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16518', 'Plan mobile robot paths and teach path plans to robots.'), ('22367', 'Establish and communicate clear objectives for all lessons, units, and projects to students.'), ('1430', 'Apply engineering principles or practices to emerging fields, such as robotics, waste management, or biomedical engineering.'), ('17716', 'Maintain awareness of new and emerging computational methods and technologies.'), ('19622', 'Research or develop electronics technologies for use in electric-drive vehicles.'), ('14629', 'Conduct logical analyses of business, scientific, engineering, and other technical problems, formulating mathematical models of problems for solution by computers.'), ('8967', 'Examine theories, such as those of probability and inference, to discover mathematical bases for new or improved methods of obtaining and evaluating numerical data.'), ('16471', 'Research, select, or apply sensors, communication technologies, or control devices for motion control, position sensing, pressure sensing, or electronic communication.')]</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>[('Design, develop, and deploy AI and machine learning models and algorithms for various applications.', 'A6.J.4.d.29855'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Strong understanding of data structures, algorithms, software design principles, and best practices for building efficient systems.', 'A6.A.9.a.24181'), ('Expertise in the development and implementation of self-driving vehicles, focusing on enhancing urban mobility, safety, and freedom of movement through a hybrid network of autonomous and human-driven transportation.', 'A6.F.6.h.25093'), ('Develop, implement, and optimize speech recognition and natural language processing systems, including handling voice command recognition, speech-to-text functionality, and related algorithms.', 'A6.J.11.e.28355'), ('Design, develop, and implement advanced AI and ML models and algorithms to solve complex business problems.', 'A6.J.7.g.27605'), ('Develop and test guidance and autopilot algorithms, including sensor technologies and radar waveforms for high fidelity perception applications.', 'A6.G.0.z.25090'), ('Practical experience in solving complex real-world problems using techniques such as deep learning, AI, robotics, graphics, computer vision, and cloud computing.', 'A6.D.1.e.23146'), ('Develop and apply machine learning methods, including predictive modeling, clustering, and regression techniques.', 'A6.J.11.g.29851'), ('Proficient in implementing and evaluating perception algorithms for object detection and tracking using various sensing modalities such as radar, lidar, and visual systems.', 'A6.A.10.c.25327'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805')]</t>
+          <t>[('Design, develop, and deploy AI and machine learning models and algorithms for various applications.', 'A6.J.4.d.29855'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Strong understanding of data structures, algorithms, software design principles, and best practices for building efficient systems.', 'A6.A.9.a.24181'), ('Expertise in the development and implementation of self-driving vehicles, focusing on enhancing urban mobility, safety, and freedom of movement through a hybrid network of autonomous and human-driven transportation.', 'A6.F.6.h.25093'), ('Develop, implement, and optimize speech recognition and natural language processing systems, including handling voice command recognition, speech-to-text functionality, and related algorithms.', 'A6.J.11.e.28355'), ('Design, develop, and implement advanced AI and ML models and algorithms to solve complex business problems.', 'A6.J.7.g.27605'), ('Apply advanced statistical and predictive modeling techniques to build, maintain, and improve multiple real-time decision systems.', 'A6.C.11.d.27773'), ('Develop and test guidance and autopilot algorithms, including sensor technologies and radar waveforms for high fidelity perception applications.', 'A6.G.0.z.25090'), ('Design, implement, and optimize perception algorithms and models for object detection, tracking, classification, and segmentation using camera and LiDAR data.', 'A6.G.0.z.28253'), ('Practical experience in solving complex real-world problems using techniques such as deep learning, AI, robotics, graphics, computer vision, and cloud computing.', 'A6.D.1.e.23146'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Develop and apply machine learning methods, including predictive modeling, clustering, and regression techniques.', 'A6.J.11.g.29851'), ('Support functional disciplines with all aspects related to ADAS algorithms and perception algorithms.', 'A6.J.9.c.24921'), ('Proficient in implementing and evaluating perception algorithms for object detection and tracking using various sensing modalities such as radar, lidar, and visual systems.', 'A6.A.10.c.25327'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805')]</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -14587,25 +14587,25 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="S84" t="n">
         <v>13</v>
       </c>
       <c r="T84" t="n">
-        <v>0.658</v>
+        <v>0.663</v>
       </c>
       <c r="U84" t="n">
-        <v>0.698</v>
+        <v>0.717</v>
       </c>
       <c r="V84" t="n">
-        <v>0.669</v>
+        <v>0.671</v>
       </c>
       <c r="W84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X84" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Ability to apply a deep understanding of machine learning, information retrieval, and natural language processing, along with strong prototyping skills and effective communication of complex algorithms and advancements in AI technology.', 'A6.J.11.b.22078'), ('Possesses basic knowledge and experience in AI, machine learning, and data science principles, along with an understanding of their applications in data analysis.', 'A6.A.16.b.28594'), ('Knowledgeable in responsible AI practices, ethical considerations, bias mitigation, and regulatory compliance in AI development and deployment.', 'A6.G.2.k.29782'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Develop and apply machine learning frameworks and libraries.', 'A6.G.0.f.29843'), ('Leads the development of advanced AI and machine learning models to address complex business challenges.', 'A6.I.0.c.29579'), ('Ability to work on innovative and impactful AI-driven machine learning projects that shape the future of technology.', 'A6.J.4.i.26325'), ('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185'), ('Develop and apply machine learning and artificial intelligence techniques in robotics and computer vision.', 'A6.J.12.d.28754'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Design, develop, and deploy AI and machine learning models and algorithms for various applications.', 'A6.J.4.d.29855')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Possesses expert knowledge of human-computer interaction principles.', 'A6.A.3.c.25588'), ('Ability to apply a deep understanding of machine learning, information retrieval, and natural language processing, along with strong prototyping skills and effective communication of complex algorithms and advancements in AI technology.', 'A6.J.11.b.22078'), ('Possesses basic knowledge and experience in AI, machine learning, and data science principles, along with an understanding of their applications in data analysis.', 'A6.A.16.b.28594'), ('Knowledgeable in responsible AI practices, ethical considerations, bias mitigation, and regulatory compliance in AI development and deployment.', 'A6.G.2.k.29782'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Develop and apply machine learning frameworks and libraries.', 'A6.G.0.f.29843'), ('Leads the development of advanced AI and machine learning models to address complex business challenges.', 'A6.I.0.c.29579'), ('Ability to work on innovative and impactful AI-driven machine learning projects that shape the future of technology.', 'A6.J.4.i.26325'), ('Demonstrates commitment to professional growth and development through continuous learning, training, and advancement opportunities in AI and related fields.', 'A6.H.1.f.23981'), ('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185'), ('Develop and apply machine learning and artificial intelligence techniques in robotics and computer vision.', 'A6.J.12.d.28754'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Design, develop, and deploy AI and machine learning models and algorithms for various applications.', 'A6.J.4.d.29855')]</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -14711,25 +14711,25 @@
         </is>
       </c>
       <c r="R85" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
       </c>
       <c r="T85" t="n">
-        <v>0.701</v>
+        <v>0.681</v>
       </c>
       <c r="U85" t="n">
         <v>0.669</v>
       </c>
       <c r="V85" t="n">
-        <v>0.701</v>
+        <v>0.681</v>
       </c>
       <c r="W85" t="n">
         <v>6</v>
       </c>
       <c r="X85" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86">
@@ -14835,17 +14835,17 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
+          <t>[('6448', 'Administer oral, written, or performance tests to measure progress and to evaluate training effectiveness.')]</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>[('Ability to create and implement machine learning algorithms and tools to address specific needs and processes.', 'A6.J.11.b.28982')]</t>
+          <t>[('Demonstrates a strong drive to learn, master, and apply new programming, data analysis techniques, and technologies to solve problems.', 'A6.J.0.k.22471'), ('Demonstrates independent and strategic problem-solving skills in planning and decision making.', 'A6.B.3.b.13430'), ('Ability to create and implement machine learning algorithms and tools to address specific needs and processes.', 'A6.J.11.b.28982')]</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -14854,25 +14854,25 @@
         </is>
       </c>
       <c r="R86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S86" t="n">
         <v>7</v>
       </c>
       <c r="T86" t="n">
-        <v>0.675</v>
+        <v>0.489</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>0.675</v>
+        <v>0.477</v>
       </c>
       <c r="W86" t="n">
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('23695', 'Plan and establish schedules.'), ('8967', 'Examine theories, such as those of probability and inference, to discover mathematical bases for new or improved methods of obtaining and evaluating numerical data.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.')]</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>[('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706')]</t>
+          <t>[('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Knowledge of reinforcement learning algorithms and unsupervised learning techniques, including understanding of regularization, embeddings, loss functions, and optimization strategies.', 'A6.A.16.b.29272'), ('Design and create logical and physical databases using relational database principles.', 'A6.E.3.f.18280'), ('Experience with graph databases, semantic layers, and data ontologies.', 'A6.E.3.f.21813'), ('Apply causal inference and exploratory data analysis techniques in statistical analysis and model development.', 'A6.C.4.k.21007'), ('Demonstrates mathematical aptitude in machine learning, computer vision, formal methods, and related advanced topics such as graph neural networks and causal discovery.', 'A6.A.16.c.24938'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706')]</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -14974,25 +14974,25 @@
         </is>
       </c>
       <c r="R87" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S87" t="n">
         <v>2</v>
       </c>
       <c r="T87" t="n">
-        <v>0.628</v>
+        <v>0.536</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="V87" t="n">
-        <v>0.628</v>
+        <v>0.544</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X87" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('16518', 'Plan mobile robot paths and teach path plans to robots.'), ('18967', 'Develop conceptual, logical, or physical network designs.'), ('23695', 'Plan and establish schedules.'), ('7368', 'Develop computational methods for solving problems that occur in areas of science and engineering or that come from applications in business or industry.')]</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>[('Familiarity with reinforcement learning techniques, applications, and advanced optimization methods in various contexts.', 'A6.A.16.b.28784'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706')]</t>
+          <t>[('Knowledge of reinforcement learning algorithms and unsupervised learning techniques, including understanding of regularization, embeddings, loss functions, and optimization strategies.', 'A6.A.16.b.29272'), ('Familiarity with reinforcement learning techniques, applications, and advanced optimization methods in various contexts.', 'A6.A.16.b.28784'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Develop and implement semantic technologies and ontologies for knowledge graphs and informatics workflows.', 'A6.E.0.j.25194'), ('Develop services and inference engine for automation agents, including techniques for reasoning, planning, and modeling workflows.', 'A6.J.5.c.27046'), ('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151')]</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -15086,25 +15086,25 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
       </c>
       <c r="T88" t="n">
-        <v>0.669</v>
+        <v>0.663</v>
       </c>
       <c r="U88" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.663</v>
       </c>
       <c r="V88" t="n">
-        <v>0.669</v>
+        <v>0.663</v>
       </c>
       <c r="W88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X88" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -15186,17 +15186,17 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('8018', 'Start gaming equipment that randomly selects numbered balls and announce winning numbers and colors.')]</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>[('processing information', 'S2.4')]</t>
+          <t>[('conduct web searches', 'T1.3'), ('processing information', 'S2.4')]</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>[('Advanced knowledge and experience utilizing a variety of machine learning techniques such as clustering, decision tree learning, and neural networks, including their real-world advantages and drawbacks in supervised and unsupervised learning applications.', 'A6.A.16.b.28737'), ('Experience with neural deep learning methods and machine learning.', 'A6.A.16.c.29894'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749')]</t>
+          <t>[('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Advanced knowledge and experience utilizing a variety of machine learning techniques such as clustering, decision tree learning, and neural networks, including their real-world advantages and drawbacks in supervised and unsupervised learning applications.', 'A6.A.16.b.28737'), ('Experience with neural deep learning methods and machine learning.', 'A6.A.16.c.29894'), ('Strong knowledge and understanding of data structures, algorithms, and object-oriented programming.', 'A6.A.9.c.22782'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749')]</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -15205,25 +15205,25 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S89" t="n">
         <v>8</v>
       </c>
       <c r="T89" t="n">
-        <v>0.785</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="U89" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="V89" t="n">
-        <v>0.785</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="W89" t="n">
         <v>2</v>
       </c>
       <c r="X89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>[('18974', 'Estimate time and materials needed to complete projects.')]</t>
+          <t>[('14633', 'Design computers and the software that runs them.'), ('14711', 'Select programming languages, design tools, or applications.'), ('18632', 'Establish and enforce administration policies and rules governing student behavior.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('18974', 'Estimate time and materials needed to complete projects.'), ('21751', 'Develop presentations on threat intelligence.')]</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>[('Basic knowledge of machine learning algorithms, artificial intelligence, and statistical methods.', 'A6.A.16.c.29897'), ('Develop and utilize natural language processing tools and techniques, including large language models and transformer architectures.', 'A6.J.4.h.29668'), ('Develop and apply machine learning and artificial intelligence techniques in robotics and computer vision.', 'A6.J.12.d.28754'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589'), ('Utilize advanced knowledge of machine learning algorithms, data structures, and software design principles to support AI/ML solutions.', 'A6.A.16.b.28280'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Knowledge of supervised, unsupervised, and deep learning techniques, including their real-world applications, advantages, and drawbacks.', 'A6.A.16.b.27805'), ('Expertise in deep learning methods and deep reinforcement learning applications.', 'A6.A.16.a.29698'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Familiarity with and background knowledge in artificial intelligence and machine learning, including recent developments and emerging technologies.', 'A6.J.0.p.26836'), ('Proficient in machine learning and deep learning techniques for applications in computer vision, including object segmentation, detection, and recognition, particularly in the context of self-driving cars.', 'A6.A.10.c.26636'), ('Ability to develop machine learning and artificial intelligence techniques and algorithms to solve complex business problems using both supervised and unsupervised methodologies.', 'A6.J.6.i.26996')]</t>
+          <t>[('Basic knowledge of machine learning algorithms, artificial intelligence, and statistical methods.', 'A6.A.16.c.29897'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Apply computer science methods and techniques to store, manipulate, transform, or present information using computer systems.', 'A6.A.3.b.25374'), ('Develop and utilize natural language processing tools and techniques, including large language models and transformer architectures.', 'A6.J.4.h.29668'), ('Develop and apply machine learning and artificial intelligence techniques in robotics and computer vision.', 'A6.J.12.d.28754'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589'), ('Utilize advanced knowledge of machine learning algorithms, data structures, and software design principles to support AI/ML solutions.', 'A6.A.16.b.28280'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Develop, implement, and evaluate linear and logistic regression and machine learning models.', 'A6.J.11.h.25160'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879'), ('Knowledge of supervised, unsupervised, and deep learning techniques, including their real-world applications, advantages, and drawbacks.', 'A6.A.16.b.27805'), ('Expertise in deep learning methods and deep reinforcement learning applications.', 'A6.A.16.a.29698'), ('Build and optimize algorithms and models to enhance the marketplace impact and operational efficiency of autonomous vehicles.', 'A6.E.1.f.28214'), ('Experience in developing and troubleshooting autonomous systems through robotics competitions and embedded processors, including sensor integration.', 'A6.F.7.a.27419'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Ability to identify, evaluate, and refine methods, models, and algorithms for developing accurate and anticipatory intelligence analysis solutions.', 'A6.J.11.e.22676'), ('Familiarity with and background knowledge in artificial intelligence and machine learning, including recent developments and emerging technologies.', 'A6.J.0.p.26836'), ('Ability to stay current with emerging AI technologies and methodologies, integrating them to enhance business operations and drive innovation.', 'A6.J.2.s.26286'), ('Proficient in machine learning and deep learning techniques for applications in computer vision, including object segmentation, detection, and recognition, particularly in the context of self-driving cars.', 'A6.A.10.c.26636'), ('Ability to develop machine learning and artificial intelligence techniques and algorithms to solve complex business problems using both supervised and unsupervised methodologies.', 'A6.J.6.i.26996')]</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -15462,25 +15462,25 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="S90" t="n">
         <v>27</v>
       </c>
       <c r="T90" t="n">
-        <v>0.695</v>
+        <v>0.669</v>
       </c>
       <c r="U90" t="n">
-        <v>0.71</v>
+        <v>0.702</v>
       </c>
       <c r="V90" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.664</v>
       </c>
       <c r="W90" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X90" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91">
@@ -15597,17 +15597,17 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
+          <t>[('16530', 'Design robotic systems, such as automatic vehicle control, autonomous vehicles, advanced displays, advanced sensing, robotic platforms, computer vision, or telematics systems.'), ('16208', 'Devise missions, challenges, or puzzles to be encountered in game play.')]</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Work on robotics-related topics such as computer vision, deep learning, machine learning, planning, human-machine teaming, and multi-robot systems.', 'A6.A.10.c.26884')]</t>
+          <t>[('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Work on robotics-related topics such as computer vision, deep learning, machine learning, planning, human-machine teaming, and multi-robot systems.', 'A6.A.10.c.26884'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Design and create logical and physical databases using relational database principles.', 'A6.E.3.f.18280'), ('Proficient in planning and knowledge representation tools and methods, with an understanding of sampling processes and critical theoretical frameworks.', 'A6.B.5.c.18071'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205')]</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -15616,25 +15616,25 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S91" t="n">
         <v>8</v>
       </c>
       <c r="T91" t="n">
-        <v>0.664</v>
+        <v>0.609</v>
       </c>
       <c r="U91" t="n">
-        <v>0.605</v>
+        <v>0.646</v>
       </c>
       <c r="V91" t="n">
-        <v>0.664</v>
+        <v>0.642</v>
       </c>
       <c r="W91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X91" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
@@ -15725,17 +15725,17 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
+          <t>[('7567', 'Formulate and implement training programs, applying principles of learning and individual differences.'), ('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>[('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800')]</t>
+          <t>[('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Strong interest in artificial intelligence and machine learning, including concepts, algorithms, applications in various fields, and continuous learning in emerging technologies.', 'A6.A.16.a.28899'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800')]</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -15744,25 +15744,25 @@
         </is>
       </c>
       <c r="R92" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
       </c>
       <c r="T92" t="n">
-        <v>0.708</v>
+        <v>0.702</v>
       </c>
       <c r="U92" t="n">
-        <v>0.713</v>
+        <v>0.705</v>
       </c>
       <c r="V92" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="W92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X92" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -15856,17 +15856,17 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
+          <t>[('16789', 'Design and apply bioinformatics algorithms including unsupervised and supervised machine learning, dynamic programming, or graphic algorithms.')]</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Perform data exploration and analysis using machine learning algorithms, linear algebra, probability theory, statistics, and optimization theory.', 'A6.J.1.k.26876'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036')]</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -15875,25 +15875,25 @@
         </is>
       </c>
       <c r="R93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
       </c>
       <c r="T93" t="n">
-        <v>0.65</v>
+        <v>0.641</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>0.65</v>
+        <v>0.641</v>
       </c>
       <c r="W93" t="n">
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -16095,7 +16095,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('6261', "Evaluate and grade students' class work, performances, projects, assignments, and papers.")]</t>
+          <t>[('19637', 'Research computerized automotive applications, such as telemetrics, intelligent transportation systems, artificial intelligence, or automatic control.'), ('22606', 'Advertise services using media such as internet advertising and brochures.'), ('16960', 'Evaluate new technologies and methods to make recommendations regarding their use.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.'), ('21058', 'Evaluate robotic systems or prototypes.'), ('7277', 'Analyze data gathered and develop solutions or alternative methods of proceeding.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('1538', 'Compile and interpret results of tests and analyses.'), ('14669', 'Verify stability, interoperability, portability, security, or scalability of system architecture.'), ('6261', "Evaluate and grade students' class work, performances, projects, assignments, and papers.")]</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -16105,7 +16105,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>[('Research and apply modern AI capabilities in machine learning, algorithms, and ethical considerations while assisting with robotic solutions.', 'A6.A.10.a.28513'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Develop data-driven algorithms and models for classification, clustering, regression, anomaly detection, and failure prediction.', 'A6.J.11.g.26934'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Develop automated techniques for the design and evaluation of AI agents and analyze usage data to improve the effectiveness of AI solutions.', 'A6.F.6.e.29441'), ('Apply machine learning techniques and statistical modeling to large datasets.', 'A6.J.14.f.29871'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Understand machine learning concepts and their implications for data infrastructure.', 'A6.A.16.c.29770'), ('Apply natural language processing (NLP) techniques for tasks such as sentiment analysis, text classification, entity recognition, and topic modeling to analyze and interpret textual data.', 'A6.G.0.n.27966')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Research and apply modern AI capabilities in machine learning, algorithms, and ethical considerations while assisting with robotic solutions.', 'A6.A.10.a.28513'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Develop and apply object-oriented design, data structures, and algorithms to build systems at scale.', 'A6.G.0.e.20979'), ('Develop data-driven algorithms and models for classification, clustering, regression, anomaly detection, and failure prediction.', 'A6.J.11.g.26934'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Knowledge of data governance, security, privacy, and ethical practices in AI development, including addressing issues like data poisoning and model theft.', 'A6.G.2.k.27697'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504'), ('Ability to identify, evaluate, and refine methods, models, and algorithms for developing accurate and anticipatory intelligence analysis solutions.', 'A6.J.11.e.22676'), ('Develop automated techniques for the design and evaluation of AI agents and analyze usage data to improve the effectiveness of AI solutions.', 'A6.F.6.e.29441'), ('Apply machine learning techniques and statistical modeling to large datasets.', 'A6.J.14.f.29871'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Understand machine learning concepts and their implications for data infrastructure.', 'A6.A.16.c.29770'), ('Develop and optimize computer vision technologies and algorithms for vision tasks in research or industrial settings.', 'A6.G.0.g.29625'), ('Model vision problems in the areas of object detection, facial recognition, and temporal machine learning.', 'A6.A.10.c.26684'), ('Apply natural language processing (NLP) techniques for tasks such as sentiment analysis, text classification, entity recognition, and topic modeling to analyze and interpret textual data.', 'A6.G.0.n.27966'), ('Familiarity with natural language processing (NLP) techniques, models, and frameworks, including text analytics, machine learning concepts, and applications in various domains.', 'A6.A.16.c.28107'), ('Develop and utilize natural language processing tools and techniques, including large language models and transformer architectures.', 'A6.J.4.h.29668'), ('Incorporate generative AI tools and techniques into customized applications, including voice and chat bots, while engaging in prompt engineering, model selection, and data preparation.', 'A6.J.2.m.28813'), ('Gain exposure to machine learning, artificial intelligence, and related technologies and applications.', 'A6.A.16.a.29554'), ('Ability to establish and govern data and algorithms for analysis and automated decision-making, ensuring quality, trust, and ethical standards in AI technology.', 'A6.J.0.n.27567'), ('Possesses in-depth knowledge of AI, machine learning, and data science concepts, including algorithmic biases, tools, and techniques for effective application and collaboration in related fields.', 'A6.A.16.b.28709'), ('Understand and apply knowledge of artificial intelligence and GenAI tools.', 'A6.A.16.c.29444')]</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -16114,25 +16114,25 @@
         </is>
       </c>
       <c r="R94" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
       </c>
       <c r="T94" t="n">
-        <v>0.715</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="U94" t="n">
-        <v>0.674</v>
+        <v>0.678</v>
       </c>
       <c r="V94" t="n">
-        <v>0.703</v>
+        <v>0.677</v>
       </c>
       <c r="W94" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="X94" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('21058', 'Evaluate robotic systems or prototypes.')]</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and implement machine learning and artificial intelligence solutions and algorithms.', 'A6.J.0.b.29816'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Knowledge of AI technologies and their applications in customer care, scientific research, marketing, decision-making systems, and innovative solutions.', 'A6.D.1.e.28844'), ('Develop and implement machine learning and artificial intelligence solutions and algorithms.', 'A6.J.0.b.29816'), ('Demonstrate familiarity with AI technologies, including machine learning, natural language processing, and computer vision.', 'A6.A.16.c.28895'), ('Possesses in-depth knowledge of AI, machine learning, and data science concepts, including algorithmic biases, tools, and techniques for effective application and collaboration in related fields.', 'A6.A.16.b.28709'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Possesses a strong passion for technology, including computer vision, drones, data utilization, and continuous process improvement.', 'A6.B.0.r.18017'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Familiarity with ethical AI principles, bias mitigation strategies, and responsible AI practices and frameworks within organizational contexts.', 'A6.G.2.k.29185')]</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -16234,25 +16234,25 @@
         </is>
       </c>
       <c r="R95" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S95" t="n">
         <v>7</v>
       </c>
       <c r="T95" t="n">
-        <v>0.724</v>
+        <v>0.681</v>
       </c>
       <c r="U95" t="n">
         <v>0.75</v>
       </c>
       <c r="V95" t="n">
-        <v>0.724</v>
+        <v>0.681</v>
       </c>
       <c r="W95" t="n">
         <v>2</v>
       </c>
       <c r="X95" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('7367', 'Apply mathematical theories and techniques to the solution of practical problems in business, engineering, the sciences, or other fields.'), ('17719', 'Train bioinformatics staff or researchers in the use of databases.'), ('374', 'Identify and document goals, anticipated progress, and plans for reevaluation.')]</t>
+          <t>[('21971', 'Train students to use drafting machines and to prepare schematic diagrams, block diagrams, control drawings, logic diagrams, integrated circuit drawings, or interconnection diagrams.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('7367', 'Apply mathematical theories and techniques to the solution of practical problems in business, engineering, the sciences, or other fields.'), ('17719', 'Train bioinformatics staff or researchers in the use of databases.'), ('20742', 'Study industrial processes to maximize the efficiency of equipment applications, including equipment placement.'), ('21247', 'Compile or develop materials to submit to granting or other funding organizations.'), ('374', 'Identify and document goals, anticipated progress, and plans for reevaluation.'), ('16790', 'Create novel computational approaches and analytical tools as required by research goals.'), ('16257', 'Develop or implement data analysis algorithms.'), ('17716', 'Maintain awareness of new and emerging computational methods and technologies.'), ('8957', 'Prepare data for processing by organizing information, checking for inaccuracies, and adjusting and weighting the raw data.'), ('20327', 'Improve search-related activities through ongoing analysis, experimentation, or optimization tests, using A/B or multivariate methods.'), ('16521', 'Debug robotics programs.')]</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>[('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Manage and develop pattern recognition and predictive modeling techniques.', 'A6.J.11.f.29584'), ('Proficient in maintaining and managing training data, records, and materials, including generating reports and ensuring content accuracy and relevance.', 'A6.E.2.e.17996'), ('Apply tools, technologies, and manufacturing processes for various systems and applications.', 'A6.F.6.d.17327'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Familiarize and apply Generative AI techniques, tools, and frameworks for automation, data processing, and AI-enabled product development.', 'A6.G.2.a.29534'), ('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Work with Python and its machine learning libraries and frameworks for data processing and orchestration.', 'A6.B.8.a.27410'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Develop and implement computer vision algorithms for object detection, feature tracking, and image processing using relevant hardware and software technologies.', 'A6.G.0.g.29612'), ('Possess a deep understanding of machine learning models, AI validation methodologies, and advanced AI techniques, such as reinforcement learning and generative adversarial networks.', 'A6.A.16.c.28701'), ('Develop intelligent programs, cognitive applications, and algorithms for data analysis and automation using AI techniques such as deep learning, generative AI, natural language processing, and image processing.', 'A6.J.11.b.29680'), ('Develop and maintain AI-driven and data analysis tools to enhance operational efficiency.', 'A6.F.1.e.28823'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Demonstrate familiarity with AI frameworks and libraries such as TensorFlow, PyTorch, and Keras for inferencing and training.', 'A6.A.22.e.27871'), ('Optimize and fine-tune AI models for performance, accuracy, scalability, and efficiency.', 'A6.J.2.q.28543')]</t>
+          <t>[('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Ability to apply best practices for artificial intelligence and machine learning.', 'A6.A.16.c.29427'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Manage and develop pattern recognition and predictive modeling techniques.', 'A6.J.11.f.29584'), ('Proficient in maintaining and managing training data, records, and materials, including generating reports and ensuring content accuracy and relevance.', 'A6.E.2.e.17996'), ('Apply tools, technologies, and manufacturing processes for various systems and applications.', 'A6.F.6.d.17327'), ('Demonstrates a strong passion for machine learning and actively invests time in learning, researching, and experimenting with new innovations in the field.', 'A6.A.16.b.27233'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Familiarize and apply Generative AI techniques, tools, and frameworks for automation, data processing, and AI-enabled product development.', 'A6.G.2.a.29534'), ('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Work with Python and its machine learning libraries and frameworks for data processing and orchestration.', 'A6.B.8.a.27410'), ('Experience with basic statistics and regression algorithms.', 'A6.A.12.d.25053'), ('Develop and implement computer vision algorithms for object detection, feature tracking, and image processing using relevant hardware and software technologies.', 'A6.G.0.g.29612'), ('Possess a deep understanding of machine learning models, AI validation methodologies, and advanced AI techniques, such as reinforcement learning and generative adversarial networks.', 'A6.A.16.c.28701'), ('Develop intelligent programs, cognitive applications, and algorithms for data analysis and automation using AI techniques such as deep learning, generative AI, natural language processing, and image processing.', 'A6.J.11.b.29680'), ('Develop and maintain AI-driven and data analysis tools to enhance operational efficiency.', 'A6.F.1.e.28823'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Write clean, maintainable, and efficient code for AI/ML model training, evaluation, and serving.', 'A6.J.13.i.29457'), ('Demonstrate familiarity with AI frameworks and libraries such as TensorFlow, PyTorch, and Keras for inferencing and training.', 'A6.A.22.e.27871'), ('Optimize and fine-tune AI models for performance, accuracy, scalability, and efficiency.', 'A6.J.2.q.28543')]</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -16408,25 +16408,25 @@
         </is>
       </c>
       <c r="R96" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S96" t="n">
         <v>16</v>
       </c>
       <c r="T96" t="n">
-        <v>0.645</v>
+        <v>0.649</v>
       </c>
       <c r="U96" t="n">
         <v>0.6929999999999999</v>
       </c>
       <c r="V96" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="W96" t="n">
         <v>4</v>
       </c>
       <c r="X96" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -16528,7 +16528,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>[('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Expertise in deep learning methods and deep reinforcement learning applications.', 'A6.A.16.a.29698'), ('Design and develop algorithms for generative models using deep learning techniques and natural language processing (NLP).', 'A6.J.10.a.29664')]</t>
+          <t>[('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Experience in deep learning algorithms for search and recommendation systems.', 'A6.A.16.c.27070'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Implement algorithms for data analysis and processing.', 'A6.J.8.f.29898'), ('Expertise in deep learning methods and deep reinforcement learning applications.', 'A6.A.16.a.29698'), ('Design and develop algorithms for generative models using deep learning techniques and natural language processing (NLP).', 'A6.J.10.a.29664')]</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -16537,25 +16537,25 @@
         </is>
       </c>
       <c r="R97" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S97" t="n">
         <v>14</v>
       </c>
       <c r="T97" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="U97" t="n">
-        <v>0.766</v>
+        <v>0.787</v>
       </c>
       <c r="V97" t="n">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
       <c r="W97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('17340', 'Obtain, distribute, or maintain low vision devices.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16124', 'Map data between source systems, data warehouses, and data marts.'), ('16115', 'Develop and document database architectures.'), ('17710', 'Confer with researchers, clinicians, or information technology staff to determine data needs and programming requirements and to provide assistance with database-related research activities.'), ('17340', 'Obtain, distribute, or maintain low vision devices.'), ('16257', 'Develop or implement data analysis algorithms.'), ('8956', 'Analyze and interpret statistical data to identify significant differences in relationships among sources of information.'), ('21823', 'Analyze, manipulate, or process large sets of data using statistical software.'), ('14673', 'Identify system data, hardware, or software components required to meet user needs.')]</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Research and implement state-of-the-art AI algorithms and techniques to enhance model performance and optimize accuracy, speed, and robustness.', 'A6.J.2.m.28729'), ('Knowledge of supervised, unsupervised, and deep learning techniques, including their real-world applications, advantages, and drawbacks.', 'A6.A.16.b.27805'), ('Support the development, testing, and deployment of AI algorithms and models.', 'A6.J.5.c.29846'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Deploy NLP and ML models in production environments, ensuring scalability and performance.', 'A6.J.13.a.27069'), ('Design and implement data models and integrations for structured and unstructured data.', 'A6.G.0.j.27803'), ('Develop and apply statistical and data mining techniques.', 'A6.C.4.r.28458'), ('Implement and apply machine learning methodologies for clustering, classification, regression, and anomaly detection, including training and validating predictive models.', 'A6.D.1.k.28888'), ('Performs data mining activities to meet customer requirements and specifications.', 'A6.C.7.f.29189'), ('Design, develop, test, and deploy scalable data solutions and architecture to support data protection, risk reduction initiatives, and new data models.', 'A6.G.0.p.22050'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Implement reinforcement learning algorithms using Python.', 'A6.J.8.f.29896'), ('Develop and deploy scalable and production-ready computer vision systems.', 'A6.G.0.g.29736'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Ability to develop and execute a comprehensive AI and data strategy that aligns with organizational goals and objectives.', 'A6.J.4.i.24754'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Integrate AI services and algorithms with advanced data solutions and enterprise infrastructure.', 'A6.J.2.g.29674'), ('Develop and apply deep learning optimization and acceleration techniques.', 'A6.G.0.f.29603'), ('Knowledgeable in responsible AI practices, ethical considerations, bias mitigation, and regulatory compliance in AI development and deployment.', 'A6.G.2.k.29782'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Develop and apply statistical and predictive modeling concepts, machine learning approaches, clustering and classification techniques, and recommendation and optimization algorithms.', 'A6.J.11.g.26277')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Research and implement state-of-the-art AI algorithms and techniques to enhance model performance and optimize accuracy, speed, and robustness.', 'A6.J.2.m.28729'), ('Knowledge of supervised, unsupervised, and deep learning techniques, including their real-world applications, advantages, and drawbacks.', 'A6.A.16.b.27805'), ('Support the development, testing, and deployment of AI algorithms and models.', 'A6.J.5.c.29846'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Proficient in working with and normalizing unstructured textual and raw data.', 'A6.D.0.c.27478'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Deploy NLP and ML models in production environments, ensuring scalability and performance.', 'A6.J.13.a.27069'), ('Develop and validate source-to-target data mappings.', 'A6.E.0.j.25141'), ('Design and implement data models and integrations for structured and unstructured data.', 'A6.G.0.j.27803'), ('Develop and optimize search algorithms, indexing, and retrieval systems for improved search quality and performance.', 'A6.F.1.e.20036'), ('Develop and apply statistical and data mining techniques.', 'A6.C.4.r.28458'), ('Implement and apply machine learning methodologies for clustering, classification, regression, and anomaly detection, including training and validating predictive models.', 'A6.D.1.k.28888'), ('Performs data mining activities to meet customer requirements and specifications.', 'A6.C.7.f.29189'), ('Design, develop, test, and deploy scalable data solutions and architecture to support data protection, risk reduction initiatives, and new data models.', 'A6.G.0.p.22050'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Implement reinforcement learning algorithms using Python.', 'A6.J.8.f.29896'), ('Develop and deploy scalable and production-ready computer vision systems.', 'A6.G.0.g.29736'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Ability to drive the adoption and implementation of AI, machine learning, and automation tools to enhance workflows, operational processes, and data management across the organization.', 'A6.J.4.i.26045'), ('Ability to develop and execute a comprehensive AI and data strategy that aligns with organizational goals and objectives.', 'A6.J.4.i.24754'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Integrate AI services and algorithms with advanced data solutions and enterprise infrastructure.', 'A6.J.2.g.29674'), ('Develop and apply deep learning optimization and acceleration techniques.', 'A6.G.0.f.29603'), ('Knowledgeable in responsible AI practices, ethical considerations, bias mitigation, and regulatory compliance in AI development and deployment.', 'A6.G.2.k.29782'), ('Ability to leverage AI and machine learning technologies to enhance organizational efficiency, support commercial goals, and drive continuous improvement through optimization and knowledge management.', 'A6.J.2.d.25130'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Possesses an understanding of data needs for AI algorithms and knowledge of AI tools for data analysis and process optimization.', 'A6.J.12.e.25106'), ('Develop and apply statistical and predictive modeling concepts, machine learning approaches, clustering and classification techniques, and recommendation and optimization algorithms.', 'A6.J.11.g.26277'), ('Analyze and interpret data using various software tools related to exercise and nutrition.', 'A6.A.14.e.17576'), ('Provides technical and scientific leadership in computer vision, large language models, and generative image technologies.', 'A6.J.2.n.27489'), ('Ensure seamless integration of AI solutions, models, and components with existing systems, infrastructures, and business processes.', 'A6.J.2.h.29313'), ('Ability to contribute to the development of innovative autonomous vehicles that enhance safety and connectivity in transportation.', 'A6.F.6.l.27294'), ('Knowledge of data governance, security, privacy, and ethical practices in AI development, including addressing issues like data poisoning and model theft.', 'A6.G.2.k.27697')]</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -16847,25 +16847,25 @@
         </is>
       </c>
       <c r="R98" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="S98" t="n">
         <v>21</v>
       </c>
       <c r="T98" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.649</v>
       </c>
       <c r="U98" t="n">
-        <v>0.719</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V98" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="W98" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X98" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="99">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
+          <t>[('22393', 'Distribute or collect tests or homework assignments.'), ('16208', 'Devise missions, challenges, or puzzles to be encountered in game play.')]</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>[('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Manage and develop pattern recognition and predictive modeling techniques.', 'A6.J.11.f.29584')]</t>
+          <t>[('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Ability to apply best practices for artificial intelligence and machine learning.', 'A6.A.16.c.29427'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Manage and develop pattern recognition and predictive modeling techniques.', 'A6.J.11.f.29584')]</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -16978,25 +16978,25 @@
         </is>
       </c>
       <c r="R99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
       </c>
       <c r="T99" t="n">
-        <v>0.73</v>
+        <v>0.722</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>0.73</v>
+        <v>0.722</v>
       </c>
       <c r="W99" t="n">
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
@@ -17107,7 +17107,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('20486', 'Plan layouts of structural architectural projects.'), ('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Demonstrates mathematical aptitude in machine learning, computer vision, formal methods, and related advanced topics such as graph neural networks and causal discovery.', 'A6.A.16.c.24938'), ('Maintain a solid foundation in data structures, algorithms, and design patterns.', 'A6.A.9.c.24888'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrate knowledge of AI and machine learning techniques, including algorithms, frameworks, and model development.', 'A6.A.16.c.29124'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Demonstrates mathematical aptitude in machine learning, computer vision, formal methods, and related advanced topics such as graph neural networks and causal discovery.', 'A6.A.16.c.24938'), ('Implement algorithms for data analysis and processing.', 'A6.J.8.f.29898'), ('Maintain a solid foundation in data structures, algorithms, and design patterns.', 'A6.A.9.c.24888'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Design and create logical and physical databases using relational database principles.', 'A6.E.3.f.18280'), ('A strong grasp of algorithms, data structures, software design principles, design patterns, and object-oriented programming concepts for efficient, scalable data processing and problem-solving.', 'A6.A.9.a.22140')]</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -17126,25 +17126,25 @@
         </is>
       </c>
       <c r="R100" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S100" t="n">
         <v>6</v>
       </c>
       <c r="T100" t="n">
-        <v>0.7</v>
+        <v>0.669</v>
       </c>
       <c r="U100" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="V100" t="n">
-        <v>0.7</v>
+        <v>0.666</v>
       </c>
       <c r="W100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X100" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
@@ -17305,17 +17305,17 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('22449', 'Present and make recommendations regarding course design, technology, and instruction delivery options.'), ('11059', 'Teach writing classes.'), ('22069', 'Assist nanoscientists or engineers in writing process specifications or documentation.'), ('1349', 'Operate computer-assisted engineering or design software or equipment to perform engineering tasks.'), ('10907', 'Design computer simulations to model physical data so that it can be better understood.'), ('9389', 'Select materials and components to be used, based on device design.')]</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>[('writing and submitting instructions, specifications and programmes for computers.', 'S5.1'), ('mathematical ability', 'T1.2'), ('collaborate on tasks', 'T3.1'), ('address audiences', 'T3.4'), ('demonstrate technical abilities', 'T6.6')]</t>
+          <t>[('writing and submitting instructions, specifications and programmes for computers.', 'S5.1'), ('mathematical ability', 'T1.2'), ('collaborate on tasks', 'T3.1'), ('address audiences', 'T3.4'), ('demonstrate technical abilities', 'T6.6'), ('making a choice from several alternative possibilities.', 'S4.9')]</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Ability to apply advanced principles of computer science, mathematics, and engineering to develop, validate, and analyze software solutions and data in support of various scientific and technical applications.', 'A6.A.3.b.23192'), ('Ability to identify business and system requirements and recommend appropriate solutions through process mapping and functional specifications.', 'A6.F.6.b.14847'), ('Ability to quickly learn and guide teams in adopting the latest technologies and techniques in computer science.', 'A6.H.0.a.22943'), ('Strong foundation in computer science principles, including data structures, algorithm design, complexity analysis, and problem-solving abilities.', 'A6.A.9.e.24492')]</t>
+          <t>[('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Ability to identify computer engineering problems and recommend corrective actions.', 'A6.G.6.c.27614'), ('Demonstrate proficiency in technical writing and communication to effectively present and teach diverse audiences about technical and scientific subjects.', 'A6.H.1.e.12160'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Conceive, develop, and implement AI and image analysis solutions to high-priority scientific problems.', 'A6.J.0.n.28338'), ('Expertise in reinforcement learning, multi-agent systems, and agent-based modeling to develop autonomous AI agents for complex decision-making.', 'A6.J.0.n.28841'), ('Design and create logical and physical databases using relational database principles.', 'A6.E.3.f.18280'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Ability to apply advanced principles of computer science, mathematics, and engineering to develop, validate, and analyze software solutions and data in support of various scientific and technical applications.', 'A6.A.3.b.23192'), ('Ability to identify business and system requirements and recommend appropriate solutions through process mapping and functional specifications.', 'A6.F.6.b.14847'), ('Ability to build intelligent, scalable systems and tools that solve real-world problems, drive data analysis, and create impactful user experiences.', 'A6.F.6.k.19489'), ('Ability to quickly learn and guide teams in adopting the latest technologies and techniques in computer science.', 'A6.H.0.a.22943'), ('Strong foundation in computer science principles, including data structures, algorithm design, complexity analysis, and problem-solving abilities.', 'A6.A.9.e.24492'), ('A robust comprehension of computer science fundamentals encompassing data structures, algorithms, programming languages, design patterns, principles, programming paradigms, and databases.', 'A6.A.9.e.20528')]</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -17324,25 +17324,25 @@
         </is>
       </c>
       <c r="R101" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="S101" t="n">
         <v>12</v>
       </c>
       <c r="T101" t="n">
-        <v>0.583</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="U101" t="n">
-        <v>0.668</v>
+        <v>0.729</v>
       </c>
       <c r="V101" t="n">
-        <v>0.669</v>
+        <v>0.633</v>
       </c>
       <c r="W101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X101" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>[('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Possesses deep and broad knowledge of core computer science fundamentals and concepts.', 'A6.A.9.e.28666'), ('Design and develop AI algorithms and solutions for various applications, including conversational systems, intelligent agents, and generative AI tools.', 'A6.J.4.d.29651'), ('Analyze and implement greedy algorithms and dynamic programming for graph-related problems.', 'A6.J.8.g.28931'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Design, implement, and validate machine learning models and techniques for real-world applications.', 'A6.J.11.b.29549'), ('Design and develop algorithms for generative models using deep learning techniques and natural language processing (NLP).', 'A6.J.10.a.29664')]</t>
+          <t>[('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Possesses deep and broad knowledge of core computer science fundamentals and concepts.', 'A6.A.9.e.28666'), ('Design and develop AI algorithms and solutions for various applications, including conversational systems, intelligent agents, and generative AI tools.', 'A6.J.4.d.29651'), ('Analyze and implement greedy algorithms and dynamic programming for graph-related problems.', 'A6.J.8.g.28931'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745'), ('Design, implement, and validate machine learning models and techniques for real-world applications.', 'A6.J.11.b.29549'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Design and develop algorithms for generative models using deep learning techniques and natural language processing (NLP).', 'A6.J.10.a.29664')]</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -17443,25 +17443,25 @@
         </is>
       </c>
       <c r="R102" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S102" t="n">
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>0.713</v>
+        <v>0.721</v>
       </c>
       <c r="U102" t="n">
-        <v>0.733</v>
+        <v>0.772</v>
       </c>
       <c r="V102" t="n">
-        <v>0.721</v>
+        <v>0.729</v>
       </c>
       <c r="W102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>[('8671', 'Prepare students for further development by encouraging them to explore learning opportunities and to persevere with challenging tasks.'), ('16518', 'Plan mobile robot paths and teach path plans to robots.'), ('14687', 'Communicate project information through presentations, technical reports, or white papers.')]</t>
+          <t>[('6466', 'Teach basic skills, such as color, shape, number and letter recognition, personal hygiene, and social skills.'), ('8671', 'Prepare students for further development by encouraging them to explore learning opportunities and to persevere with challenging tasks.'), ('22179', 'Maintain current knowledge of relevant research.'), ('219', 'Develop techniques for measuring and identifying trees.'), ('8967', 'Examine theories, such as those of probability and inference, to discover mathematical bases for new or improved methods of obtaining and evaluating numerical data.'), ('374', 'Identify and document goals, anticipated progress, and plans for reevaluation.'), ('21421', 'Interview or correspond with agents and claimants to correct errors or omissions and to investigate questionable claims.'), ('4457', 'Answer questions about game rules and casino policies.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16518', 'Plan mobile robot paths and teach path plans to robots.'), ('14687', 'Communicate project information through presentations, technical reports, or white papers.')]</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Apply causal inference and exploratory data analysis techniques in statistical analysis and model development.', 'A6.C.4.k.21007'), ('Strong understanding of machine learning algorithms and techniques, including regression, classification, clustering, deep learning, statistical modeling, data mining, and data preprocessing methods.', 'A6.A.16.b.29690'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Develop and implement object detection, classification, and segmentation algorithms for image and video analysis.', 'A6.G.0.g.28401'), ('Create and develop predictive models and machine-learning algorithms using various techniques.', 'A6.J.11.g.29774'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Develop and implement large language models (LLMs) for tasks in natural language processing, including training, fine-tuning, prompt engineering, and application in business workflows.', 'A6.J.10.a.29505'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Ability to share and apply knowledge, experience, and skills effectively.', 'A6.A.4.b.13239'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Create and implement applications using artificial intelligence solutions across various sectors, including medicine and construction.', 'A6.J.4.d.29737'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Expertise in natural language processing (NLP), including machine translation, conversational AI, and computational linguistics techniques.', 'A6.A.16.c.28715'), ('Implement and optimize graph algorithms and graph databases, including troubleshooting and enhancing query performance.', 'A6.E.4.g.24852'), ('Apply causal inference and exploratory data analysis techniques in statistical analysis and model development.', 'A6.C.4.k.21007'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Strong understanding of machine learning algorithms and techniques, including regression, classification, clustering, deep learning, statistical modeling, data mining, and data preprocessing methods.', 'A6.A.16.b.29690'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Design and create logical and physical databases using relational database principles.', 'A6.E.3.f.18280'), ('Develop and implement predictive models and algorithms to enhance decision-making across various business functions.', 'A6.J.4.f.28483'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Train machine learning algorithms for data classification and speech recognition.', 'A6.J.11.f.29893'), ('Research and develop improvements to existing and new signal processing algorithms.', 'A6.G.0.z.19221'), ('Apply optimization theory and statistical methods, including sampling and probability theory.', 'A6.B.5.c.27256'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Develop and implement object detection, classification, and segmentation algorithms for image and video analysis.', 'A6.G.0.g.28401'), ('Create and develop predictive models and machine-learning algorithms using various techniques.', 'A6.J.11.g.29774'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Develop and implement large language models (LLMs) for tasks in natural language processing, including training, fine-tuning, prompt engineering, and application in business workflows.', 'A6.J.10.a.29505'), ('Design and develop AI algorithms and solutions for various applications, including conversational systems, intelligent agents, and generative AI tools.', 'A6.J.4.d.29651'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Ability to share and apply knowledge, experience, and skills effectively.', 'A6.A.4.b.13239'), ('In-depth understanding of modern machine learning techniques and theory.', 'A6.A.16.a.29745')]</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -17601,25 +17601,25 @@
         </is>
       </c>
       <c r="R103" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="S103" t="n">
         <v>19</v>
       </c>
       <c r="T103" t="n">
-        <v>0.694</v>
+        <v>0.676</v>
       </c>
       <c r="U103" t="n">
-        <v>0.75</v>
+        <v>0.746</v>
       </c>
       <c r="V103" t="n">
-        <v>0.747</v>
+        <v>0.702</v>
       </c>
       <c r="W103" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X103" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>[('7371', 'Develop mathematical or statistical models of phenomena to be used for analysis or for computational simulation.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('7371', 'Develop mathematical or statistical models of phenomena to be used for analysis or for computational simulation.'), ('21669', 'Develop or direct software system testing or validation procedures, programming, or documentation.')]</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -17913,7 +17913,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('10902', 'Develop, test, or program new robots.'), ('21123', 'Select and invite guest speakers to speak to classes.')]</t>
+          <t>[('19232', 'Operate optical systems to capture dynamic magnetic resonance imaging (MRI) images, such as functional brain imaging, real-time organ motion tracking, or musculoskeletal anatomy and trajectory visualization.'), ('21057', 'Build, configure, or test robots or robotic applications.'), ('23242', 'Operate typing, adding, calculating, or billing machines.'), ('16136', 'Identify or monitor current and potential customers, using business intelligence tools.'), ('21325', 'Network within communities to find and attract new business.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('7277', 'Analyze data gathered and develop solutions or alternative methods of proceeding.'), ('21076', 'Answer telephones and assist customers with their questions.'), ('19637', 'Research computerized automotive applications, such as telemetrics, intelligent transportation systems, artificial intelligence, or automatic control.'), ('10901', 'Train others to install, use, or maintain robots.'), ('10902', 'Develop, test, or program new robots.'), ('16511', 'Provide technical support for robotic systems.'), ('7378', 'Collaborate with others in the organization to ensure successful implementation of chosen problem solutions.'), ('21123', 'Select and invite guest speakers to speak to classes.'), ('12961', 'Present research findings to groups of people.')]</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[('Develop predictive models and evaluate their performance using statistical and algorithmic solutions.', 'A6.J.3.a.29835'), ('Ability to identify and leverage AI and machine learning technologies to enhance products, optimize processes, and improve customer experiences.', 'A6.J.4.i.27367'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Apply AI/ML techniques to forecasting, anomaly detection, and treasury analytics.', 'A6.J.8.b.26756'), ('Develop and maintain documentation for AI models, processes, and systems.', 'A6.J.2.h.24799'), ('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Manages the integration of AI models and algorithms into big data platforms, ensuring proper handling of structured and unstructured data.', 'A6.A.14.z.25472'), ('Knowledge of AI technologies and their applications in customer care, scientific research, marketing, decision-making systems, and innovative solutions.', 'A6.D.1.e.28844'), ('Ability to develop and manage state-of-the-art predictive algorithms that utilize large-scale data to automate and optimize decisions.', 'A6.J.6.g.27239'), ('Leverage big data technologies to analyze large datasets and derive insights for improving business outcomes and decision-making.', 'A6.D.0.ae.27944'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('Research, design, implement, and evaluate machine learning and deep learning algorithms to address various applications.', 'A6.J.6.b.29200'), ('Build and optimize algorithms and models to enhance the marketplace impact and operational efficiency of autonomous vehicles.', 'A6.E.1.f.28214'), ('Familiarity with robotics process automation (RPA) technologies and their integration with automation systems.', 'A6.A.15.o.24405'), ('Identify opportunities for automation and AI integration to enhance processes and product capabilities.', 'A6.C.9.j.23380'), ('Expertise in driving and implementing digital transformation through process design, innovation, automation, and data strategy, with a focus on workforce management systems and analytics.', 'A6.A.14.h.16736')]</t>
+          <t>[('Knowledgeable in the application of advanced technologies like LLMs, computer vision, encryption, and autonomous vehicles across various fields including healthcare and deep learning.', 'A6.J.2.n.24591'), ('Familiarity with robotics, machine learning techniques, automation technologies, and advanced vehicle systems, including vision systems and sensor technologies.', 'A6.A.18.c.24823'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Automate engineering workflows and processes, including financial operations and onboarding.', 'A6.E.4.f.19063'), ('Develop predictive models and evaluate their performance using statistical and algorithmic solutions.', 'A6.J.3.a.29835'), ('Ability to stay current with emerging AI technologies and methodologies, integrating them to enhance business operations and drive innovation.', 'A6.J.2.s.26286'), ('Ability to identify and leverage AI and machine learning technologies to enhance products, optimize processes, and improve customer experiences.', 'A6.J.4.i.27367'), ('Familiarity with machine learning methodologies and experience in applying them, particularly in additive manufacturing and computational vision, is advantageous but not mandatory.', 'A6.J.11.h.23783'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Apply AI/ML techniques to forecasting, anomaly detection, and treasury analytics.', 'A6.J.8.b.26756'), ('Awareness of ethical considerations and regulatory compliance related to data privacy, bias detection, and responsible AI usage in data science and machine learning.', 'A6.G.2.k.28414'), ('Develop and maintain documentation for AI models, processes, and systems.', 'A6.J.2.h.24799'), ('Ability to apply artificial intelligence and machine learning techniques to solve complex business problems and drive new opportunities.', 'A6.A.22.c.27854'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706'), ('Manages the integration of AI models and algorithms into big data platforms, ensuring proper handling of structured and unstructured data.', 'A6.A.14.z.25472'), ('Knowledge of AI technologies and their applications in customer care, scientific research, marketing, decision-making systems, and innovative solutions.', 'A6.D.1.e.28844'), ('Ability to translate business needs into actionable data analysis and AI model development to enhance performance and drive value creation.', 'A6.D.0.a.22636'), ('Leads the development of advanced AI and machine learning models to address complex business challenges.', 'A6.I.0.c.29579'), ('Ability to develop and manage state-of-the-art predictive algorithms that utilize large-scale data to automate and optimize decisions.', 'A6.J.6.g.27239'), ('Leverage big data technologies to analyze large datasets and derive insights for improving business outcomes and decision-making.', 'A6.D.0.ae.27944'), ('Investigate new technologies, methodologies, and data sources for potential applications and algorithm development.', 'A6.J.2.q.23085'), ('Deep understanding of machine learning and deep learning concepts, algorithms, architectures, and optimization techniques.', 'A6.J.14.d.29426'), ('Research, design, implement, and evaluate machine learning and deep learning algorithms to address various applications.', 'A6.J.6.b.29200'), ('Leverage deep learning and machine learning techniques to train AI models on large datasets for generating original, human-like content.', 'A6.J.3.d.27894'), ('Proficient in monitoring and responding to customer issues on social media and other platforms, managing chatbot interactions, and ensuring effective communication through live chat and email support.', 'A6.H.3.g.20886'), ('Develop and enhance conversational AI solutions such as chatbots and virtual assistants, utilizing natural language processing and digital messaging strategies.', 'A6.J.2.h.29414'), ('Ability to collaborate with security and risk leaders to identify, anticipate, and mitigate manipulation risks in AI systems, ensuring ethical implementation and restoring trust.', 'A6.J.9.g.24325'), ('Collaborate with AI engineers and researchers to integrate AI/ML algorithms into applications and productionize inference for embedding models and rerankers.', 'A6.J.6.b.27701'), ('Build and optimize algorithms and models to enhance the marketplace impact and operational efficiency of autonomous vehicles.', 'A6.E.1.f.28214'), ('Design, develop, and implement AI models and algorithms, focusing on multimodal data integration and ethical implications.', 'A6.J.4.d.29589'), ('Develop, implement, and test control algorithms and AI/ML models for robotic systems, including motion trajectory planning, sensor integration, and safety features.', 'A6.G.0.z.27853'), ('Ability to collaborate with cross-functional teams to design, integrate, deploy, and optimize software and hardware for robotic systems.', 'A6.H.6.a.22278'), ('Familiarity with robotics process automation (RPA) technologies and their integration with automation systems.', 'A6.A.15.o.24405'), ('Develop and implement innovative solutions using artificial intelligence and Generative AI to enhance productivity and improve business functions.', 'A6.J.4.e.28950'), ('Ability to drive the adoption and implementation of AI, machine learning, and automation tools to enhance workflows, operational processes, and data management across the organization.', 'A6.J.4.i.26045'), ('Design and develop predictive models to support business decision-making and inform business strategy.', 'A6.J.8.j.26834'), ('Identify opportunities for automation and AI integration to enhance processes and product capabilities.', 'A6.C.9.j.23380'), ('Expertise in driving and implementing digital transformation through process design, innovation, automation, and data strategy, with a focus on workforce management systems and analytics.', 'A6.A.14.h.16736'), ('Designs and implements automation strategies and systems to enhance operational efficiency and reduce manual workflows.', 'A6.C.9.d.17458'), ('Interest in developing and applying machine learning and AI to create impactful, scalable solutions for businesses and customers.', 'A6.J.11.e.26799'), ('Ability to evaluate and adapt emerging AI technologies and tools to align with data privacy regulations and support legal practices.', 'A6.J.2.s.27797')]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -17932,25 +17932,25 @@
         </is>
       </c>
       <c r="R105" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="S105" t="n">
         <v>13</v>
       </c>
       <c r="T105" t="n">
-        <v>0.619</v>
+        <v>0.602</v>
       </c>
       <c r="U105" t="n">
-        <v>0.665</v>
+        <v>0.644</v>
       </c>
       <c r="V105" t="n">
-        <v>0.635</v>
+        <v>0.618</v>
       </c>
       <c r="W105" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="X105" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="106">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>[('16891', 'Create complex and dynamic mathematical models of population, community, or ecological systems.'), ('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('7207', 'Design or coordinate successive phases of problem analysis, solution proposals, or testing.'), ('20327', 'Improve search-related activities through ongoing analysis, experimentation, or optimization tests, using A/B or multivariate methods.'), ('374', 'Identify and document goals, anticipated progress, and plans for reevaluation.'), ('16891', 'Create complex and dynamic mathematical models of population, community, or ecological systems.'), ('16123', 'Perform system analysis, data analysis or programming, using a variety of computer languages and procedures.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('20230', 'Provide advice on best practices and implementation for selection.')]</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>[('Expertise in applying machine learning algorithms to large sets of structured and unstructured data for solving problems in pattern recognition, target detection, tracking, decision support systems, and robotics.', 'A6.J.7.e.29564'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151')]</t>
+          <t>[('Develop and implement complex AI/ML algorithms and models.', 'A6.J.4.e.29873'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Build and optimize efficient, scalable information retrieval systems and search algorithms.', 'A6.E.6.l.24698'), ('Develop and implement robotic algorithms for navigation, perception, planning, and sensor processing.', 'A6.G.0.z.29153'), ('Demonstrates independent and strategic problem-solving skills in planning and decision making.', 'A6.B.3.b.13430'), ('Expertise in applying machine learning algorithms to large sets of structured and unstructured data for solving problems in pattern recognition, target detection, tracking, decision support systems, and robotics.', 'A6.J.7.e.29564'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Apply machine learning algorithms for pattern recognition and predictive modeling in biological data.', 'A6.J.14.f.29796'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Design, develop, and implement knowledge-based systems, including ontologies, taxonomies, and knowledge graphs to support data integration and semantic search.', 'A6.G.0.j.27688'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Apply AI and machine learning techniques to build intelligent systems that enhance products and experiences.', 'A6.G.0.n.29719')]</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -18071,25 +18071,25 @@
         </is>
       </c>
       <c r="R106" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
       </c>
       <c r="T106" t="n">
-        <v>0.745</v>
+        <v>0.694</v>
       </c>
       <c r="U106" t="n">
-        <v>0.76</v>
+        <v>0.749</v>
       </c>
       <c r="V106" t="n">
-        <v>0.745</v>
+        <v>0.699</v>
       </c>
       <c r="W106" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X106" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107">
@@ -18174,7 +18174,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('16518', 'Plan mobile robot paths and teach path plans to robots.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.')]</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>[('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706')]</t>
+          <t>[('Develop and apply deep learning optimization and acceleration techniques.', 'A6.G.0.f.29603'), ('Design and implement relational database systems and architecture.', 'A6.E.3.f.23590'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Knowledge of machine learning and data science concepts and principles.', 'A6.A.16.a.29474'), ('Develop a basic understanding of artificial intelligence concepts and explore how AI tools can enhance processes and efficiency.', 'A6.J.0.a.27706')]</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -18193,25 +18193,25 @@
         </is>
       </c>
       <c r="R107" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
       </c>
       <c r="T107" t="n">
-        <v>0.628</v>
+        <v>0.669</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="V107" t="n">
-        <v>0.628</v>
+        <v>0.659</v>
       </c>
       <c r="W107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('16435', 'Build models for algorithm or control feature verification testing.'), ('8454', 'Plan and establish work schedules, assignments, and production sequences to meet production goals.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('23695', 'Plan and establish schedules.'), ('18470', 'Prepare graphic representations or drawings of proposed plans or designs.'), ('16257', 'Develop or implement data analysis algorithms.'), ('16790', 'Create novel computational approaches and analytical tools as required by research goals.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.'), ('14623', 'Analyze problems to develop solutions involving computer hardware and software.')]</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>[('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Develop feature vectors for input into machine learning algorithms.', 'A6.E.5.l.29888'), ('Develop and implement statistical models and algorithms for data-driven decision-making and business challenges.', 'A6.F.6.j.25884'), ('Prototype and evaluate optimization algorithms, such as linear programming, dynamic programming, and heuristic algorithms, for large-scale, non-linear, constrained optimization problems.', 'A6.J.9.k.19568'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Design, develop, and implement advanced AI and ML models and algorithms to solve complex business problems.', 'A6.J.7.g.27605')]</t>
+          <t>[('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Understand, implement, and codify algorithms while evaluating their performance and suitability for problem-solving in various applications.', 'A6.G.0.e.26376'), ('Design and create logical and physical databases using relational database principles.', 'A6.E.3.f.18280'), ('Familiarity with knowledge graphs, graph databases, and related algorithms for organizing and analyzing complex data.', 'A6.B.5.c.20195'), ('Develop feature vectors for input into machine learning algorithms.', 'A6.E.5.l.29888'), ('Define and assess artificial intelligence vision, strategy, and practices for defense applications.', 'A6.J.4.d.24091'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Implement and integrate machine learning and AI models into production environments, overseeing their lifecycle and improving knowledge organization strategies using ontology management and semantic enrichment tools.', 'A6.J.2.j.25485'), ('Perform fuzzy matching, text mining, and data reduction.', 'A6.D.1.k.28989'), ('Knowledge and experience in reinforcement learning algorithms and their application in decision-making systems and agent training.', 'A6.A.16.b.29244'), ('Develop and implement statistical models and algorithms for data-driven decision-making and business challenges.', 'A6.F.6.j.25884'), ('Prototype and evaluate optimization algorithms, such as linear programming, dynamic programming, and heuristic algorithms, for large-scale, non-linear, constrained optimization problems.', 'A6.J.9.k.19568'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Design, develop, and implement advanced AI and ML models and algorithms to solve complex business problems.', 'A6.J.7.g.27605')]</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -18349,25 +18349,25 @@
         </is>
       </c>
       <c r="R108" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="S108" t="n">
         <v>6</v>
       </c>
       <c r="T108" t="n">
-        <v>0.68</v>
+        <v>0.636</v>
       </c>
       <c r="U108" t="n">
-        <v>0.737</v>
+        <v>0.677</v>
       </c>
       <c r="V108" t="n">
-        <v>0.68</v>
+        <v>0.619</v>
       </c>
       <c r="W108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X108" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('9796', 'Select statistical tests for analyzing data.'), ('7380', 'Perform validation and testing of models to ensure adequacy, and reformulate models, as necessary.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('9796', 'Select statistical tests for analyzing data.'), ('12190', 'Measure customers, using tape measures, and record measurements.'), ('15693', 'Design or implement plant warehousing strategies for production materials or finished products.'), ('7380', 'Perform validation and testing of models to ensure adequacy, and reformulate models, as necessary.')]</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>[('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop and optimize machine learning models using various algorithms and techniques, including supervised, unsupervised, deep learning, and reinforcement learning.', 'A6.J.12.d.29738'), ('Conduct model training, evaluation, and validation to ensure high performance and accuracy in various applications.', 'A6.B.2.m.28668'), ('Design and implement machine learning and AI models and algorithms for real production environments.', 'A6.J.4.d.29161'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Understand and apply model evaluation metrics and techniques for model training and validation.', 'A6.J.11.g.28405'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800')]</t>
+          <t>[('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Develop and optimize machine learning models using various algorithms and techniques, including supervised, unsupervised, deep learning, and reinforcement learning.', 'A6.J.12.d.29738'), ('Conduct model training, evaluation, and validation to ensure high performance and accuracy in various applications.', 'A6.B.2.m.28668'), ('Strong understanding of feature engineering, model evaluation, performance optimization, and monitoring, including metrics related to precision, recall, bias, robustness, and scalability.', 'A6.J.6.b.29129'), ('Perform performance tuning, profiling, analysis, and optimization.', 'A6.J.8.h.21225'), ('Design and implement machine learning and AI models and algorithms for real production environments.', 'A6.J.4.d.29161'), ('Ability to utilize and conduct problem-solving techniques effectively.', 'A6.B.0.f.14814'), ('Analyze and implement greedy algorithms and dynamic programming for graph-related problems.', 'A6.J.8.g.28931'), ('Construct and search Knowledge Graphs using vector similarity search and vector databases.', 'A6.E.4.g.24174'), ('Design, develop, and implement natural language processing systems and models.', 'A6.J.11.j.29749'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Implement basic machine learning algorithms and techniques to solve specific problems.', 'A6.J.11.h.29889'), ('Understand and apply model evaluation metrics and techniques for model training and validation.', 'A6.J.11.g.28405'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800')]</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -18492,25 +18492,25 @@
         </is>
       </c>
       <c r="R109" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="S109" t="n">
         <v>12</v>
       </c>
       <c r="T109" t="n">
-        <v>0.727</v>
+        <v>0.673</v>
       </c>
       <c r="U109" t="n">
-        <v>0.716</v>
+        <v>0.763</v>
       </c>
       <c r="V109" t="n">
-        <v>0.727</v>
+        <v>0.7</v>
       </c>
       <c r="W109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X109" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.')]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('14623', 'Analyze problems to develop solutions involving computer hardware and software.'), ('15996', 'Devise or apply independent models or tools to help verify results of analytical systems.')]</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>[('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Ability to develop machine learning and artificial intelligence techniques and algorithms to solve complex business problems using both supervised and unsupervised methodologies.', 'A6.J.6.i.26996'), ('Provide software structure and validation direction for AI software solutions that integrate AI algorithms to solve applied problems.', 'A6.J.4.d.26074')]</t>
+          <t>[('Design, implement, and optimize multi-agent systems for complex problem-solving and autonomous workflows, incorporating orchestration, collaboration, and reinforcement learning techniques.', 'A6.J.8.c.29499'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Develop and implement generative AI solutions using embedding models, RAG techniques, and prompt engineering.', 'A6.J.4.e.29804'), ('Understand fundamental AI and machine learning concepts, algorithms, techniques, and workflows.', 'A6.A.16.c.29610'), ('Optimize AI algorithms and applications for performance, scalability, reliability, and cost-effectiveness.', 'A6.E.5.e.28686'), ('Ability to develop machine learning and artificial intelligence techniques and algorithms to solve complex business problems using both supervised and unsupervised methodologies.', 'A6.J.6.i.26996'), ('Provide software structure and validation direction for AI software solutions that integrate AI algorithms to solve applied problems.', 'A6.J.4.d.26074'), ('Ability to independently manage solution implementation and application design while effectively navigating ambiguity and complexity.', 'A6.H.7.e.14684')]</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -18614,25 +18614,25 @@
         </is>
       </c>
       <c r="R110" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
       </c>
       <c r="T110" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.648</v>
       </c>
       <c r="U110" t="n">
-        <v>0.635</v>
+        <v>0.668</v>
       </c>
       <c r="V110" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.648</v>
       </c>
       <c r="W110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X110" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111">
@@ -18765,7 +18765,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>[('1279', 'Assign, coordinate, and review work and activities of programming personnel.')]</t>
+          <t>[('20582', 'Compile and present evidence for court actions.'), ('1279', 'Assign, coordinate, and review work and activities of programming personnel.')]</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -18775,7 +18775,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Integrate machine learning models and AI algorithms into software applications and products.', 'A6.J.0.m.29507'), ('Demonstrates a strong interest in artificial intelligence, machine learning, automation, and their practical applications in various fields.', 'A6.A.16.c.29600'), ('Invent and develop AI algorithms and neural models for program generation and problem-solving on large-scale hardware systems.', 'A6.J.11.b.27446'), ('Support the development and optimization of inference algorithms.', 'A6.J.2.g.29899'), ('Develop and implement algorithms and data structures to solve problems using web technologies and object-oriented programming.', 'A6.G.0.e.18538'), ('Demonstrate knowledge and experience with data structures, algorithms, and software design principles.', 'A6.A.9.c.23784'), ('Apply optimization theory and statistical methods, including sampling and probability theory.', 'A6.B.5.c.27256'), ('Experience with large scale search and machine learning systems.', 'A6.G.0.f.28435'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Design and implement evaluation frameworks and metrics for agentic AI systems.', 'A6.J.4.d.29858')]</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -18784,25 +18784,25 @@
         </is>
       </c>
       <c r="R111" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S111" t="n">
         <v>7</v>
       </c>
       <c r="T111" t="n">
-        <v>0.786</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="U111" t="n">
-        <v>0.87</v>
+        <v>0.783</v>
       </c>
       <c r="V111" t="n">
-        <v>0.786</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="W111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X111" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112">
@@ -18964,7 +18964,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16123', 'Perform system analysis, data analysis or programming, using a variety of computer languages and procedures.')]</t>
+          <t>[('16577', 'Program complex robotic systems, such as vision systems.'), ('22605', 'Adhere to schedules to keep events running on time.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('16257', 'Develop or implement data analysis algorithms.'), ('7207', 'Design or coordinate successive phases of problem analysis, solution proposals, or testing.'), ('8967', 'Examine theories, such as those of probability and inference, to discover mathematical bases for new or improved methods of obtaining and evaluating numerical data.'), ('16590', 'Train robots, using artificial intelligence software or interactive training techniques, to perform simple or complex tasks, such as designing and carrying out a series of iterative tests of chemical samples.'), ('3776', 'Present and summarize cases to judges and juries.'), ('16123', 'Perform system analysis, data analysis or programming, using a variety of computer languages and procedures.')]</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Knowledge and application of machine learning techniques, algorithms, and their implementation across various fields.', 'A6.A.16.a.29819'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Implement and apply various supervised and unsupervised machine learning techniques, including decision trees, neural networks, clustering algorithms, and regression models.', 'A6.J.11.j.29598'), ('Apply AI/ML techniques to forecasting, anomaly detection, and treasury analytics.', 'A6.J.8.b.26756'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Demonstrate a solid understanding of feature engineering and model evaluation techniques.', 'A6.B.7.c.29808')]</t>
+          <t>[('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Possesses intellectual curiosity and the ability to rapidly learn new concepts, algorithms, frameworks, and technologies as needed.', 'A6.H.0.a.18070'), ('Develop prototypes and proof-of-concepts for AI applications, including natural language processing, classification, prediction, and computer vision.', 'A6.J.4.h.29504'), ('Define, build, and benchmark new algorithms and functionalities needed for the next generation of AI.', 'A6.J.8.f.29205'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Implement and apply Bayesian modeling techniques in multimodal data analysis, including feature selection and hierarchical Bayesian techniques.', 'A6.C.4.k.28775'), ('Research and evaluate new machine learning and statistics algorithms, concepts, and frameworks.', 'A6.J.3.d.27279'), ('Practical and extensive experience in supervised and unsupervised machine learning methods.', 'A6.A.16.b.29687'), ('Knowledge and application of machine learning techniques, algorithms, and their implementation across various fields.', 'A6.A.16.a.29819'), ('Proficient in Natural Language Processing and Computer Vision techniques.', 'A6.A.16.c.29866'), ('Knowledge of machine learning algorithms, models, and tools for data mining, clustering, and predictive analysis.', 'A6.J.14.d.29459'), ('Evaluate and compare optimization algorithms and related quantitative processes.', 'A6.J.11.c.23389'), ('Knowledge of machine learning concepts, algorithms, and methods.', 'A6.A.16.a.29892'), ('Implement and apply various supervised and unsupervised machine learning techniques, including decision trees, neural networks, clustering algorithms, and regression models.', 'A6.J.11.j.29598'), ('Design and develop AI algorithms and solutions for various applications, including conversational systems, intelligent agents, and generative AI tools.', 'A6.J.4.d.29651'), ('Apply AI/ML techniques to forecasting, anomaly detection, and treasury analytics.', 'A6.J.8.b.26756'), ('Integrate machine learning models and AI technologies into practical applications and deploy AI-driven solutions.', 'A6.J.0.m.29151'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Develop and implement image processing and computer vision algorithms.', 'A6.G.0.g.29805'), ('Demonstrate a solid understanding of feature engineering and model evaluation techniques.', 'A6.B.7.c.29808'), ('Develop, train, implement, and evaluate deep learning models.', 'A6.J.12.d.29879')]</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -18983,25 +18983,25 @@
         </is>
       </c>
       <c r="R112" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
       </c>
       <c r="T112" t="n">
-        <v>0.714</v>
+        <v>0.706</v>
       </c>
       <c r="U112" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="V112" t="n">
         <v>0.701</v>
       </c>
-      <c r="V112" t="n">
-        <v>0.704</v>
-      </c>
       <c r="W112" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X112" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('17713', 'Develop or apply data mining and machine learning algorithms.'), ('17557', 'Develop defense plans or tactics, using intelligence and other information.'), ('5592', 'Attend training sessions to increase knowledge and skills.')]</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>[('Demonstrate an understanding of computer science fundamentals, including data structures, algorithms, and AI/machine learning concepts.', 'A6.A.9.e.26712'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Develop and optimize algorithms for robotics perception, navigation, planning, and control systems.', 'A6.G.0.z.28415'), ('Program and prototype algorithms using MATLAB, Python, and other engineering tools.', 'A6.B.8.q.26434'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Develop and apply expertise in artificial intelligence and machine learning algorithms.', 'A6.J.4.h.29758'), ('Provide assistance in training artificial intelligence models and support advanced AI/ML and data science use cases.', 'A6.A.16.c.29359'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Apply optimization theory and statistical methods, including sampling and probability theory.', 'A6.B.5.c.27256')]</t>
+          <t>[('Demonstrate an understanding of computer science fundamentals, including data structures, algorithms, and AI/machine learning concepts.', 'A6.A.9.e.26712'), ('Develop and implement agentic systems and AI agents for automation.', 'A6.J.5.c.29890'), ('Develop and optimize algorithms for robotics perception, navigation, planning, and control systems.', 'A6.G.0.z.28415'), ('Program and prototype algorithms using MATLAB, Python, and other engineering tools.', 'A6.B.8.q.26434'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Ability to identify, investigate, and resolve problems by determining logical solutions and recommending corrective actions.', 'A6.G.6.a.15328'), ('Experience with machine learning and artificial intelligence principles.', 'A6.A.16.c.29868'), ('Possesses a basic understanding of AI and machine learning concepts and applications through experience or coursework.', 'A6.A.16.c.29590'), ('Develop and apply expertise in artificial intelligence and machine learning algorithms.', 'A6.J.4.h.29758'), ('Analyze, model, and simulate data using various tools and methods to obtain insights and support decision-making processes.', 'A6.B.6.c.24999'), ('Provide assistance in training artificial intelligence models and support advanced AI/ML and data science use cases.', 'A6.A.16.c.29359'), ('Develop and apply machine learning algorithms and mathematical optimization techniques.', 'A6.G.0.f.29723'), ('Experience in deep learning algorithms for search and recommendation systems.', 'A6.A.16.c.27070'), ('Design and create logical and physical databases using relational database principles.', 'A6.E.3.f.18280'), ('Apply optimization theory and statistical methods, including sampling and probability theory.', 'A6.B.5.c.27256')]</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -19171,25 +19171,25 @@
         </is>
       </c>
       <c r="R113" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="S113" t="n">
         <v>14</v>
       </c>
       <c r="T113" t="n">
-        <v>0.705</v>
+        <v>0.646</v>
       </c>
       <c r="U113" t="n">
         <v>0.739</v>
       </c>
       <c r="V113" t="n">
-        <v>0.705</v>
+        <v>0.652</v>
       </c>
       <c r="W113" t="n">
         <v>5</v>
       </c>
       <c r="X113" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[('11428', 'Coordinate work activities with other construction project activities.'), ('17713', 'Develop or apply data mining and machine learning algorithms.'), ('14623', 'Analyze problems to develop solutions involving computer hardware and software.')]</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -19304,7 +19304,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>[('Develop and implement artificial intelligence and machine learning techniques for various applications and data analyses.', 'A6.J.11.h.29491'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Solid understanding of machine learning concepts, algorithms, techniques, and their practical applications.', 'A6.J.3.c.29814'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Experience with neural deep learning methods and machine learning.', 'A6.A.16.c.29894'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Possess a deep understanding of machine learning models, AI validation methodologies, and advanced AI techniques, such as reinforcement learning and generative adversarial networks.', 'A6.A.16.c.28701'), ('Ability to design, develop, and implement AI models and machine learning algorithms for various high-impact projects and applications.', 'A6.J.0.n.28204')]</t>
+          <t>[('Develop and implement artificial intelligence and machine learning techniques for various applications and data analyses.', 'A6.J.11.h.29491'), ('Expertise in computer engineering and applied research across fields such as cybersecurity, artificial intelligence, machine learning, embedded systems, and advanced data analytics, focusing on cyber-physical systems, systems architecture, and hardware design.', 'A6.J.11.d.25316'), ('Hold a PhD in AI, machine learning, or a related field.', 'A6.A.16.b.29025'), ('Possess a deep understanding of machine learning models, AI validation methodologies, and advanced AI techniques, such as reinforcement learning and generative adversarial networks.', 'A6.A.16.c.28701'), ('Demonstrates creativity, collaboration, and technical proficiency while maintaining an open-minded and curious approach to projects.', 'A6.H.6.c.14392'), ('Solid understanding of machine learning and artificial intelligence concepts and fundamentals.', 'A6.A.16.b.29596'), ('Solid understanding of machine learning concepts, algorithms, techniques, and their practical applications.', 'A6.J.3.c.29814'), ('Develop and implement deep learning algorithms, including neural networks and convolutional neural networks.', 'A6.J.12.d.29646'), ('Experience with neural deep learning methods and machine learning.', 'A6.A.16.c.29894'), ('Understand concepts of artificial intelligence, machine learning, and generative AI.', 'A6.A.16.c.29800'), ('Ability to design, develop, and implement AI models and machine learning algorithms for various high-impact projects and applications.', 'A6.J.0.n.28204')]</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -19313,25 +19313,25 @@
         </is>
       </c>
       <c r="R114" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S114" t="n">
         <v>11</v>
       </c>
       <c r="T114" t="n">
-        <v>0.732</v>
+        <v>0.675</v>
       </c>
       <c r="U114" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.663</v>
       </c>
       <c r="V114" t="n">
-        <v>0.732</v>
+        <v>0.675</v>
       </c>
       <c r="W114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X114" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
